--- a/Promotions/LangMod/EN/Dialog/Drama/artificer_golem.xlsx
+++ b/Promotions/LangMod/EN/Dialog/Drama/artificer_golem.xlsx
@@ -8,7 +8,7 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="niyon" sheetId="1" state="visible" r:id="rId2"/>
+    <sheet name="golem" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="82">
   <si>
     <t xml:space="preserve">step</t>
   </si>
@@ -67,6 +67,56 @@
     <t xml:space="preserve">main</t>
   </si>
   <si>
+    <t xml:space="preserve">golemLoadData</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">!hasFlag,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">golemStateCheck</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">setFlag</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">golemStateCheck</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">,0</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">Awaiting instructions.</t>
   </si>
   <si>
@@ -88,9 +138,24 @@
     <t xml:space="preserve">choice/bye</t>
   </si>
   <si>
+    <t xml:space="preserve">end</t>
+  </si>
+  <si>
     <t xml:space="preserve">cancel</t>
   </si>
   <si>
+    <t xml:space="preserve">invoke*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golem_tutorial()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golemStateCheck,1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reload</t>
+  </si>
+  <si>
     <t xml:space="preserve">Listing available modifications.</t>
   </si>
   <si>
@@ -106,125 +171,34 @@
     <t xml:space="preserve">Memory Chip Installation.</t>
   </si>
   <si>
+    <t xml:space="preserve">normalframetutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Golem Documentation</t>
+  </si>
+  <si>
     <t xml:space="preserve">normaltutorial</t>
   </si>
   <si>
-    <t xml:space="preserve">Golem Documentation</t>
+    <t xml:space="preserve">Golem Upgrade Documentation</t>
   </si>
   <si>
     <t xml:space="preserve">componentcooldown</t>
   </si>
   <si>
-    <t xml:space="preserve">invoke*</t>
-  </si>
-  <si>
     <t xml:space="preserve">check_component_cooldown()</t>
   </si>
   <si>
     <t xml:space="preserve">tg</t>
   </si>
   <si>
-    <t xml:space="preserve">componentcapacity</t>
+    <t xml:space="preserve">componentcapacityreached</t>
   </si>
   <si>
     <t xml:space="preserve">check_component_capacity()</t>
   </si>
   <si>
     <t xml:space="preserve">componentready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasItem,artificer_golem_component_chip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit can be upgraded with a Golem Component Chip.
-However, it appears you do not have one available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">end</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit is still integrating with the recent component slot expansion. It takes 72 hours to fully integrate a new Golem Component Chip. Please wait before attempting to install another.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit cannot install any more Golem Component Chips as it has reached maximum capacity (256.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit is ready to install the Golem Component Chip.
-Do you wish to proceed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">componentinstall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes (Consumes one Golem Component Chip.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No (End.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acknowledged. Installing Golem Component Chip…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artificer_install_component_chip()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installation Complete. Beginning integration process. This unit will need 72 hours to complete the integration process and cannot take new Component Chips in this time.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">memoryready</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasItem,artificer_golem_memory_chip</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit can be upgraded with a Golem Memory Chip.
-However, it appears you do not have one available.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit is ready to install the Golem Memory Chip.
-Do you wish to proceed?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">memoryinstall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes (Consumes one Memory Chip.)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acknowledged. Installing Golem Memory Chip…</t>
-  </si>
-  <si>
-    <t xml:space="preserve">artificer_install_memory_chip()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Installation Complete.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Acknowledged. This unit shall go over the available Golem Documentation.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit can be upgraded with two different kinds of Golem Chips.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Golem Component Chip expands the available Gene Slots of this unit. However, after installation, an integration period of 72 Hours must pass before another can be installed. A maximum of 256 of these chips can be installed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Golem Memory Chip adds Feat Points to this unit. The amount of Feat Points added is dependent on the material hardness of the Golem Memory Chip added. There is no limit to how many of these chips can be installed.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">golem_tutorial()</t>
-  </si>
-  <si>
-    <t xml:space="preserve">normalframetutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reload</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hasFlag,golem_mim</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This unit is using the Mim Frame. The Mim Frame is a basic frame that values versaitility. Possessing a normal physical humanoid structure, we are able to optimize chip installations, benefiting from both kinds of chips twice as much.</t>
   </si>
   <si>
     <r>
@@ -235,8 +209,124 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">hasFlag,</t>
+      <t xml:space="preserve">hasItem,</t>
     </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC9A26D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">artificer_golem_componentchip</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit can be upgraded with a Golem Component Chip.
+However, it appears you do not have one available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit is still integrating with the recent component slot expansion. It takes 72 hours to fully integrate a new Golem Component Chip. Please wait before attempting to install another.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit cannot install any more Golem Component Chips as it has reached maximum capacity (32)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit is ready to install the Golem Component Chip.
+Do you wish to proceed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">componentinstall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes (Consumes one Golem Component Chip.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No (End.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledged. Installing Golem Component Chip…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">artificer_install_component_chip()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation Complete. Beginning integration process. This unit will need 72 hours to complete the integration process and cannot take new Component Chips in this time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">memoryready</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">hasItem,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10.5"/>
+        <color rgb="FFC9A26D"/>
+        <rFont val="JetBrains Mono"/>
+        <family val="3"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">artificer_golem_memorychip</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit can be upgraded with a Golem Memory Chip.
+However, it appears you do not have one available.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit is ready to install the Golem Memory Chip.
+Do you wish to proceed?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">memoryinstall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes (Consumes one Memory Chip.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledged. Installing Golem Memory Chip…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">artificer_install_memory_chip()</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Installation Complete.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledged. This unit shall go over the Golem Upgrade Documentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This unit can be upgraded with two different kinds of Golem Chips.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Golem Component Chip expands the available Gene Slots of this unit. However, after installation, an integration period of 72 Hours must pass before another can be installed. A maximum of 16 of these chips can be installed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Golem Memory Chip adds Feat Points to this unit. The amount of Feat Points added is dependent on the material hardness of the Golem Memory Chip added. There is no limit to how many of these chips can be installed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Return to Configuration Menu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acknowledged, this unit shall go over the Golem Frame documentation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">if_flag(golType,==1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Mim Type Frame is a basic frame that values versatility. Possessing a normal physical humanoid structure, they are able to optimize chip installations, benefiting from both kinds of chips twice as much.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -244,7 +334,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">golem_</t>
+      <t xml:space="preserve">if_flag</t>
     </r>
     <r>
       <rPr>
@@ -254,23 +344,13 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">harpy</t>
+      <t xml:space="preserve">(golType,==2)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">This unit is using the Harpy Frame. The Harpy Frame is a lightweight flight capable frame that values mobility. By sacrificing our physical durability, we possess increased mobility and evasiveness, providing aerial support for our forces.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hasFlag,</t>
-    </r>
+    <t xml:space="preserve">The Harpy Frame is a lightweight flight capable frame that values mobility. By sacrificing physical durability, they possess increased mobility and evasiveness, providing aerial recon support for allied forces.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -278,7 +358,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">golem_</t>
+      <t xml:space="preserve">if_flag</t>
     </r>
     <r>
       <rPr>
@@ -288,23 +368,13 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">siren</t>
+      <t xml:space="preserve">(golType,==3)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">This unit is using the Siren Frame. The Siren Frame is an aquatic frame that shows it's true potential in the correct environment. Designed for aquatic operations, when floating in air or water we are able to demonstrate increased mobility. We also possess a water based heat shunting system, allowing us to increase our magical output when wet.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">hasFlag,</t>
-    </r>
+    <t xml:space="preserve">The Siren Frame is an aquatic frame that shows its true potential in the correct environment. Designed for aquatic operations, when floating in air or water they are able to demonstrate increased mobility. They are also equipped a liquid based heat shunting system, allowing increased magical output when wet.</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
@@ -312,7 +382,7 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">golem_</t>
+      <t xml:space="preserve">if_flag</t>
     </r>
     <r>
       <rPr>
@@ -322,14 +392,14 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">titan</t>
+      <t xml:space="preserve">(golType,==4)</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">This unit is using the Titan Frame. The Titan Frame is a massive armored frame that is designed to be ridden. Although we are slower than the smaller golems frame types, our heavy armor and sizeable bulk make us formidable on the frontline. Our full potential is unlocked when uniting with our pilot. Together, we can uphold any mission. Protection of the Pilot is the prime directive.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">golem_tutorial_clear()</t>
+    <t xml:space="preserve">The Titan Frame is a massive armored frame that is designed to be ridden. Although they are slower than the smaller frames, their heavy armor and sizable bulk make us formidable on the front line. Their full potential is unlocked when boarded by their pilot. Together, we can uphold any mission. Protection of the Pilot is the prime directive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">That concludes the primer on Golem Frame types.</t>
   </si>
 </sst>
 </file>
@@ -339,7 +409,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -398,6 +468,19 @@
       <charset val="134"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Arial"/>
@@ -412,28 +495,24 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <sz val="10.5"/>
+      <color rgb="FFC9A26D"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FF787878"/>
+      <name val="JetBrains Mono"/>
+      <family val="3"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C5700"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10.5"/>
-      <color rgb="FF787878"/>
-      <name val="JetBrains Mono"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="10.5"/>
@@ -508,11 +587,11 @@
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="4" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -537,39 +616,43 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="22" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="21" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -577,23 +660,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -681,7 +752,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U430"/>
+  <dimension ref="A1:U439"/>
   <sheetFormatPr defaultColWidth="7.3359375" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="25"/>
@@ -747,7 +818,7 @@
       <c r="H2" s="2"/>
       <c r="I2" s="2" t="n">
         <f aca="false">MAX(I4:I1048576)</f>
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -831,13 +902,14 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
     </row>
-    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
+      <c r="B8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
       <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -845,87 +917,94 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
     </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
+      <c r="E9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>18</v>
+      </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
       <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>17</v>
-      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="I10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2"/>
-      <c r="B11" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="2"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
       <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>20</v>
-      </c>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2"/>
-      <c r="B12" s="6"/>
-      <c r="C12" s="6"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
       <c r="E12" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F12" s="2"/>
       <c r="G12" s="2"/>
       <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="6"/>
+      <c r="I12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F13" s="2"/>
       <c r="G13" s="2"/>
@@ -937,10 +1016,14 @@
     </row>
     <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2"/>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="7"/>
       <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="F14" s="2"/>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
@@ -950,15 +1033,13 @@
       <c r="L14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="6"/>
+      <c r="A15" s="2"/>
+      <c r="B15" s="5"/>
+      <c r="C15" s="7"/>
       <c r="D15" s="2"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
@@ -966,95 +1047,85 @@
       <c r="L15" s="2"/>
     </row>
     <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2"/>
-      <c r="B16" s="2"/>
-      <c r="C16" s="6"/>
+      <c r="A16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5"/>
+      <c r="C16" s="7"/>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="L16" s="6" t="s">
-        <v>23</v>
-      </c>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2"/>
-      <c r="B17" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="C17" s="6"/>
+      <c r="B17" s="5"/>
+      <c r="C17" s="7"/>
       <c r="D17" s="2"/>
       <c r="E17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="F17" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="F17" s="8" t="s">
+        <v>29</v>
+      </c>
       <c r="G17" s="2"/>
       <c r="H17" s="2"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L17" s="6"/>
-    </row>
-    <row r="18" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="3"/>
-      <c r="B18" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F18" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="3"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
     </row>
     <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2"/>
-      <c r="B19" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C19" s="2"/>
+      <c r="B19" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" s="7"/>
       <c r="D19" s="2"/>
-      <c r="E19" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F19" s="8"/>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="L19" s="6"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2"/>
-      <c r="B20" s="6"/>
-      <c r="C20" s="2"/>
+      <c r="A20" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="2"/>
+      <c r="C20" s="7"/>
       <c r="D20" s="2"/>
-      <c r="E20" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
@@ -1062,147 +1133,203 @@
       <c r="L20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6"/>
+      <c r="A21" s="2"/>
       <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
+      <c r="C21" s="7"/>
       <c r="D21" s="2"/>
-      <c r="E21" s="2" t="s">
-        <v>22</v>
-      </c>
+      <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="2"/>
       <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="I21" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="K21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2"/>
-      <c r="B22" s="5"/>
-      <c r="C22" s="2"/>
+      <c r="B22" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C22" s="7"/>
       <c r="D22" s="2"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
+      <c r="E22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F22" s="2"/>
       <c r="G22" s="2"/>
       <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="I22" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="K22" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="L22" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="6"/>
-      <c r="F23" s="6"/>
-      <c r="G23" s="2"/>
+      <c r="A23" s="3"/>
+      <c r="B23" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
       <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I23" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="O23" s="4"/>
+      <c r="P23" s="4"/>
+      <c r="Q23" s="4"/>
+      <c r="R23" s="4"/>
+      <c r="S23" s="4"/>
+      <c r="T23" s="4"/>
+      <c r="U23" s="4"/>
+    </row>
+    <row r="24" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="2"/>
-      <c r="B24" s="5" t="s">
-        <v>30</v>
+      <c r="B24" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
-      <c r="E24" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="G24" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="E24" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
       <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-    </row>
-    <row r="25" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I24" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="J24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L24" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="2"/>
-      <c r="B25" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="2"/>
+      <c r="B25" s="7" t="s">
+        <v>39</v>
+      </c>
       <c r="D25" s="2"/>
-      <c r="E25" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="G25" s="9" t="s">
-        <v>33</v>
-      </c>
+      <c r="E25" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
       <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
+      <c r="I25" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="J25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="L25" s="7" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6"/>
-      <c r="B26" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="A26" s="2"/>
+      <c r="B26" s="7"/>
+      <c r="C26" s="2"/>
       <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
+      <c r="E26" s="7" t="s">
+        <v>25</v>
+      </c>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
-      <c r="K26" s="0"/>
+      <c r="K26" s="2"/>
       <c r="L26" s="2"/>
     </row>
-    <row r="27" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="2"/>
-      <c r="B27" s="5"/>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="C27" s="2"/>
       <c r="D27" s="2"/>
-      <c r="E27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>27</v>
+      </c>
       <c r="F27" s="2"/>
       <c r="G27" s="2"/>
       <c r="H27" s="2"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="L27" s="6"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="2"/>
-      <c r="B28" s="6" t="s">
-        <v>39</v>
-      </c>
+      <c r="B28" s="5"/>
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
-      <c r="E28" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="E28" s="7"/>
+      <c r="F28" s="7"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
     </row>
     <row r="29" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6"/>
-      <c r="B29" s="2"/>
+      <c r="A29" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29" s="3"/>
       <c r="C29" s="2"/>
       <c r="D29" s="2"/>
-      <c r="E29" s="2"/>
-      <c r="F29" s="2"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
       <c r="G29" s="2"/>
       <c r="H29" s="2"/>
       <c r="I29" s="2"/>
@@ -1210,1196 +1337,1358 @@
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
     </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="B30" s="2"/>
+    <row r="30" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="2"/>
+      <c r="B30" s="5" t="s">
+        <v>41</v>
+      </c>
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
-      <c r="E30" s="6"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
+      <c r="E30" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G30" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H30" s="2"/>
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
     </row>
-    <row r="31" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="15.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="2"/>
-      <c r="B31" s="2"/>
+      <c r="B31" s="5" t="s">
+        <v>44</v>
+      </c>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
+      <c r="E31" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="G31" s="13" t="s">
+        <v>43</v>
+      </c>
       <c r="H31" s="2"/>
-      <c r="I31" s="7"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="L31" s="6"/>
-    </row>
-    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2"/>
-      <c r="B32" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="C32" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+    </row>
+    <row r="32" customFormat="false" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="7"/>
+      <c r="B32" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>47</v>
+      </c>
       <c r="D32" s="2"/>
-      <c r="E32" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="6"/>
+      <c r="G32" s="2"/>
       <c r="H32" s="2"/>
-      <c r="I32" s="7"/>
-      <c r="J32" s="6"/>
-      <c r="K32" s="6"/>
-      <c r="L32" s="6"/>
-    </row>
-    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I32" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="2"/>
-      <c r="B33" s="2"/>
+      <c r="B33" s="5"/>
       <c r="C33" s="2"/>
       <c r="D33" s="2"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
       <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="2"/>
+      <c r="I33" s="10" t="n">
+        <v>8</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="K33" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="L33" s="7" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="B34" s="2"/>
+      <c r="A34" s="2"/>
+      <c r="B34" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="7"/>
-      <c r="J34" s="6"/>
-      <c r="K34" s="6"/>
-      <c r="L34" s="6"/>
-    </row>
-    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="2"/>
+      <c r="E34" s="7" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7"/>
       <c r="B35" s="2"/>
-      <c r="C35" s="6"/>
+      <c r="C35" s="2"/>
       <c r="D35" s="2"/>
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="6"/>
+      <c r="G35" s="2"/>
       <c r="H35" s="2"/>
-      <c r="I35" s="7"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6" t="s">
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="L35" s="6"/>
-    </row>
-    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="2"/>
-      <c r="B36" s="6" t="s">
-        <v>39</v>
-      </c>
+      <c r="B36" s="2"/>
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
-      <c r="E36" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F36" s="6"/>
-      <c r="G36" s="6"/>
+      <c r="E36" s="7"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="7"/>
       <c r="H36" s="2"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
       <c r="L36" s="2"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-    </row>
-    <row r="37" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="37" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="2"/>
       <c r="B37" s="2"/>
-      <c r="C37" s="6"/>
+      <c r="C37" s="2"/>
       <c r="D37" s="2"/>
       <c r="E37" s="2"/>
       <c r="F37" s="2"/>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="I37" s="7"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-      <c r="S37" s="1"/>
-      <c r="T37" s="1"/>
-      <c r="U37" s="1"/>
+      <c r="I37" s="10" t="n">
+        <v>9</v>
+      </c>
+      <c r="J37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="K37" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="L37" s="7" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="6"/>
-      <c r="D38" s="6"/>
-      <c r="E38" s="2"/>
+      <c r="A38" s="2"/>
+      <c r="B38" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="F38" s="2"/>
-      <c r="G38" s="6"/>
+      <c r="G38" s="7"/>
       <c r="H38" s="2"/>
-      <c r="I38" s="7"/>
-      <c r="J38" s="6"/>
-      <c r="K38" s="6"/>
-      <c r="L38" s="6"/>
-    </row>
-    <row r="39" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I38" s="10"/>
+      <c r="J38" s="7"/>
+      <c r="K38" s="7"/>
+      <c r="L38" s="7"/>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="2"/>
-      <c r="B39" s="8"/>
-      <c r="C39" s="6"/>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
+      <c r="B39" s="2"/>
+      <c r="C39" s="2"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="7"/>
       <c r="H39" s="2"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
-      <c r="K39" s="6" t="s">
-        <v>42</v>
-      </c>
+      <c r="K39" s="2"/>
       <c r="L39" s="2"/>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="3"/>
-      <c r="B40" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="C40" s="3"/>
-      <c r="D40" s="3"/>
-      <c r="E40" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F40" s="3"/>
-      <c r="G40" s="3"/>
+      <c r="A40" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40" s="2"/>
+      <c r="C40" s="2"/>
+      <c r="D40" s="2"/>
+      <c r="E40" s="2"/>
+      <c r="F40" s="2"/>
+      <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="I40" s="3"/>
-      <c r="J40" s="3"/>
-      <c r="K40" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="L40" s="3"/>
-    </row>
-    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="5"/>
-      <c r="B41" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C41" s="6"/>
-      <c r="D41" s="6"/>
-      <c r="E41" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I40" s="10"/>
+      <c r="J40" s="7"/>
+      <c r="K40" s="7"/>
+      <c r="L40" s="7"/>
+    </row>
+    <row r="41" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="2"/>
+      <c r="B41" s="2"/>
+      <c r="C41" s="7"/>
+      <c r="D41" s="2"/>
+      <c r="E41" s="2"/>
       <c r="F41" s="2"/>
-      <c r="G41" s="6"/>
+      <c r="G41" s="7"/>
       <c r="H41" s="2"/>
-      <c r="I41" s="7"/>
-      <c r="J41" s="6"/>
-      <c r="K41" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L41" s="6"/>
+      <c r="I41" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="J41" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="L41" s="7" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="2"/>
-      <c r="B42" s="6" t="s">
-        <v>39</v>
+      <c r="B42" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
-      <c r="E42" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F42" s="6"/>
-      <c r="G42" s="6"/>
+      <c r="E42" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
       <c r="H42" s="2"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
+      <c r="O42" s="4"/>
+      <c r="P42" s="4"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
+      <c r="U42" s="4"/>
     </row>
     <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="2"/>
       <c r="B43" s="2"/>
-      <c r="C43" s="6"/>
-      <c r="D43" s="6"/>
+      <c r="C43" s="7"/>
+      <c r="D43" s="2"/>
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
       <c r="H43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="L43" s="2"/>
-    </row>
-    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="14" t="s">
-        <v>43</v>
+      <c r="I43" s="10"/>
+      <c r="J43" s="7"/>
+      <c r="K43" s="7"/>
+      <c r="L43" s="7"/>
+    </row>
+    <row r="44" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="12" t="s">
+        <v>46</v>
       </c>
       <c r="B44" s="2"/>
-      <c r="C44" s="6"/>
-      <c r="D44" s="6"/>
+      <c r="C44" s="7"/>
+      <c r="D44" s="7"/>
       <c r="E44" s="2"/>
       <c r="F44" s="2"/>
-      <c r="G44" s="2"/>
+      <c r="G44" s="7"/>
       <c r="H44" s="2"/>
-      <c r="I44" s="7"/>
-      <c r="J44" s="6"/>
-      <c r="K44" s="6"/>
-      <c r="L44" s="6"/>
-    </row>
-    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I44" s="10"/>
+      <c r="J44" s="7"/>
+      <c r="K44" s="7"/>
+      <c r="L44" s="7"/>
+      <c r="M44" s="1"/>
+      <c r="N44" s="1"/>
+      <c r="O44" s="1"/>
+      <c r="P44" s="1"/>
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+    </row>
+    <row r="45" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="2"/>
-      <c r="B45" s="2"/>
-      <c r="C45" s="2"/>
-      <c r="D45" s="2"/>
-      <c r="E45" s="2"/>
-      <c r="F45" s="2"/>
-      <c r="G45" s="6"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="7"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
       <c r="H45" s="2"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="6"/>
-      <c r="K45" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="L45" s="6"/>
-    </row>
-    <row r="46" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="2"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-      <c r="E46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="G46" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="I45" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="K45" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="L45" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="3"/>
+      <c r="B46" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C46" s="3"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F46" s="3"/>
+      <c r="G46" s="3"/>
       <c r="H46" s="2"/>
-      <c r="I46" s="2"/>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-      <c r="L46" s="2"/>
-    </row>
-    <row r="47" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
-      <c r="D47" s="2"/>
-      <c r="E47" s="2"/>
+      <c r="I46" s="3" t="n">
+        <v>12</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="5"/>
+      <c r="B47" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C47" s="7"/>
+      <c r="D47" s="7"/>
+      <c r="E47" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
+      <c r="G47" s="7"/>
       <c r="H47" s="2"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="6"/>
-      <c r="K47" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="L47" s="6"/>
+      <c r="I47" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="J47" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K47" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L47" s="7" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="2"/>
-      <c r="B48" s="6" t="s">
-        <v>39</v>
+      <c r="B48" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
-      <c r="E48" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="6"/>
+      <c r="E48" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="7"/>
+      <c r="G48" s="7"/>
       <c r="H48" s="2"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="6"/>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
     </row>
     <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2"/>
       <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
       <c r="E49" s="2"/>
       <c r="F49" s="2"/>
       <c r="G49" s="2"/>
       <c r="H49" s="2"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="6"/>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="O49" s="4"/>
-      <c r="P49" s="4"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="4"/>
-      <c r="T49" s="4"/>
-      <c r="U49" s="4"/>
-    </row>
-    <row r="50" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="14" t="s">
-        <v>26</v>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="15" t="s">
+        <v>52</v>
       </c>
       <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-      <c r="E50" s="6"/>
-      <c r="F50" s="6"/>
-      <c r="G50" s="6"/>
+      <c r="C50" s="7"/>
+      <c r="D50" s="7"/>
+      <c r="E50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
       <c r="H50" s="2"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="6"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1"/>
-      <c r="U50" s="1"/>
+      <c r="I50" s="10"/>
+      <c r="J50" s="7"/>
+      <c r="K50" s="7"/>
+      <c r="L50" s="7"/>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2"/>
-      <c r="B51" s="10" t="s">
-        <v>49</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>50</v>
-      </c>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
       <c r="D51" s="2"/>
       <c r="E51" s="2"/>
       <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
+      <c r="G51" s="7"/>
       <c r="H51" s="2"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="6"/>
-      <c r="K51" s="6"/>
-      <c r="L51" s="6"/>
-    </row>
-    <row r="52" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I51" s="10" t="n">
+        <v>14</v>
+      </c>
+      <c r="J51" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="K51" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="L51" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="2"/>
       <c r="B52" s="2"/>
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
+      <c r="E52" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="G52" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="H52" s="2"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="6"/>
-      <c r="K52" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L52" s="6"/>
-    </row>
-    <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+    </row>
+    <row r="53" customFormat="false" ht="39.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="2"/>
-      <c r="B53" s="6" t="s">
-        <v>39</v>
-      </c>
+      <c r="B53" s="2"/>
       <c r="C53" s="2"/>
       <c r="D53" s="2"/>
-      <c r="E53" s="6" t="s">
-        <v>22</v>
-      </c>
+      <c r="E53" s="2"/>
       <c r="F53" s="2"/>
       <c r="G53" s="2"/>
       <c r="H53" s="2"/>
-      <c r="I53" s="7"/>
-      <c r="J53" s="6"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="6"/>
+      <c r="I53" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="J53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K53" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="L53" s="7" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="54" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2"/>
-      <c r="B54" s="2"/>
+      <c r="B54" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
-      <c r="E54" s="2"/>
+      <c r="E54" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
+      <c r="G54" s="7"/>
       <c r="H54" s="2"/>
-      <c r="I54" s="7"/>
-      <c r="J54" s="6"/>
-      <c r="K54" s="6"/>
-      <c r="L54" s="6"/>
+      <c r="I54" s="10"/>
+      <c r="J54" s="7"/>
+      <c r="K54" s="7"/>
+      <c r="L54" s="7"/>
     </row>
     <row r="55" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="12" t="s">
-        <v>49</v>
-      </c>
+      <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
       <c r="D55" s="2"/>
-      <c r="E55" s="6"/>
-      <c r="F55" s="6"/>
-      <c r="G55" s="6"/>
+      <c r="E55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-      <c r="L55" s="2"/>
-    </row>
-    <row r="56" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="2"/>
-      <c r="B56" s="8"/>
-      <c r="C56" s="6"/>
-      <c r="D56" s="6"/>
-      <c r="E56" s="6"/>
-      <c r="F56" s="6"/>
-      <c r="G56" s="6"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="7"/>
+      <c r="K55" s="7"/>
+      <c r="L55" s="7"/>
+      <c r="O55" s="4"/>
+      <c r="P55" s="4"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="4"/>
+      <c r="T55" s="4"/>
+      <c r="U55" s="4"/>
+    </row>
+    <row r="56" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="7"/>
+      <c r="F56" s="7"/>
+      <c r="G56" s="7"/>
       <c r="H56" s="2"/>
-      <c r="I56" s="2"/>
-      <c r="J56" s="2"/>
-      <c r="K56" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="L56" s="2"/>
-      <c r="O56" s="0"/>
-      <c r="P56" s="0"/>
-      <c r="Q56" s="0"/>
-      <c r="R56" s="0"/>
-      <c r="S56" s="0"/>
-      <c r="T56" s="0"/>
-      <c r="U56" s="0"/>
-    </row>
-    <row r="57" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" s="3"/>
-      <c r="D57" s="3"/>
-      <c r="E57" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+      <c r="I56" s="10"/>
+      <c r="J56" s="7"/>
+      <c r="K56" s="7"/>
+      <c r="L56" s="7"/>
+    </row>
+    <row r="57" s="4" customFormat="true" ht="14.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="2"/>
+      <c r="B57" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D57" s="2"/>
+      <c r="E57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
       <c r="H57" s="2"/>
-      <c r="I57" s="3"/>
-      <c r="J57" s="3"/>
-      <c r="K57" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="L57" s="2"/>
-      <c r="O57" s="0"/>
-      <c r="P57" s="0"/>
-      <c r="Q57" s="0"/>
-      <c r="R57" s="0"/>
-      <c r="S57" s="0"/>
-      <c r="T57" s="0"/>
-      <c r="U57" s="0"/>
-    </row>
-    <row r="58" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="5"/>
-      <c r="B58" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="C58" s="6"/>
-      <c r="D58" s="6"/>
-      <c r="E58" s="2" t="s">
-        <v>19</v>
-      </c>
+      <c r="I57" s="10"/>
+      <c r="J57" s="7"/>
+      <c r="K57" s="7"/>
+      <c r="L57" s="7"/>
+      <c r="M57" s="1"/>
+      <c r="N57" s="1"/>
+      <c r="O57" s="1"/>
+      <c r="P57" s="1"/>
+      <c r="Q57" s="1"/>
+      <c r="R57" s="1"/>
+      <c r="S57" s="1"/>
+      <c r="T57" s="1"/>
+      <c r="U57" s="1"/>
+    </row>
+    <row r="58" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="2"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+      <c r="D58" s="2"/>
+      <c r="E58" s="2"/>
       <c r="F58" s="2"/>
-      <c r="G58" s="6"/>
+      <c r="G58" s="2"/>
       <c r="H58" s="2"/>
-      <c r="I58" s="7"/>
-      <c r="J58" s="6"/>
-      <c r="K58" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="L58" s="6"/>
-      <c r="O58" s="0"/>
-      <c r="P58" s="0"/>
-      <c r="Q58" s="0"/>
-      <c r="R58" s="0"/>
-      <c r="S58" s="0"/>
-      <c r="T58" s="0"/>
-      <c r="U58" s="0"/>
+      <c r="I58" s="10" t="n">
+        <v>16</v>
+      </c>
+      <c r="J58" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K58" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="L58" s="7" t="s">
+        <v>60</v>
+      </c>
     </row>
     <row r="59" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="2"/>
-      <c r="B59" s="6" t="s">
-        <v>39</v>
+      <c r="B59" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" s="2"/>
-      <c r="E59" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F59" s="6"/>
-      <c r="G59" s="6"/>
+      <c r="E59" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
       <c r="H59" s="2"/>
-      <c r="I59" s="2"/>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2"/>
-      <c r="L59" s="6"/>
-      <c r="O59" s="0"/>
-      <c r="P59" s="0"/>
-      <c r="Q59" s="0"/>
-      <c r="R59" s="0"/>
-      <c r="S59" s="0"/>
-      <c r="T59" s="0"/>
-      <c r="U59" s="0"/>
+      <c r="I59" s="10"/>
+      <c r="J59" s="7"/>
+      <c r="K59" s="7"/>
+      <c r="L59" s="7"/>
     </row>
     <row r="60" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="2"/>
-      <c r="B60" s="8"/>
+      <c r="B60" s="2"/>
       <c r="C60" s="2"/>
       <c r="D60" s="2"/>
       <c r="E60" s="2"/>
       <c r="F60" s="2"/>
       <c r="G60" s="2"/>
       <c r="H60" s="2"/>
-      <c r="I60" s="7"/>
-      <c r="J60" s="6"/>
-      <c r="K60" s="6"/>
-      <c r="L60" s="6"/>
+      <c r="I60" s="10"/>
+      <c r="J60" s="7"/>
+      <c r="K60" s="7"/>
+      <c r="L60" s="7"/>
     </row>
     <row r="61" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B61" s="3"/>
-      <c r="C61" s="3"/>
-      <c r="D61" s="3"/>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="G61" s="3"/>
+      <c r="A61" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+      <c r="D61" s="2"/>
+      <c r="E61" s="7"/>
+      <c r="F61" s="7"/>
+      <c r="G61" s="7"/>
       <c r="H61" s="2"/>
-      <c r="I61" s="3"/>
-      <c r="J61" s="3"/>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3"/>
-    </row>
-    <row r="62" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+    </row>
+    <row r="62" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="2"/>
-      <c r="B62" s="2"/>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
-      <c r="E62" s="2"/>
-      <c r="F62" s="2"/>
-      <c r="G62" s="6"/>
+      <c r="B62" s="11"/>
+      <c r="C62" s="7"/>
+      <c r="D62" s="7"/>
+      <c r="E62" s="7"/>
+      <c r="F62" s="7"/>
+      <c r="G62" s="7"/>
       <c r="H62" s="2"/>
-      <c r="I62" s="7"/>
-      <c r="J62" s="6"/>
-      <c r="K62" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="L62" s="6"/>
-    </row>
-    <row r="63" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="2"/>
-      <c r="B63" s="2"/>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
-      <c r="E63" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G63" s="6" t="s">
-        <v>33</v>
-      </c>
+      <c r="I62" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J62" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="K62" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="L62" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="3"/>
+      <c r="B63" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="3"/>
+      <c r="D63" s="3"/>
+      <c r="E63" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="F63" s="3"/>
+      <c r="G63" s="3"/>
       <c r="H63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="L63" s="6"/>
-    </row>
-    <row r="64" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="2"/>
-      <c r="B64" s="2"/>
-      <c r="C64" s="2"/>
-      <c r="D64" s="2"/>
-      <c r="E64" s="2"/>
+      <c r="I63" s="3" t="n">
+        <v>18</v>
+      </c>
+      <c r="J63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="L63" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="5"/>
+      <c r="B64" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" s="7"/>
+      <c r="D64" s="7"/>
+      <c r="E64" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="F64" s="2"/>
-      <c r="G64" s="2"/>
+      <c r="G64" s="7"/>
       <c r="H64" s="2"/>
-      <c r="I64" s="7"/>
-      <c r="J64" s="6"/>
-      <c r="K64" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="L64" s="6"/>
+      <c r="I64" s="10" t="n">
+        <v>19</v>
+      </c>
+      <c r="J64" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="K64" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="L64" s="7" t="s">
+        <v>54</v>
+      </c>
     </row>
     <row r="65" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="2"/>
-      <c r="B65" s="6" t="s">
-        <v>39</v>
+      <c r="B65" s="7" t="s">
+        <v>26</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" s="2"/>
-      <c r="E65" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F65" s="2"/>
-      <c r="G65" s="6"/>
+      <c r="E65" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F65" s="7"/>
+      <c r="G65" s="7"/>
       <c r="H65" s="2"/>
-      <c r="I65" s="7"/>
-      <c r="J65" s="6"/>
-      <c r="K65" s="6"/>
-      <c r="L65" s="6"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
     </row>
     <row r="66" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="2"/>
-      <c r="B66" s="2"/>
+      <c r="B66" s="11"/>
       <c r="C66" s="2"/>
       <c r="D66" s="2"/>
       <c r="E66" s="2"/>
       <c r="F66" s="2"/>
       <c r="G66" s="2"/>
       <c r="H66" s="2"/>
-      <c r="I66" s="7"/>
-      <c r="J66" s="6"/>
-      <c r="K66" s="6"/>
-      <c r="L66" s="6"/>
+      <c r="I66" s="10"/>
+      <c r="J66" s="7"/>
+      <c r="K66" s="7"/>
+      <c r="L66" s="7"/>
     </row>
     <row r="67" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="B67" s="2"/>
-      <c r="C67" s="2"/>
-      <c r="D67" s="2"/>
-      <c r="E67" s="6"/>
-      <c r="F67" s="6"/>
-      <c r="G67" s="2"/>
+      <c r="A67" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+      <c r="D67" s="3"/>
+      <c r="E67" s="3"/>
+      <c r="F67" s="3"/>
+      <c r="G67" s="3"/>
       <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
-      <c r="J67" s="2"/>
-      <c r="K67" s="2"/>
-      <c r="L67" s="2"/>
+      <c r="I67" s="3"/>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3"/>
+      <c r="L67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="2"/>
-      <c r="B68" s="10"/>
+      <c r="B68" s="2"/>
       <c r="C68" s="2"/>
       <c r="D68" s="2"/>
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="G68" s="2"/>
+      <c r="G68" s="7"/>
       <c r="H68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="L68" s="2"/>
-    </row>
-    <row r="69" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="6"/>
-      <c r="B69" s="5"/>
+      <c r="I68" s="10" t="n">
+        <v>20</v>
+      </c>
+      <c r="J68" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="K68" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="L68" s="7" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="26.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="2"/>
+      <c r="B69" s="2"/>
       <c r="C69" s="2"/>
       <c r="D69" s="2"/>
-      <c r="E69" s="2"/>
-      <c r="F69" s="2"/>
-      <c r="G69" s="2"/>
+      <c r="E69" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F69" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="G69" s="7" t="s">
+        <v>43</v>
+      </c>
       <c r="H69" s="2"/>
-      <c r="I69" s="7"/>
-      <c r="J69" s="6"/>
-      <c r="K69" s="2" t="s">
-        <v>59</v>
-      </c>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
       <c r="L69" s="2"/>
     </row>
-    <row r="70" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="70" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="2"/>
-      <c r="B70" s="6"/>
+      <c r="B70" s="2"/>
       <c r="C70" s="2"/>
       <c r="D70" s="2"/>
-      <c r="E70" s="6"/>
+      <c r="E70" s="2"/>
       <c r="F70" s="2"/>
       <c r="G70" s="2"/>
       <c r="H70" s="2"/>
-      <c r="I70" s="7"/>
-      <c r="J70" s="6"/>
-      <c r="K70" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L70" s="6"/>
-    </row>
-    <row r="71" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="12"/>
-      <c r="B71" s="2"/>
+      <c r="I70" s="10" t="n">
+        <v>21</v>
+      </c>
+      <c r="J70" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="K70" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="L70" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="2"/>
+      <c r="B71" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="C71" s="2"/>
       <c r="D71" s="2"/>
-      <c r="E71" s="2"/>
+      <c r="E71" s="7" t="s">
+        <v>27</v>
+      </c>
       <c r="F71" s="2"/>
-      <c r="G71" s="6"/>
+      <c r="G71" s="7"/>
       <c r="H71" s="2"/>
-      <c r="I71" s="7"/>
-      <c r="J71" s="6"/>
-      <c r="K71" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="L71" s="6"/>
-      <c r="O71" s="4"/>
-      <c r="P71" s="4"/>
-      <c r="Q71" s="4"/>
-      <c r="R71" s="4"/>
-      <c r="S71" s="4"/>
-      <c r="T71" s="4"/>
-      <c r="U71" s="4"/>
+      <c r="I71" s="10"/>
+      <c r="J71" s="7"/>
+      <c r="K71" s="7"/>
+      <c r="L71" s="7"/>
     </row>
     <row r="72" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="12"/>
+      <c r="A72" s="2"/>
       <c r="B72" s="2"/>
       <c r="C72" s="2"/>
       <c r="D72" s="2"/>
-      <c r="E72" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="F72" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="G72" s="6"/>
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="G72" s="2"/>
       <c r="H72" s="2"/>
-      <c r="I72" s="7"/>
-      <c r="J72" s="6"/>
-      <c r="K72" s="6"/>
-      <c r="L72" s="6"/>
-      <c r="O72" s="4"/>
-      <c r="P72" s="4"/>
-      <c r="Q72" s="4"/>
-      <c r="R72" s="4"/>
-      <c r="S72" s="4"/>
-      <c r="T72" s="4"/>
-      <c r="U72" s="4"/>
+      <c r="I72" s="10"/>
+      <c r="J72" s="7"/>
+      <c r="K72" s="7"/>
+      <c r="L72" s="7"/>
     </row>
     <row r="73" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="12"/>
-      <c r="B73" s="12" t="s">
-        <v>63</v>
-      </c>
+      <c r="A73" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B73" s="2"/>
       <c r="C73" s="2"/>
       <c r="D73" s="2"/>
-      <c r="E73" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F73" s="16"/>
-      <c r="G73" s="6"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="7"/>
+      <c r="G73" s="2"/>
       <c r="H73" s="2"/>
-      <c r="I73" s="7"/>
-      <c r="J73" s="6"/>
-      <c r="K73" s="6"/>
-      <c r="L73" s="6"/>
-      <c r="O73" s="4"/>
-      <c r="P73" s="4"/>
-      <c r="Q73" s="4"/>
-      <c r="R73" s="4"/>
-      <c r="S73" s="4"/>
-      <c r="T73" s="4"/>
-      <c r="U73" s="4"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
     </row>
     <row r="74" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="12"/>
-      <c r="B74" s="2"/>
+      <c r="A74" s="2"/>
+      <c r="B74" s="5"/>
       <c r="C74" s="2"/>
       <c r="D74" s="2"/>
       <c r="E74" s="2"/>
-      <c r="F74" s="16"/>
-      <c r="G74" s="6"/>
+      <c r="F74" s="2"/>
+      <c r="G74" s="2"/>
       <c r="H74" s="2"/>
-      <c r="I74" s="7"/>
-      <c r="J74" s="6"/>
-      <c r="K74" s="6"/>
-      <c r="L74" s="6"/>
-      <c r="O74" s="4"/>
-      <c r="P74" s="4"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="4"/>
-      <c r="T74" s="4"/>
-      <c r="U74" s="4"/>
+      <c r="I74" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="J74" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="L74" s="1" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="B75" s="2"/>
+      <c r="A75" s="7"/>
+      <c r="B75" s="5"/>
       <c r="C75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
-      <c r="F75" s="16"/>
-      <c r="G75" s="6"/>
+      <c r="F75" s="2"/>
+      <c r="G75" s="2"/>
       <c r="H75" s="2"/>
-      <c r="I75" s="7"/>
-      <c r="J75" s="6"/>
-      <c r="K75" s="6"/>
-      <c r="L75" s="6"/>
-      <c r="O75" s="4"/>
-      <c r="P75" s="4"/>
-      <c r="Q75" s="4"/>
-      <c r="R75" s="4"/>
-      <c r="S75" s="4"/>
-      <c r="T75" s="4"/>
-      <c r="U75" s="4"/>
-    </row>
-    <row r="76" s="4" customFormat="true" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I75" s="10" t="n">
+        <v>23</v>
+      </c>
+      <c r="J75" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="K75" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="L75" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="2"/>
-      <c r="B76" s="2"/>
-      <c r="C76" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="B76" s="7"/>
+      <c r="C76" s="2"/>
       <c r="D76" s="2"/>
-      <c r="E76" s="2"/>
+      <c r="E76" s="7"/>
       <c r="F76" s="2"/>
       <c r="G76" s="2"/>
       <c r="H76" s="2"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="6"/>
-      <c r="K76" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="L76" s="6"/>
-      <c r="M76" s="1"/>
-      <c r="N76" s="1"/>
-      <c r="O76" s="1"/>
-      <c r="P76" s="1"/>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1"/>
-      <c r="U76" s="1"/>
-    </row>
-    <row r="77" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="2"/>
-      <c r="B77" s="6"/>
-      <c r="C77" s="2" t="s">
-        <v>67</v>
-      </c>
+      <c r="I76" s="10" t="n">
+        <v>24</v>
+      </c>
+      <c r="J76" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K76" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="L76" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="12"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
       <c r="D77" s="2"/>
-      <c r="E77" s="6"/>
+      <c r="E77" s="2"/>
       <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
+      <c r="G77" s="7"/>
       <c r="H77" s="2"/>
-      <c r="I77" s="7"/>
-      <c r="J77" s="6"/>
-      <c r="K77" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="L77" s="6"/>
-    </row>
-    <row r="78" customFormat="false" ht="90.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="2"/>
-      <c r="B78" s="5"/>
-      <c r="C78" s="2" t="s">
-        <v>69</v>
-      </c>
+      <c r="I77" s="10" t="n">
+        <v>25</v>
+      </c>
+      <c r="J77" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="K77" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="L77" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="O77" s="4"/>
+      <c r="P77" s="4"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="4"/>
+      <c r="T77" s="4"/>
+      <c r="U77" s="4"/>
+    </row>
+    <row r="78" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="12"/>
+      <c r="B78" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C78" s="2"/>
       <c r="D78" s="2"/>
-      <c r="E78" s="6"/>
+      <c r="E78" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
+      <c r="G78" s="7"/>
       <c r="H78" s="2"/>
-      <c r="I78" s="7"/>
-      <c r="J78" s="6"/>
-      <c r="K78" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="L78" s="6"/>
+      <c r="I78" s="10" t="n">
+        <v>26</v>
+      </c>
+      <c r="J78" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K78" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L78" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="O78" s="4"/>
+      <c r="P78" s="4"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="4"/>
+      <c r="T78" s="4"/>
+      <c r="U78" s="4"/>
     </row>
     <row r="79" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="6"/>
-      <c r="B79" s="5"/>
-      <c r="C79" s="2" t="s">
-        <v>71</v>
-      </c>
+      <c r="A79" s="12"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="2"/>
       <c r="D79" s="2"/>
-      <c r="E79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
+      <c r="E79" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F79" s="8"/>
+      <c r="G79" s="7"/>
       <c r="H79" s="2"/>
-      <c r="I79" s="2"/>
-      <c r="J79" s="2"/>
-      <c r="K79" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="L79" s="2"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="7"/>
+      <c r="K79" s="7"/>
+      <c r="L79" s="7"/>
+      <c r="O79" s="4"/>
+      <c r="P79" s="4"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="4"/>
+      <c r="T79" s="4"/>
+      <c r="U79" s="4"/>
     </row>
     <row r="80" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="3"/>
-      <c r="E80" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F80" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="G80" s="3"/>
+      <c r="A80" s="12"/>
+      <c r="B80" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" s="2"/>
+      <c r="E80" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F80" s="8"/>
+      <c r="G80" s="7"/>
       <c r="H80" s="2"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3"/>
+      <c r="I80" s="10"/>
+      <c r="J80" s="7"/>
+      <c r="K80" s="7"/>
+      <c r="L80" s="7"/>
+      <c r="O80" s="4"/>
+      <c r="P80" s="4"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
+      <c r="S80" s="4"/>
+      <c r="T80" s="4"/>
+      <c r="U80" s="4"/>
     </row>
     <row r="81" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="5"/>
-      <c r="B81" s="11" t="s">
-        <v>14</v>
-      </c>
+      <c r="A81" s="12"/>
+      <c r="B81" s="2"/>
       <c r="C81" s="2"/>
       <c r="D81" s="2"/>
-      <c r="E81" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
+      <c r="E81" s="2"/>
+      <c r="F81" s="8"/>
+      <c r="G81" s="7"/>
       <c r="H81" s="2"/>
-      <c r="I81" s="7"/>
-      <c r="J81" s="6"/>
-      <c r="K81" s="6"/>
-      <c r="L81" s="6"/>
+      <c r="I81" s="10"/>
+      <c r="J81" s="7"/>
+      <c r="K81" s="7"/>
+      <c r="L81" s="7"/>
+      <c r="O81" s="4"/>
+      <c r="P81" s="4"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4"/>
+      <c r="S81" s="4"/>
+      <c r="T81" s="4"/>
+      <c r="U81" s="4"/>
     </row>
     <row r="82" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="2"/>
+      <c r="A82" s="12" t="s">
+        <v>37</v>
+      </c>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
       <c r="D82" s="2"/>
-      <c r="E82" s="6"/>
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
+      <c r="E82" s="2"/>
+      <c r="F82" s="8"/>
+      <c r="G82" s="7"/>
       <c r="H82" s="2"/>
-      <c r="I82" s="2"/>
-      <c r="J82" s="2"/>
-      <c r="K82" s="2"/>
-      <c r="L82" s="2"/>
-    </row>
-    <row r="83" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="2"/>
+      <c r="I82" s="10"/>
+      <c r="J82" s="7"/>
+      <c r="K82" s="7"/>
+      <c r="L82" s="7"/>
+      <c r="O82" s="4"/>
+      <c r="P82" s="4"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="4"/>
+      <c r="S82" s="4"/>
+      <c r="T82" s="4"/>
+      <c r="U82" s="4"/>
+    </row>
+    <row r="83" customFormat="false" ht="27.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="12"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
       <c r="D83" s="2"/>
       <c r="E83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
+      <c r="F83" s="8"/>
+      <c r="G83" s="7"/>
       <c r="H83" s="2"/>
-      <c r="I83" s="7"/>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
-      <c r="L83" s="6"/>
-    </row>
-    <row r="84" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I83" s="10" t="n">
+        <v>27</v>
+      </c>
+      <c r="J83" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="K83" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="L83" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="O83" s="4"/>
+      <c r="P83" s="4"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4"/>
+      <c r="S83" s="4"/>
+      <c r="T83" s="4"/>
+      <c r="U83" s="4"/>
+    </row>
+    <row r="84" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
       <c r="D84" s="2"/>
-      <c r="E84" s="6"/>
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
+      <c r="E84" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G84" s="7"/>
       <c r="H84" s="2"/>
-      <c r="I84" s="2"/>
-      <c r="J84" s="2"/>
-      <c r="K84" s="2"/>
-      <c r="L84" s="2"/>
-    </row>
-    <row r="85" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I84" s="10" t="n">
+        <v>28</v>
+      </c>
+      <c r="J84" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="K84" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="L84" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="2"/>
-      <c r="B85" s="8"/>
+      <c r="B85" s="7"/>
       <c r="C85" s="2"/>
       <c r="D85" s="2"/>
-      <c r="E85" s="2"/>
-      <c r="F85" s="2"/>
-      <c r="G85" s="2"/>
+      <c r="E85" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F85" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="G85" s="7"/>
       <c r="H85" s="2"/>
-      <c r="I85" s="7"/>
-      <c r="J85" s="6"/>
-      <c r="K85" s="6"/>
-      <c r="L85" s="6"/>
-    </row>
-    <row r="86" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3"/>
-      <c r="B86" s="3"/>
-      <c r="C86" s="3"/>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="3"/>
-      <c r="G86" s="3"/>
+      <c r="I85" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="J85" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K85" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="L85" s="7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="78.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="2"/>
+      <c r="B86" s="5"/>
+      <c r="C86" s="2"/>
+      <c r="D86" s="2"/>
+      <c r="E86" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F86" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="G86" s="7"/>
       <c r="H86" s="2"/>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3"/>
-    </row>
-    <row r="87" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="5"/>
-      <c r="B87" s="2"/>
+      <c r="I86" s="10" t="n">
+        <v>30</v>
+      </c>
+      <c r="J86" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="K86" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="L86" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="7"/>
+      <c r="B87" s="5"/>
       <c r="C87" s="2"/>
       <c r="D87" s="2"/>
-      <c r="E87" s="2"/>
-      <c r="F87" s="2"/>
-      <c r="G87" s="2"/>
+      <c r="E87" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F87" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="G87" s="7"/>
       <c r="H87" s="2"/>
-      <c r="I87" s="2"/>
-      <c r="J87" s="2"/>
-      <c r="K87" s="2"/>
-      <c r="L87" s="2"/>
-    </row>
-    <row r="88" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="2"/>
-      <c r="B88" s="2"/>
+      <c r="I87" s="10" t="n">
+        <v>31</v>
+      </c>
+      <c r="J87" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="K87" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="L87" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="7"/>
+      <c r="B88" s="5"/>
       <c r="C88" s="2"/>
       <c r="D88" s="2"/>
-      <c r="E88" s="6"/>
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
+      <c r="E88" s="2"/>
+      <c r="F88" s="2"/>
+      <c r="G88" s="2"/>
       <c r="H88" s="2"/>
-      <c r="I88" s="2"/>
-      <c r="J88" s="2"/>
-      <c r="K88" s="2"/>
-      <c r="L88" s="2"/>
-    </row>
-    <row r="89" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A89" s="2"/>
-      <c r="B89" s="2"/>
+      <c r="I88" s="10" t="n">
+        <v>32</v>
+      </c>
+      <c r="J88" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="K88" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="L88" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89" s="4" customFormat="true" ht="14" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="7"/>
+      <c r="B89" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="C89" s="2"/>
       <c r="D89" s="2"/>
-      <c r="E89" s="2"/>
+      <c r="E89" s="2" t="s">
+        <v>23</v>
+      </c>
       <c r="F89" s="2"/>
-      <c r="G89" s="2"/>
+      <c r="G89" s="7"/>
       <c r="H89" s="2"/>
-      <c r="I89" s="7"/>
-      <c r="J89" s="6"/>
-      <c r="K89" s="6"/>
-      <c r="L89" s="6"/>
+      <c r="I89" s="10" t="n">
+        <v>33</v>
+      </c>
+      <c r="J89" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="K89" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="L89" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="M89" s="1"/>
+      <c r="N89" s="1"/>
+      <c r="O89" s="1"/>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="1"/>
+      <c r="S89" s="1"/>
+      <c r="T89" s="1"/>
+      <c r="U89" s="1"/>
     </row>
     <row r="90" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A90" s="2"/>
-      <c r="B90" s="6"/>
+      <c r="A90" s="5"/>
+      <c r="B90" s="7"/>
       <c r="C90" s="2"/>
       <c r="D90" s="2"/>
-      <c r="E90" s="2"/>
-      <c r="F90" s="2"/>
-      <c r="G90" s="2"/>
+      <c r="E90" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" s="8"/>
+      <c r="G90" s="7"/>
       <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
-      <c r="J90" s="2"/>
-      <c r="K90" s="2"/>
-      <c r="L90" s="2"/>
+      <c r="I90" s="10"/>
+      <c r="J90" s="7"/>
+      <c r="K90" s="7"/>
+      <c r="L90" s="7"/>
     </row>
     <row r="91" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A91" s="6"/>
-      <c r="B91" s="2"/>
+      <c r="A91" s="2"/>
+      <c r="B91" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="C91" s="2"/>
       <c r="D91" s="2"/>
-      <c r="E91" s="2"/>
-      <c r="F91" s="2"/>
-      <c r="G91" s="2"/>
+      <c r="E91" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F91" s="8"/>
+      <c r="G91" s="7"/>
       <c r="H91" s="2"/>
-      <c r="I91" s="2"/>
-      <c r="J91" s="2"/>
-      <c r="K91" s="2"/>
-      <c r="L91" s="2"/>
-      <c r="O91" s="4"/>
-      <c r="P91" s="4"/>
-      <c r="Q91" s="4"/>
-      <c r="R91" s="4"/>
-      <c r="S91" s="4"/>
-      <c r="T91" s="4"/>
-      <c r="U91" s="4"/>
-    </row>
-    <row r="92" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I91" s="10"/>
+      <c r="J91" s="7"/>
+      <c r="K91" s="7"/>
+      <c r="L91" s="7"/>
+    </row>
+    <row r="92" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
       <c r="D92" s="2"/>
-      <c r="E92" s="6"/>
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
+      <c r="E92" s="2"/>
+      <c r="F92" s="2"/>
+      <c r="G92" s="2"/>
       <c r="H92" s="2"/>
-      <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2"/>
-      <c r="L92" s="2"/>
-      <c r="M92" s="1"/>
-      <c r="N92" s="1"/>
-      <c r="O92" s="1"/>
-      <c r="P92" s="1"/>
-      <c r="Q92" s="1"/>
-      <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
-      <c r="T92" s="1"/>
-      <c r="U92" s="1"/>
+      <c r="I92" s="10"/>
+      <c r="J92" s="7"/>
+      <c r="K92" s="7"/>
+      <c r="L92" s="7"/>
     </row>
     <row r="93" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
       <c r="D93" s="2"/>
-      <c r="E93" s="2"/>
-      <c r="F93" s="2"/>
-      <c r="G93" s="2"/>
+      <c r="E93" s="7"/>
+      <c r="F93" s="7"/>
+      <c r="G93" s="7"/>
       <c r="H93" s="2"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="6"/>
-      <c r="K93" s="6"/>
-      <c r="L93" s="6"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2"/>
     </row>
     <row r="94" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="2"/>
-      <c r="B94" s="2"/>
+      <c r="B94" s="11"/>
       <c r="C94" s="2"/>
       <c r="D94" s="2"/>
       <c r="E94" s="2"/>
       <c r="F94" s="2"/>
       <c r="G94" s="2"/>
       <c r="H94" s="2"/>
-      <c r="I94" s="7"/>
-      <c r="J94" s="6"/>
-      <c r="K94" s="6"/>
-      <c r="L94" s="6"/>
+      <c r="I94" s="10"/>
+      <c r="J94" s="7"/>
+      <c r="K94" s="7"/>
+      <c r="L94" s="7"/>
     </row>
     <row r="95" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="2"/>
-      <c r="B95" s="2"/>
-      <c r="C95" s="2"/>
-      <c r="D95" s="2"/>
-      <c r="E95" s="6"/>
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
+      <c r="A95" s="3"/>
+      <c r="B95" s="3"/>
+      <c r="C95" s="3"/>
+      <c r="D95" s="3"/>
+      <c r="E95" s="3"/>
+      <c r="F95" s="3"/>
+      <c r="G95" s="3"/>
       <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
-      <c r="J95" s="2"/>
-      <c r="K95" s="2"/>
-      <c r="L95" s="2"/>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="3"/>
+      <c r="L95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A96" s="2"/>
+      <c r="A96" s="5"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
       <c r="D96" s="2"/>
@@ -2407,99 +2696,90 @@
       <c r="F96" s="2"/>
       <c r="G96" s="2"/>
       <c r="H96" s="2"/>
-      <c r="I96" s="7"/>
-      <c r="J96" s="6"/>
-      <c r="K96" s="6"/>
-      <c r="L96" s="6"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
     </row>
     <row r="97" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="2"/>
-      <c r="B97" s="8"/>
+      <c r="B97" s="2"/>
       <c r="C97" s="2"/>
       <c r="D97" s="2"/>
-      <c r="E97" s="6"/>
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
+      <c r="E97" s="7"/>
+      <c r="F97" s="7"/>
+      <c r="G97" s="7"/>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
       <c r="J97" s="2"/>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
-      <c r="O97" s="4"/>
-      <c r="P97" s="4"/>
-      <c r="Q97" s="4"/>
-      <c r="R97" s="4"/>
-      <c r="S97" s="4"/>
-      <c r="T97" s="4"/>
-      <c r="U97" s="4"/>
-    </row>
-    <row r="98" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A98" s="3"/>
-      <c r="B98" s="3"/>
-      <c r="C98" s="3"/>
-      <c r="D98" s="3"/>
-      <c r="E98" s="3"/>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
+    </row>
+    <row r="98" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="2"/>
+      <c r="B98" s="2"/>
+      <c r="C98" s="2"/>
+      <c r="D98" s="2"/>
+      <c r="E98" s="2"/>
+      <c r="F98" s="2"/>
+      <c r="G98" s="2"/>
       <c r="H98" s="2"/>
-      <c r="I98" s="3"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
-      <c r="L98" s="3"/>
-      <c r="M98" s="1"/>
-      <c r="N98" s="1"/>
-      <c r="O98" s="1"/>
-      <c r="P98" s="1"/>
-      <c r="Q98" s="1"/>
-      <c r="R98" s="1"/>
-      <c r="S98" s="1"/>
-      <c r="T98" s="1"/>
-      <c r="U98" s="1"/>
+      <c r="I98" s="10"/>
+      <c r="J98" s="7"/>
+      <c r="K98" s="7"/>
+      <c r="L98" s="7"/>
     </row>
     <row r="99" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="5"/>
-      <c r="B99" s="2"/>
+      <c r="A99" s="2"/>
+      <c r="B99" s="7"/>
       <c r="C99" s="2"/>
       <c r="D99" s="2"/>
       <c r="E99" s="2"/>
       <c r="F99" s="2"/>
       <c r="G99" s="2"/>
       <c r="H99" s="2"/>
-      <c r="I99" s="7"/>
-      <c r="J99" s="6"/>
-      <c r="K99" s="6"/>
-      <c r="L99" s="6"/>
+      <c r="I99" s="2"/>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
     </row>
     <row r="100" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="2"/>
-      <c r="B100" s="6"/>
+      <c r="A100" s="7"/>
+      <c r="B100" s="2"/>
       <c r="C100" s="2"/>
       <c r="D100" s="2"/>
-      <c r="E100" s="6"/>
+      <c r="E100" s="2"/>
       <c r="F100" s="2"/>
-      <c r="G100" s="6"/>
+      <c r="G100" s="2"/>
       <c r="H100" s="2"/>
-      <c r="I100" s="7"/>
-      <c r="J100" s="6"/>
-      <c r="K100" s="6"/>
-      <c r="L100" s="6"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="O100" s="4"/>
+      <c r="P100" s="4"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4"/>
+      <c r="S100" s="4"/>
+      <c r="T100" s="4"/>
+      <c r="U100" s="4"/>
     </row>
     <row r="101" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="2"/>
-      <c r="B101" s="6"/>
+      <c r="B101" s="2"/>
       <c r="C101" s="2"/>
       <c r="D101" s="2"/>
-      <c r="E101" s="6"/>
-      <c r="F101" s="2"/>
-      <c r="G101" s="6"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
       <c r="H101" s="2"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="6"/>
-      <c r="K101" s="6"/>
-      <c r="L101" s="6"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
     </row>
     <row r="102" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A102" s="6"/>
+      <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
       <c r="D102" s="2"/>
@@ -2507,38 +2787,38 @@
       <c r="F102" s="2"/>
       <c r="G102" s="2"/>
       <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-      <c r="K102" s="2"/>
-      <c r="L102" s="2"/>
+      <c r="I102" s="10"/>
+      <c r="J102" s="7"/>
+      <c r="K102" s="7"/>
+      <c r="L102" s="7"/>
     </row>
     <row r="103" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
       <c r="D103" s="2"/>
-      <c r="E103" s="6"/>
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
+      <c r="E103" s="2"/>
+      <c r="F103" s="2"/>
+      <c r="G103" s="2"/>
       <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-      <c r="K103" s="2"/>
-      <c r="L103" s="2"/>
+      <c r="I103" s="10"/>
+      <c r="J103" s="7"/>
+      <c r="K103" s="7"/>
+      <c r="L103" s="7"/>
     </row>
     <row r="104" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
       <c r="D104" s="2"/>
-      <c r="E104" s="2"/>
-      <c r="F104" s="2"/>
-      <c r="G104" s="2"/>
+      <c r="E104" s="7"/>
+      <c r="F104" s="7"/>
+      <c r="G104" s="7"/>
       <c r="H104" s="2"/>
-      <c r="I104" s="7"/>
-      <c r="J104" s="6"/>
-      <c r="K104" s="6"/>
-      <c r="L104" s="6"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
     </row>
     <row r="105" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="2"/>
@@ -2547,106 +2827,106 @@
       <c r="D105" s="2"/>
       <c r="E105" s="2"/>
       <c r="F105" s="2"/>
-      <c r="G105" s="6"/>
+      <c r="G105" s="2"/>
       <c r="H105" s="2"/>
-      <c r="I105" s="7"/>
-      <c r="J105" s="6"/>
-      <c r="K105" s="6"/>
-      <c r="L105" s="6"/>
+      <c r="I105" s="10"/>
+      <c r="J105" s="7"/>
+      <c r="K105" s="7"/>
+      <c r="L105" s="7"/>
     </row>
     <row r="106" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="2"/>
-      <c r="B106" s="2"/>
+      <c r="B106" s="11"/>
       <c r="C106" s="2"/>
       <c r="D106" s="2"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
+      <c r="E106" s="7"/>
+      <c r="F106" s="7"/>
+      <c r="G106" s="7"/>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
-    </row>
-    <row r="107" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="2"/>
-      <c r="B107" s="2"/>
-      <c r="C107" s="2"/>
-      <c r="D107" s="2"/>
-      <c r="E107" s="2"/>
-      <c r="F107" s="2"/>
-      <c r="G107" s="2"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="4"/>
+      <c r="T106" s="4"/>
+      <c r="U106" s="4"/>
+    </row>
+    <row r="107" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="3"/>
+      <c r="B107" s="3"/>
+      <c r="C107" s="3"/>
+      <c r="D107" s="3"/>
+      <c r="E107" s="3"/>
+      <c r="F107" s="3"/>
+      <c r="G107" s="3"/>
       <c r="H107" s="2"/>
-      <c r="I107" s="7"/>
-      <c r="J107" s="6"/>
-      <c r="K107" s="6"/>
-      <c r="L107" s="6"/>
+      <c r="I107" s="3"/>
+      <c r="J107" s="3"/>
+      <c r="K107" s="3"/>
+      <c r="L107" s="3"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="O107" s="1"/>
+      <c r="P107" s="1"/>
+      <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+      <c r="S107" s="1"/>
+      <c r="T107" s="1"/>
+      <c r="U107" s="1"/>
     </row>
     <row r="108" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="2"/>
+      <c r="A108" s="5"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
       <c r="D108" s="2"/>
-      <c r="E108" s="6"/>
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
+      <c r="E108" s="2"/>
+      <c r="F108" s="2"/>
+      <c r="G108" s="2"/>
       <c r="H108" s="2"/>
-      <c r="I108" s="2"/>
-      <c r="J108" s="2"/>
-      <c r="K108" s="2"/>
-      <c r="L108" s="2"/>
+      <c r="I108" s="10"/>
+      <c r="J108" s="7"/>
+      <c r="K108" s="7"/>
+      <c r="L108" s="7"/>
     </row>
     <row r="109" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="2"/>
-      <c r="B109" s="5"/>
+      <c r="B109" s="7"/>
       <c r="C109" s="2"/>
       <c r="D109" s="2"/>
-      <c r="E109" s="2"/>
+      <c r="E109" s="7"/>
       <c r="F109" s="2"/>
-      <c r="G109" s="2"/>
+      <c r="G109" s="7"/>
       <c r="H109" s="2"/>
-      <c r="I109" s="7"/>
-      <c r="J109" s="6"/>
-      <c r="K109" s="6"/>
-      <c r="L109" s="6"/>
-      <c r="O109" s="4"/>
-      <c r="P109" s="4"/>
-      <c r="Q109" s="4"/>
-      <c r="R109" s="4"/>
-      <c r="S109" s="4"/>
-      <c r="T109" s="4"/>
-      <c r="U109" s="4"/>
-    </row>
-    <row r="110" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="3"/>
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="3"/>
-      <c r="E110" s="3"/>
-      <c r="F110" s="3"/>
-      <c r="G110" s="3"/>
+      <c r="I109" s="10"/>
+      <c r="J109" s="7"/>
+      <c r="K109" s="7"/>
+      <c r="L109" s="7"/>
+    </row>
+    <row r="110" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="2"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="2"/>
+      <c r="D110" s="2"/>
+      <c r="E110" s="7"/>
+      <c r="F110" s="2"/>
+      <c r="G110" s="7"/>
       <c r="H110" s="2"/>
-      <c r="I110" s="3"/>
-      <c r="J110" s="3"/>
-      <c r="K110" s="3"/>
-      <c r="L110" s="3"/>
-      <c r="M110" s="1"/>
-      <c r="N110" s="1"/>
-      <c r="O110" s="1"/>
-      <c r="P110" s="1"/>
-      <c r="Q110" s="1"/>
-      <c r="R110" s="1"/>
-      <c r="S110" s="1"/>
-      <c r="T110" s="1"/>
-      <c r="U110" s="1"/>
+      <c r="I110" s="10"/>
+      <c r="J110" s="7"/>
+      <c r="K110" s="7"/>
+      <c r="L110" s="7"/>
     </row>
     <row r="111" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="5"/>
+      <c r="A111" s="7"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
       <c r="D111" s="2"/>
-      <c r="E111" s="6"/>
-      <c r="F111" s="6"/>
+      <c r="E111" s="2"/>
+      <c r="F111" s="2"/>
       <c r="G111" s="2"/>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
@@ -2656,20 +2936,20 @@
     </row>
     <row r="112" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="2"/>
-      <c r="B112" s="6"/>
+      <c r="B112" s="2"/>
       <c r="C112" s="2"/>
       <c r="D112" s="2"/>
-      <c r="E112" s="6"/>
-      <c r="F112" s="2"/>
-      <c r="G112" s="2"/>
+      <c r="E112" s="7"/>
+      <c r="F112" s="7"/>
+      <c r="G112" s="7"/>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
       <c r="K112" s="2"/>
       <c r="L112" s="2"/>
     </row>
-    <row r="113" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="6"/>
+    <row r="113" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
       <c r="D113" s="2"/>
@@ -2677,38 +2957,47 @@
       <c r="F113" s="2"/>
       <c r="G113" s="2"/>
       <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-      <c r="K113" s="2"/>
-      <c r="L113" s="2"/>
+      <c r="I113" s="10"/>
+      <c r="J113" s="7"/>
+      <c r="K113" s="7"/>
+      <c r="L113" s="7"/>
+      <c r="M113" s="1"/>
+      <c r="N113" s="1"/>
+      <c r="O113" s="1"/>
+      <c r="P113" s="1"/>
+      <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+      <c r="S113" s="1"/>
+      <c r="T113" s="1"/>
+      <c r="U113" s="1"/>
     </row>
     <row r="114" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
       <c r="D114" s="2"/>
-      <c r="E114" s="6"/>
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
+      <c r="E114" s="2"/>
+      <c r="F114" s="2"/>
+      <c r="G114" s="7"/>
       <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
-      <c r="K114" s="2"/>
-      <c r="L114" s="2"/>
+      <c r="I114" s="10"/>
+      <c r="J114" s="7"/>
+      <c r="K114" s="7"/>
+      <c r="L114" s="7"/>
     </row>
     <row r="115" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
       <c r="D115" s="2"/>
-      <c r="E115" s="2"/>
-      <c r="F115" s="2"/>
-      <c r="G115" s="2"/>
+      <c r="E115" s="7"/>
+      <c r="F115" s="7"/>
+      <c r="G115" s="7"/>
       <c r="H115" s="2"/>
-      <c r="I115" s="7"/>
-      <c r="J115" s="6"/>
-      <c r="K115" s="6"/>
-      <c r="L115" s="6"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
     </row>
     <row r="116" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="2"/>
@@ -2717,21 +3006,21 @@
       <c r="D116" s="2"/>
       <c r="E116" s="2"/>
       <c r="F116" s="2"/>
-      <c r="G116" s="6"/>
+      <c r="G116" s="2"/>
       <c r="H116" s="2"/>
-      <c r="I116" s="7"/>
-      <c r="J116" s="6"/>
-      <c r="K116" s="6"/>
-      <c r="L116" s="6"/>
+      <c r="I116" s="10"/>
+      <c r="J116" s="7"/>
+      <c r="K116" s="7"/>
+      <c r="L116" s="7"/>
     </row>
     <row r="117" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="2"/>
-      <c r="B117" s="8"/>
+      <c r="B117" s="2"/>
       <c r="C117" s="2"/>
       <c r="D117" s="2"/>
-      <c r="E117" s="6"/>
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
+      <c r="E117" s="7"/>
+      <c r="F117" s="7"/>
+      <c r="G117" s="7"/>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
       <c r="J117" s="2"/>
@@ -2739,41 +3028,48 @@
       <c r="L117" s="2"/>
     </row>
     <row r="118" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A118" s="3"/>
-      <c r="B118" s="3"/>
-      <c r="C118" s="3"/>
-      <c r="D118" s="3"/>
-      <c r="E118" s="3"/>
-      <c r="F118" s="3"/>
-      <c r="G118" s="3"/>
+      <c r="A118" s="2"/>
+      <c r="B118" s="5"/>
+      <c r="C118" s="2"/>
+      <c r="D118" s="2"/>
+      <c r="E118" s="2"/>
+      <c r="F118" s="2"/>
+      <c r="G118" s="2"/>
       <c r="H118" s="2"/>
-      <c r="I118" s="3"/>
-      <c r="J118" s="3"/>
-      <c r="K118" s="3"/>
-      <c r="L118" s="3"/>
+      <c r="I118" s="10"/>
+      <c r="J118" s="7"/>
+      <c r="K118" s="7"/>
+      <c r="L118" s="7"/>
+      <c r="O118" s="4"/>
+      <c r="P118" s="4"/>
+      <c r="Q118" s="4"/>
+      <c r="R118" s="4"/>
+      <c r="S118" s="4"/>
+      <c r="T118" s="4"/>
+      <c r="U118" s="4"/>
     </row>
     <row r="119" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A119" s="5"/>
-      <c r="B119" s="2"/>
-      <c r="C119" s="2"/>
-      <c r="D119" s="2"/>
-      <c r="E119" s="2"/>
-      <c r="F119" s="2"/>
-      <c r="G119" s="6"/>
+      <c r="A119" s="3"/>
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="3"/>
+      <c r="E119" s="3"/>
+      <c r="F119" s="3"/>
+      <c r="G119" s="3"/>
       <c r="H119" s="2"/>
-      <c r="I119" s="7"/>
-      <c r="J119" s="6"/>
-      <c r="K119" s="6"/>
-      <c r="L119" s="6"/>
+      <c r="I119" s="3"/>
+      <c r="J119" s="3"/>
+      <c r="K119" s="3"/>
+      <c r="L119" s="3"/>
     </row>
     <row r="120" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A120" s="2"/>
+      <c r="A120" s="5"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
       <c r="D120" s="2"/>
-      <c r="E120" s="6"/>
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
+      <c r="E120" s="7"/>
+      <c r="F120" s="7"/>
+      <c r="G120" s="2"/>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
       <c r="J120" s="2"/>
@@ -2782,27 +3078,20 @@
     </row>
     <row r="121" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="2"/>
-      <c r="B121" s="2"/>
+      <c r="B121" s="7"/>
       <c r="C121" s="2"/>
       <c r="D121" s="2"/>
-      <c r="E121" s="2"/>
+      <c r="E121" s="7"/>
       <c r="F121" s="2"/>
       <c r="G121" s="2"/>
       <c r="H121" s="2"/>
-      <c r="I121" s="7"/>
-      <c r="J121" s="6"/>
-      <c r="K121" s="6"/>
-      <c r="L121" s="6"/>
-      <c r="O121" s="4"/>
-      <c r="P121" s="4"/>
-      <c r="Q121" s="4"/>
-      <c r="R121" s="4"/>
-      <c r="S121" s="4"/>
-      <c r="T121" s="4"/>
-      <c r="U121" s="4"/>
-    </row>
-    <row r="122" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A122" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2"/>
+    </row>
+    <row r="122" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="7"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
       <c r="D122" s="2"/>
@@ -2810,70 +3099,70 @@
       <c r="F122" s="2"/>
       <c r="G122" s="2"/>
       <c r="H122" s="2"/>
-      <c r="I122" s="7"/>
-      <c r="J122" s="6"/>
-      <c r="K122" s="6"/>
-      <c r="L122" s="6"/>
-      <c r="M122" s="1"/>
-      <c r="N122" s="1"/>
-      <c r="O122" s="1"/>
-      <c r="P122" s="1"/>
-      <c r="Q122" s="1"/>
-      <c r="R122" s="1"/>
-      <c r="S122" s="1"/>
-      <c r="T122" s="1"/>
-      <c r="U122" s="1"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
     </row>
     <row r="123" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
       <c r="D123" s="2"/>
-      <c r="E123" s="2"/>
-      <c r="F123" s="2"/>
-      <c r="G123" s="2"/>
+      <c r="E123" s="7"/>
+      <c r="F123" s="7"/>
+      <c r="G123" s="7"/>
       <c r="H123" s="2"/>
-      <c r="I123" s="7"/>
-      <c r="J123" s="6"/>
-      <c r="K123" s="6"/>
-      <c r="L123" s="6"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2"/>
     </row>
     <row r="124" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
       <c r="D124" s="2"/>
-      <c r="E124" s="6"/>
-      <c r="F124" s="6"/>
-      <c r="G124" s="6"/>
+      <c r="E124" s="2"/>
+      <c r="F124" s="2"/>
+      <c r="G124" s="2"/>
       <c r="H124" s="2"/>
-      <c r="I124" s="2"/>
-      <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
-      <c r="L124" s="2"/>
-    </row>
-    <row r="125" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="I124" s="10"/>
+      <c r="J124" s="7"/>
+      <c r="K124" s="7"/>
+      <c r="L124" s="7"/>
+    </row>
+    <row r="125" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
       <c r="D125" s="2"/>
-      <c r="E125" s="6"/>
-      <c r="F125" s="6"/>
-      <c r="G125" s="2"/>
+      <c r="E125" s="2"/>
+      <c r="F125" s="2"/>
+      <c r="G125" s="7"/>
       <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
-      <c r="J125" s="2"/>
-      <c r="K125" s="2"/>
-      <c r="L125" s="2"/>
+      <c r="I125" s="10"/>
+      <c r="J125" s="7"/>
+      <c r="K125" s="7"/>
+      <c r="L125" s="7"/>
+      <c r="M125" s="1"/>
+      <c r="N125" s="1"/>
+      <c r="O125" s="1"/>
+      <c r="P125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+      <c r="S125" s="1"/>
+      <c r="T125" s="1"/>
+      <c r="U125" s="1"/>
     </row>
     <row r="126" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="2"/>
-      <c r="B126" s="6"/>
+      <c r="B126" s="11"/>
       <c r="C126" s="2"/>
       <c r="D126" s="2"/>
-      <c r="E126" s="6"/>
-      <c r="F126" s="2"/>
-      <c r="G126" s="2"/>
+      <c r="E126" s="7"/>
+      <c r="F126" s="7"/>
+      <c r="G126" s="7"/>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
@@ -2888,416 +3177,407 @@
       <c r="E127" s="3"/>
       <c r="F127" s="3"/>
       <c r="G127" s="3"/>
-      <c r="H127" s="3"/>
+      <c r="H127" s="2"/>
       <c r="I127" s="3"/>
       <c r="J127" s="3"/>
       <c r="K127" s="3"/>
       <c r="L127" s="3"/>
     </row>
     <row r="128" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A128" s="3"/>
-      <c r="B128" s="3"/>
-      <c r="C128" s="3"/>
-      <c r="D128" s="3"/>
-      <c r="E128" s="6"/>
-      <c r="F128" s="6"/>
-      <c r="G128" s="6"/>
-      <c r="H128" s="3"/>
-      <c r="I128" s="3"/>
-      <c r="J128" s="3"/>
-      <c r="K128" s="3"/>
-      <c r="L128" s="3"/>
+      <c r="A128" s="5"/>
+      <c r="B128" s="2"/>
+      <c r="C128" s="2"/>
+      <c r="D128" s="2"/>
+      <c r="E128" s="2"/>
+      <c r="F128" s="2"/>
+      <c r="G128" s="7"/>
+      <c r="H128" s="2"/>
+      <c r="I128" s="10"/>
+      <c r="J128" s="7"/>
+      <c r="K128" s="7"/>
+      <c r="L128" s="7"/>
     </row>
     <row r="129" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A129" s="5"/>
+      <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
       <c r="D129" s="2"/>
-      <c r="E129" s="2"/>
-      <c r="F129" s="2"/>
-      <c r="G129" s="6"/>
-      <c r="H129" s="7"/>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="7"/>
+      <c r="H129" s="2"/>
       <c r="I129" s="2"/>
-      <c r="J129" s="6"/>
-      <c r="K129" s="6"/>
-      <c r="L129" s="6"/>
-      <c r="O129" s="4"/>
-      <c r="P129" s="4"/>
-      <c r="Q129" s="4"/>
-      <c r="R129" s="4"/>
-      <c r="S129" s="4"/>
-      <c r="T129" s="4"/>
-      <c r="U129" s="4"/>
-    </row>
-    <row r="130" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2"/>
+    </row>
+    <row r="130" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="2"/>
-      <c r="B130" s="6"/>
+      <c r="B130" s="2"/>
       <c r="C130" s="2"/>
       <c r="D130" s="2"/>
-      <c r="E130" s="6"/>
+      <c r="E130" s="2"/>
       <c r="F130" s="2"/>
       <c r="G130" s="2"/>
-      <c r="H130" s="7"/>
-      <c r="I130" s="2"/>
-      <c r="J130" s="6"/>
-      <c r="K130" s="6"/>
-      <c r="L130" s="6"/>
-      <c r="M130" s="1"/>
-      <c r="N130" s="1"/>
-      <c r="O130" s="1"/>
-      <c r="P130" s="1"/>
-      <c r="Q130" s="1"/>
-      <c r="R130" s="1"/>
-      <c r="S130" s="1"/>
-      <c r="T130" s="1"/>
-      <c r="U130" s="1"/>
+      <c r="H130" s="2"/>
+      <c r="I130" s="10"/>
+      <c r="J130" s="7"/>
+      <c r="K130" s="7"/>
+      <c r="L130" s="7"/>
+      <c r="O130" s="4"/>
+      <c r="P130" s="4"/>
+      <c r="Q130" s="4"/>
+      <c r="R130" s="4"/>
+      <c r="S130" s="4"/>
+      <c r="T130" s="4"/>
+      <c r="U130" s="4"/>
     </row>
     <row r="131" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="2"/>
-      <c r="B131" s="6"/>
-      <c r="C131" s="6"/>
+      <c r="B131" s="2"/>
+      <c r="C131" s="2"/>
       <c r="D131" s="2"/>
-      <c r="E131" s="6"/>
+      <c r="E131" s="2"/>
       <c r="F131" s="2"/>
       <c r="G131" s="2"/>
-      <c r="H131" s="7"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="6"/>
-      <c r="K131" s="6"/>
-      <c r="L131" s="6"/>
+      <c r="H131" s="2"/>
+      <c r="I131" s="10"/>
+      <c r="J131" s="7"/>
+      <c r="K131" s="7"/>
+      <c r="L131" s="7"/>
     </row>
     <row r="132" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="2"/>
-      <c r="B132" s="8"/>
-      <c r="C132" s="19"/>
+      <c r="B132" s="2"/>
+      <c r="C132" s="2"/>
       <c r="D132" s="2"/>
-      <c r="E132" s="6"/>
+      <c r="E132" s="2"/>
       <c r="F132" s="2"/>
       <c r="G132" s="2"/>
-      <c r="H132" s="7"/>
-      <c r="I132" s="2"/>
-      <c r="J132" s="6"/>
-      <c r="K132" s="6"/>
-      <c r="L132" s="6"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="10"/>
+      <c r="J132" s="7"/>
+      <c r="K132" s="7"/>
+      <c r="L132" s="7"/>
     </row>
     <row r="133" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A133" s="3"/>
-      <c r="B133" s="3"/>
-      <c r="C133" s="3"/>
-      <c r="D133" s="3"/>
-      <c r="E133" s="3"/>
-      <c r="F133" s="3"/>
-      <c r="G133" s="3"/>
-      <c r="H133" s="3"/>
-      <c r="I133" s="3"/>
-      <c r="J133" s="3"/>
-      <c r="K133" s="3"/>
-      <c r="L133" s="3"/>
+      <c r="A133" s="2"/>
+      <c r="B133" s="2"/>
+      <c r="C133" s="2"/>
+      <c r="D133" s="2"/>
+      <c r="E133" s="7"/>
+      <c r="F133" s="7"/>
+      <c r="G133" s="7"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
     </row>
     <row r="134" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="2"/>
-      <c r="B134" s="6"/>
-      <c r="C134" s="6"/>
+      <c r="B134" s="2"/>
+      <c r="C134" s="2"/>
       <c r="D134" s="2"/>
-      <c r="E134" s="6"/>
-      <c r="F134" s="2"/>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
       <c r="G134" s="2"/>
-      <c r="H134" s="7"/>
+      <c r="H134" s="2"/>
       <c r="I134" s="2"/>
-      <c r="J134" s="6"/>
-      <c r="K134" s="6"/>
-      <c r="L134" s="6"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
     </row>
     <row r="135" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="2"/>
-      <c r="B135" s="6"/>
-      <c r="C135" s="6"/>
+      <c r="B135" s="7"/>
+      <c r="C135" s="2"/>
       <c r="D135" s="2"/>
-      <c r="E135" s="6"/>
+      <c r="E135" s="7"/>
       <c r="F135" s="2"/>
       <c r="G135" s="2"/>
-      <c r="H135" s="7"/>
+      <c r="H135" s="2"/>
       <c r="I135" s="2"/>
-      <c r="J135" s="6"/>
-      <c r="K135" s="6"/>
-      <c r="L135" s="6"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
     </row>
     <row r="136" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A136" s="2"/>
-      <c r="B136" s="6"/>
-      <c r="C136" s="6"/>
-      <c r="D136" s="2"/>
-      <c r="E136" s="6"/>
-      <c r="F136" s="2"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="7"/>
-      <c r="I136" s="2"/>
-      <c r="J136" s="6"/>
-      <c r="K136" s="6"/>
-      <c r="L136" s="6"/>
-    </row>
-    <row r="137" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A137" s="2"/>
-      <c r="B137" s="6"/>
-      <c r="C137" s="6"/>
-      <c r="D137" s="2"/>
-      <c r="E137" s="6"/>
-      <c r="F137" s="2"/>
-      <c r="G137" s="2"/>
-      <c r="H137" s="7"/>
-      <c r="I137" s="2"/>
-      <c r="J137" s="6"/>
-      <c r="K137" s="6"/>
-      <c r="L137" s="6"/>
+      <c r="A136" s="3"/>
+      <c r="B136" s="3"/>
+      <c r="C136" s="3"/>
+      <c r="D136" s="3"/>
+      <c r="E136" s="3"/>
+      <c r="F136" s="3"/>
+      <c r="G136" s="3"/>
+      <c r="H136" s="3"/>
+      <c r="I136" s="3"/>
+      <c r="J136" s="3"/>
+      <c r="K136" s="3"/>
+      <c r="L136" s="3"/>
+    </row>
+    <row r="137" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A137" s="3"/>
+      <c r="B137" s="3"/>
+      <c r="C137" s="3"/>
+      <c r="D137" s="3"/>
+      <c r="E137" s="7"/>
+      <c r="F137" s="7"/>
+      <c r="G137" s="7"/>
+      <c r="H137" s="3"/>
+      <c r="I137" s="3"/>
+      <c r="J137" s="3"/>
+      <c r="K137" s="3"/>
+      <c r="L137" s="3"/>
+      <c r="M137" s="1"/>
+      <c r="N137" s="1"/>
+      <c r="O137" s="1"/>
+      <c r="P137" s="1"/>
+      <c r="Q137" s="1"/>
+      <c r="R137" s="1"/>
+      <c r="S137" s="1"/>
+      <c r="T137" s="1"/>
+      <c r="U137" s="1"/>
     </row>
     <row r="138" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A138" s="2"/>
-      <c r="B138" s="6"/>
-      <c r="C138" s="6"/>
+      <c r="A138" s="5"/>
+      <c r="B138" s="2"/>
+      <c r="C138" s="2"/>
       <c r="D138" s="2"/>
-      <c r="E138" s="6"/>
+      <c r="E138" s="2"/>
       <c r="F138" s="2"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="7"/>
+      <c r="G138" s="7"/>
+      <c r="H138" s="10"/>
       <c r="I138" s="2"/>
-      <c r="J138" s="6"/>
-      <c r="K138" s="6"/>
-      <c r="L138" s="6"/>
+      <c r="J138" s="7"/>
+      <c r="K138" s="7"/>
+      <c r="L138" s="7"/>
+      <c r="O138" s="4"/>
+      <c r="P138" s="4"/>
+      <c r="Q138" s="4"/>
+      <c r="R138" s="4"/>
+      <c r="S138" s="4"/>
+      <c r="T138" s="4"/>
+      <c r="U138" s="4"/>
     </row>
     <row r="139" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="2"/>
-      <c r="B139" s="6"/>
-      <c r="C139" s="6"/>
-      <c r="D139" s="6"/>
-      <c r="E139" s="6"/>
+      <c r="B139" s="7"/>
+      <c r="C139" s="2"/>
+      <c r="D139" s="2"/>
+      <c r="E139" s="7"/>
       <c r="F139" s="2"/>
       <c r="G139" s="2"/>
-      <c r="H139" s="7"/>
+      <c r="H139" s="10"/>
       <c r="I139" s="2"/>
-      <c r="J139" s="6"/>
-      <c r="K139" s="6"/>
-      <c r="L139" s="6"/>
+      <c r="J139" s="7"/>
+      <c r="K139" s="7"/>
+      <c r="L139" s="7"/>
     </row>
     <row r="140" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="2"/>
-      <c r="B140" s="6"/>
-      <c r="C140" s="2"/>
+      <c r="B140" s="7"/>
+      <c r="C140" s="7"/>
       <c r="D140" s="2"/>
-      <c r="E140" s="6"/>
+      <c r="E140" s="7"/>
       <c r="F140" s="2"/>
       <c r="G140" s="2"/>
-      <c r="H140" s="7"/>
+      <c r="H140" s="10"/>
       <c r="I140" s="2"/>
-      <c r="J140" s="6"/>
-      <c r="K140" s="6"/>
-      <c r="L140" s="6"/>
+      <c r="J140" s="7"/>
+      <c r="K140" s="7"/>
+      <c r="L140" s="7"/>
     </row>
     <row r="141" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="2"/>
-      <c r="B141" s="6"/>
-      <c r="C141" s="2"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="13"/>
       <c r="D141" s="2"/>
-      <c r="E141" s="6"/>
+      <c r="E141" s="7"/>
       <c r="F141" s="2"/>
       <c r="G141" s="2"/>
-      <c r="H141" s="2"/>
+      <c r="H141" s="10"/>
       <c r="I141" s="2"/>
-      <c r="J141" s="2"/>
-      <c r="K141" s="2"/>
-      <c r="L141" s="2"/>
+      <c r="J141" s="7"/>
+      <c r="K141" s="7"/>
+      <c r="L141" s="7"/>
     </row>
     <row r="142" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A142" s="6"/>
-      <c r="B142" s="2"/>
-      <c r="C142" s="2"/>
-      <c r="D142" s="2"/>
-      <c r="E142" s="2"/>
-      <c r="F142" s="2"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
-      <c r="J142" s="2"/>
-      <c r="K142" s="2"/>
-      <c r="L142" s="2"/>
-      <c r="O142" s="4"/>
-      <c r="P142" s="4"/>
-      <c r="Q142" s="4"/>
-      <c r="R142" s="4"/>
-      <c r="S142" s="4"/>
-      <c r="T142" s="4"/>
-      <c r="U142" s="4"/>
-    </row>
-    <row r="143" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A143" s="6"/>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6"/>
+      <c r="A142" s="3"/>
+      <c r="B142" s="3"/>
+      <c r="C142" s="3"/>
+      <c r="D142" s="3"/>
+      <c r="E142" s="3"/>
+      <c r="F142" s="3"/>
+      <c r="G142" s="3"/>
+      <c r="H142" s="3"/>
+      <c r="I142" s="3"/>
+      <c r="J142" s="3"/>
+      <c r="K142" s="3"/>
+      <c r="L142" s="3"/>
+    </row>
+    <row r="143" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A143" s="2"/>
+      <c r="B143" s="7"/>
+      <c r="C143" s="7"/>
       <c r="D143" s="2"/>
-      <c r="E143" s="2"/>
+      <c r="E143" s="7"/>
       <c r="F143" s="2"/>
       <c r="G143" s="2"/>
-      <c r="H143" s="2"/>
+      <c r="H143" s="10"/>
       <c r="I143" s="2"/>
-      <c r="J143" s="2"/>
-      <c r="K143" s="2"/>
-      <c r="L143" s="2"/>
-      <c r="M143" s="1"/>
-      <c r="N143" s="1"/>
-      <c r="O143" s="1"/>
-      <c r="P143" s="1"/>
-      <c r="Q143" s="1"/>
-      <c r="R143" s="1"/>
-      <c r="S143" s="1"/>
-      <c r="T143" s="1"/>
-      <c r="U143" s="1"/>
+      <c r="J143" s="7"/>
+      <c r="K143" s="7"/>
+      <c r="L143" s="7"/>
     </row>
     <row r="144" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A144" s="2"/>
-      <c r="B144" s="6"/>
-      <c r="C144" s="6"/>
+      <c r="B144" s="7"/>
+      <c r="C144" s="7"/>
       <c r="D144" s="2"/>
-      <c r="E144" s="2"/>
+      <c r="E144" s="7"/>
       <c r="F144" s="2"/>
       <c r="G144" s="2"/>
-      <c r="H144" s="2"/>
+      <c r="H144" s="10"/>
       <c r="I144" s="2"/>
-      <c r="J144" s="2"/>
-      <c r="K144" s="2"/>
-      <c r="L144" s="2"/>
-    </row>
-    <row r="145" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J144" s="7"/>
+      <c r="K144" s="7"/>
+      <c r="L144" s="7"/>
+    </row>
+    <row r="145" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A145" s="2"/>
-      <c r="B145" s="6"/>
-      <c r="C145" s="6"/>
+      <c r="B145" s="7"/>
+      <c r="C145" s="7"/>
       <c r="D145" s="2"/>
-      <c r="E145" s="2"/>
+      <c r="E145" s="7"/>
       <c r="F145" s="2"/>
       <c r="G145" s="2"/>
-      <c r="H145" s="2"/>
+      <c r="H145" s="10"/>
       <c r="I145" s="2"/>
-      <c r="J145" s="2"/>
-      <c r="K145" s="2"/>
-      <c r="L145" s="2"/>
+      <c r="J145" s="7"/>
+      <c r="K145" s="7"/>
+      <c r="L145" s="7"/>
+      <c r="M145" s="1"/>
+      <c r="N145" s="1"/>
+      <c r="O145" s="1"/>
+      <c r="P145" s="1"/>
+      <c r="Q145" s="1"/>
+      <c r="R145" s="1"/>
+      <c r="S145" s="1"/>
+      <c r="T145" s="1"/>
+      <c r="U145" s="1"/>
     </row>
     <row r="146" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A146" s="2"/>
-      <c r="B146" s="6"/>
-      <c r="C146" s="6"/>
+      <c r="B146" s="7"/>
+      <c r="C146" s="7"/>
       <c r="D146" s="2"/>
-      <c r="E146" s="2"/>
+      <c r="E146" s="7"/>
       <c r="F146" s="2"/>
       <c r="G146" s="2"/>
-      <c r="H146" s="2"/>
+      <c r="H146" s="10"/>
       <c r="I146" s="2"/>
-      <c r="J146" s="2"/>
-      <c r="K146" s="2"/>
-      <c r="L146" s="2"/>
+      <c r="J146" s="7"/>
+      <c r="K146" s="7"/>
+      <c r="L146" s="7"/>
     </row>
     <row r="147" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A147" s="2"/>
-      <c r="B147" s="6"/>
-      <c r="C147" s="6"/>
+      <c r="B147" s="7"/>
+      <c r="C147" s="7"/>
       <c r="D147" s="2"/>
-      <c r="E147" s="2"/>
+      <c r="E147" s="7"/>
       <c r="F147" s="2"/>
       <c r="G147" s="2"/>
-      <c r="H147" s="2"/>
+      <c r="H147" s="10"/>
       <c r="I147" s="2"/>
-      <c r="J147" s="2"/>
-      <c r="K147" s="2"/>
-      <c r="L147" s="2"/>
+      <c r="J147" s="7"/>
+      <c r="K147" s="7"/>
+      <c r="L147" s="7"/>
     </row>
     <row r="148" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A148" s="2"/>
-      <c r="B148" s="2"/>
-      <c r="C148" s="2"/>
-      <c r="D148" s="2"/>
-      <c r="E148" s="6"/>
-      <c r="F148" s="6"/>
-      <c r="G148" s="6"/>
-      <c r="H148" s="2"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
+      <c r="D148" s="7"/>
+      <c r="E148" s="7"/>
+      <c r="F148" s="2"/>
+      <c r="G148" s="2"/>
+      <c r="H148" s="10"/>
       <c r="I148" s="2"/>
-      <c r="J148" s="2"/>
-      <c r="K148" s="2"/>
-      <c r="L148" s="2"/>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
+      <c r="L148" s="7"/>
     </row>
     <row r="149" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A149" s="2"/>
-      <c r="B149" s="2"/>
+      <c r="B149" s="7"/>
       <c r="C149" s="2"/>
       <c r="D149" s="2"/>
-      <c r="E149" s="2"/>
+      <c r="E149" s="7"/>
       <c r="F149" s="2"/>
       <c r="G149" s="2"/>
-      <c r="H149" s="7"/>
+      <c r="H149" s="10"/>
       <c r="I149" s="2"/>
-      <c r="J149" s="6"/>
-      <c r="K149" s="6"/>
-      <c r="L149" s="6"/>
-      <c r="O149" s="4"/>
-      <c r="P149" s="4"/>
-      <c r="Q149" s="4"/>
-      <c r="R149" s="4"/>
-      <c r="S149" s="4"/>
-      <c r="T149" s="4"/>
-      <c r="U149" s="4"/>
-    </row>
-    <row r="150" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J149" s="7"/>
+      <c r="K149" s="7"/>
+      <c r="L149" s="7"/>
+    </row>
+    <row r="150" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A150" s="2"/>
-      <c r="B150" s="2"/>
-      <c r="C150" s="20"/>
+      <c r="B150" s="7"/>
+      <c r="C150" s="2"/>
       <c r="D150" s="2"/>
-      <c r="E150" s="6"/>
-      <c r="F150" s="6"/>
-      <c r="G150" s="6"/>
-      <c r="H150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="2"/>
+      <c r="G150" s="2"/>
+      <c r="H150" s="2"/>
       <c r="I150" s="2"/>
-      <c r="J150" s="19"/>
-      <c r="K150" s="19"/>
-      <c r="L150" s="19"/>
-      <c r="M150" s="1"/>
-      <c r="N150" s="1"/>
-      <c r="O150" s="1"/>
-      <c r="P150" s="1"/>
-      <c r="Q150" s="1"/>
-      <c r="R150" s="1"/>
-      <c r="S150" s="1"/>
-      <c r="T150" s="1"/>
-      <c r="U150" s="1"/>
+      <c r="J150" s="2"/>
+      <c r="K150" s="2"/>
+      <c r="L150" s="2"/>
     </row>
     <row r="151" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A151" s="2"/>
+      <c r="A151" s="7"/>
       <c r="B151" s="2"/>
-      <c r="C151" s="20"/>
+      <c r="C151" s="2"/>
       <c r="D151" s="2"/>
       <c r="E151" s="2"/>
       <c r="F151" s="2"/>
-      <c r="G151" s="19"/>
-      <c r="H151" s="7"/>
+      <c r="G151" s="2"/>
+      <c r="H151" s="2"/>
       <c r="I151" s="2"/>
-      <c r="J151" s="6"/>
-      <c r="K151" s="6"/>
-      <c r="L151" s="6"/>
+      <c r="J151" s="2"/>
+      <c r="K151" s="2"/>
+      <c r="L151" s="2"/>
+      <c r="O151" s="4"/>
+      <c r="P151" s="4"/>
+      <c r="Q151" s="4"/>
+      <c r="R151" s="4"/>
+      <c r="S151" s="4"/>
+      <c r="T151" s="4"/>
+      <c r="U151" s="4"/>
     </row>
     <row r="152" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A152" s="2"/>
-      <c r="B152" s="6"/>
-      <c r="C152" s="2"/>
+      <c r="A152" s="7"/>
+      <c r="B152" s="7"/>
+      <c r="C152" s="7"/>
       <c r="D152" s="2"/>
-      <c r="E152" s="6"/>
+      <c r="E152" s="2"/>
       <c r="F152" s="2"/>
       <c r="G152" s="2"/>
-      <c r="H152" s="7"/>
+      <c r="H152" s="2"/>
       <c r="I152" s="2"/>
-      <c r="J152" s="6"/>
-      <c r="K152" s="6"/>
-      <c r="L152" s="6"/>
+      <c r="J152" s="2"/>
+      <c r="K152" s="2"/>
+      <c r="L152" s="2"/>
     </row>
     <row r="153" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A153" s="2"/>
-      <c r="B153" s="6"/>
-      <c r="C153" s="2"/>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
       <c r="D153" s="2"/>
-      <c r="E153" s="6"/>
+      <c r="E153" s="2"/>
       <c r="F153" s="2"/>
       <c r="G153" s="2"/>
       <c r="H153" s="2"/>
@@ -3307,9 +3587,9 @@
       <c r="L153" s="2"/>
     </row>
     <row r="154" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A154" s="6"/>
-      <c r="B154" s="2"/>
-      <c r="C154" s="2"/>
+      <c r="A154" s="2"/>
+      <c r="B154" s="7"/>
+      <c r="C154" s="7"/>
       <c r="D154" s="2"/>
       <c r="E154" s="2"/>
       <c r="F154" s="2"/>
@@ -3322,12 +3602,12 @@
     </row>
     <row r="155" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A155" s="2"/>
-      <c r="B155" s="2"/>
-      <c r="C155" s="2"/>
+      <c r="B155" s="7"/>
+      <c r="C155" s="7"/>
       <c r="D155" s="2"/>
-      <c r="E155" s="6"/>
-      <c r="F155" s="6"/>
-      <c r="G155" s="6"/>
+      <c r="E155" s="2"/>
+      <c r="F155" s="2"/>
+      <c r="G155" s="2"/>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
@@ -3336,94 +3616,96 @@
     </row>
     <row r="156" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A156" s="2"/>
-      <c r="B156" s="2"/>
-      <c r="C156" s="2"/>
+      <c r="B156" s="7"/>
+      <c r="C156" s="7"/>
       <c r="D156" s="2"/>
       <c r="E156" s="2"/>
       <c r="F156" s="2"/>
       <c r="G156" s="2"/>
-      <c r="H156" s="7"/>
+      <c r="H156" s="2"/>
       <c r="I156" s="2"/>
-      <c r="J156" s="6"/>
-      <c r="K156" s="6"/>
-      <c r="L156" s="6"/>
+      <c r="J156" s="2"/>
+      <c r="K156" s="2"/>
+      <c r="L156" s="2"/>
     </row>
     <row r="157" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
       <c r="D157" s="2"/>
-      <c r="E157" s="2"/>
-      <c r="F157" s="2"/>
-      <c r="G157" s="2"/>
-      <c r="H157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="7"/>
+      <c r="G157" s="7"/>
+      <c r="H157" s="2"/>
       <c r="I157" s="2"/>
-      <c r="J157" s="6"/>
-      <c r="K157" s="6"/>
-      <c r="L157" s="6"/>
-    </row>
-    <row r="158" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J157" s="2"/>
+      <c r="K157" s="2"/>
+      <c r="L157" s="2"/>
+    </row>
+    <row r="158" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
       <c r="D158" s="2"/>
-      <c r="E158" s="6"/>
-      <c r="F158" s="6"/>
+      <c r="E158" s="2"/>
+      <c r="F158" s="2"/>
       <c r="G158" s="2"/>
-      <c r="H158" s="2"/>
+      <c r="H158" s="10"/>
       <c r="I158" s="2"/>
-      <c r="J158" s="2"/>
-      <c r="K158" s="2"/>
-      <c r="L158" s="2"/>
+      <c r="J158" s="7"/>
+      <c r="K158" s="7"/>
+      <c r="L158" s="7"/>
+      <c r="M158" s="1"/>
+      <c r="N158" s="1"/>
     </row>
     <row r="159" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
-      <c r="C159" s="2"/>
+      <c r="C159" s="18"/>
       <c r="D159" s="2"/>
-      <c r="E159" s="2"/>
-      <c r="F159" s="2"/>
-      <c r="G159" s="6"/>
-      <c r="H159" s="7"/>
+      <c r="E159" s="7"/>
+      <c r="F159" s="7"/>
+      <c r="G159" s="7"/>
+      <c r="H159" s="10"/>
       <c r="I159" s="2"/>
-      <c r="J159" s="6"/>
-      <c r="K159" s="6"/>
-      <c r="L159" s="6"/>
+      <c r="J159" s="13"/>
+      <c r="K159" s="13"/>
+      <c r="L159" s="13"/>
     </row>
     <row r="160" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="2"/>
-      <c r="B160" s="6"/>
-      <c r="C160" s="6"/>
+      <c r="B160" s="2"/>
+      <c r="C160" s="18"/>
       <c r="D160" s="2"/>
       <c r="E160" s="2"/>
       <c r="F160" s="2"/>
-      <c r="G160" s="2"/>
-      <c r="H160" s="2"/>
+      <c r="G160" s="13"/>
+      <c r="H160" s="10"/>
       <c r="I160" s="2"/>
-      <c r="J160" s="2"/>
-      <c r="K160" s="2"/>
-      <c r="L160" s="2"/>
+      <c r="J160" s="7"/>
+      <c r="K160" s="7"/>
+      <c r="L160" s="7"/>
     </row>
     <row r="161" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A161" s="2"/>
-      <c r="B161" s="6"/>
+      <c r="B161" s="7"/>
       <c r="C161" s="2"/>
       <c r="D161" s="2"/>
-      <c r="E161" s="6"/>
+      <c r="E161" s="7"/>
       <c r="F161" s="2"/>
       <c r="G161" s="2"/>
-      <c r="H161" s="2"/>
+      <c r="H161" s="10"/>
       <c r="I161" s="2"/>
-      <c r="J161" s="2"/>
-      <c r="K161" s="2"/>
-      <c r="L161" s="2"/>
+      <c r="J161" s="7"/>
+      <c r="K161" s="7"/>
+      <c r="L161" s="7"/>
     </row>
     <row r="162" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A162" s="6"/>
-      <c r="B162" s="2"/>
+      <c r="A162" s="2"/>
+      <c r="B162" s="7"/>
       <c r="C162" s="2"/>
       <c r="D162" s="2"/>
-      <c r="E162" s="2"/>
+      <c r="E162" s="7"/>
       <c r="F162" s="2"/>
       <c r="G162" s="2"/>
       <c r="H162" s="2"/>
@@ -3433,13 +3715,13 @@
       <c r="L162" s="2"/>
     </row>
     <row r="163" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A163" s="2"/>
+      <c r="A163" s="7"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
       <c r="D163" s="2"/>
-      <c r="E163" s="6"/>
-      <c r="F163" s="6"/>
-      <c r="G163" s="6"/>
+      <c r="E163" s="2"/>
+      <c r="F163" s="2"/>
+      <c r="G163" s="2"/>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
@@ -3451,16 +3733,16 @@
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
       <c r="D164" s="2"/>
-      <c r="E164" s="2"/>
-      <c r="F164" s="2"/>
-      <c r="G164" s="2"/>
-      <c r="H164" s="7"/>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="7"/>
+      <c r="H164" s="2"/>
       <c r="I164" s="2"/>
-      <c r="J164" s="6"/>
-      <c r="K164" s="6"/>
-      <c r="L164" s="6"/>
-    </row>
-    <row r="165" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="J164" s="2"/>
+      <c r="K164" s="2"/>
+      <c r="L164" s="2"/>
+    </row>
+    <row r="165" s="4" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -3468,11 +3750,20 @@
       <c r="E165" s="2"/>
       <c r="F165" s="2"/>
       <c r="G165" s="2"/>
-      <c r="H165" s="7"/>
+      <c r="H165" s="10"/>
       <c r="I165" s="2"/>
-      <c r="J165" s="6"/>
-      <c r="K165" s="6"/>
-      <c r="L165" s="6"/>
+      <c r="J165" s="7"/>
+      <c r="K165" s="7"/>
+      <c r="L165" s="7"/>
+      <c r="M165" s="1"/>
+      <c r="N165" s="1"/>
+      <c r="O165" s="1"/>
+      <c r="P165" s="1"/>
+      <c r="Q165" s="1"/>
+      <c r="R165" s="1"/>
+      <c r="S165" s="1"/>
+      <c r="T165" s="1"/>
+      <c r="U165" s="1"/>
     </row>
     <row r="166" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="2"/>
@@ -3482,25 +3773,25 @@
       <c r="E166" s="2"/>
       <c r="F166" s="2"/>
       <c r="G166" s="2"/>
-      <c r="H166" s="7"/>
+      <c r="H166" s="10"/>
       <c r="I166" s="2"/>
-      <c r="J166" s="6"/>
-      <c r="K166" s="6"/>
-      <c r="L166" s="6"/>
+      <c r="J166" s="7"/>
+      <c r="K166" s="7"/>
+      <c r="L166" s="7"/>
     </row>
     <row r="167" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
       <c r="D167" s="2"/>
-      <c r="E167" s="2"/>
-      <c r="F167" s="2"/>
+      <c r="E167" s="7"/>
+      <c r="F167" s="7"/>
       <c r="G167" s="2"/>
-      <c r="H167" s="7"/>
+      <c r="H167" s="2"/>
       <c r="I167" s="2"/>
-      <c r="J167" s="6"/>
-      <c r="K167" s="6"/>
-      <c r="L167" s="6"/>
+      <c r="J167" s="2"/>
+      <c r="K167" s="2"/>
+      <c r="L167" s="2"/>
     </row>
     <row r="168" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="2"/>
@@ -3509,21 +3800,21 @@
       <c r="D168" s="2"/>
       <c r="E168" s="2"/>
       <c r="F168" s="2"/>
-      <c r="G168" s="6"/>
-      <c r="H168" s="7"/>
+      <c r="G168" s="7"/>
+      <c r="H168" s="10"/>
       <c r="I168" s="2"/>
-      <c r="J168" s="6"/>
-      <c r="K168" s="6"/>
-      <c r="L168" s="6"/>
+      <c r="J168" s="7"/>
+      <c r="K168" s="7"/>
+      <c r="L168" s="7"/>
     </row>
     <row r="169" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A169" s="2"/>
-      <c r="B169" s="2"/>
-      <c r="C169" s="2"/>
+      <c r="B169" s="7"/>
+      <c r="C169" s="7"/>
       <c r="D169" s="2"/>
-      <c r="E169" s="6"/>
-      <c r="F169" s="6"/>
-      <c r="G169" s="6"/>
+      <c r="E169" s="2"/>
+      <c r="F169" s="2"/>
+      <c r="G169" s="2"/>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
@@ -3532,40 +3823,40 @@
     </row>
     <row r="170" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="2"/>
-      <c r="B170" s="2"/>
+      <c r="B170" s="7"/>
       <c r="C170" s="2"/>
       <c r="D170" s="2"/>
-      <c r="E170" s="2"/>
+      <c r="E170" s="7"/>
       <c r="F170" s="2"/>
       <c r="G170" s="2"/>
-      <c r="H170" s="7"/>
+      <c r="H170" s="2"/>
       <c r="I170" s="2"/>
-      <c r="J170" s="6"/>
-      <c r="K170" s="6"/>
-      <c r="L170" s="6"/>
+      <c r="J170" s="2"/>
+      <c r="K170" s="2"/>
+      <c r="L170" s="2"/>
     </row>
     <row r="171" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A171" s="2"/>
-      <c r="B171" s="6"/>
+      <c r="A171" s="7"/>
+      <c r="B171" s="2"/>
       <c r="C171" s="2"/>
       <c r="D171" s="2"/>
-      <c r="E171" s="6"/>
+      <c r="E171" s="2"/>
       <c r="F171" s="2"/>
       <c r="G171" s="2"/>
-      <c r="H171" s="7"/>
+      <c r="H171" s="2"/>
       <c r="I171" s="2"/>
-      <c r="J171" s="6"/>
-      <c r="K171" s="6"/>
-      <c r="L171" s="6"/>
+      <c r="J171" s="2"/>
+      <c r="K171" s="2"/>
+      <c r="L171" s="2"/>
     </row>
     <row r="172" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A172" s="6"/>
+      <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
+      <c r="E172" s="7"/>
+      <c r="F172" s="7"/>
+      <c r="G172" s="7"/>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
@@ -3577,14 +3868,14 @@
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
-      <c r="E173" s="6"/>
-      <c r="F173" s="6"/>
-      <c r="G173" s="6"/>
-      <c r="H173" s="2"/>
+      <c r="E173" s="2"/>
+      <c r="F173" s="2"/>
+      <c r="G173" s="2"/>
+      <c r="H173" s="10"/>
       <c r="I173" s="2"/>
-      <c r="J173" s="2"/>
-      <c r="K173" s="2"/>
-      <c r="L173" s="2"/>
+      <c r="J173" s="7"/>
+      <c r="K173" s="7"/>
+      <c r="L173" s="7"/>
     </row>
     <row r="174" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="2"/>
@@ -3594,11 +3885,11 @@
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
       <c r="G174" s="2"/>
-      <c r="H174" s="7"/>
+      <c r="H174" s="10"/>
       <c r="I174" s="2"/>
-      <c r="J174" s="6"/>
-      <c r="K174" s="6"/>
-      <c r="L174" s="6"/>
+      <c r="J174" s="7"/>
+      <c r="K174" s="7"/>
+      <c r="L174" s="7"/>
     </row>
     <row r="175" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="2"/>
@@ -3608,11 +3899,11 @@
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
       <c r="G175" s="2"/>
-      <c r="H175" s="7"/>
+      <c r="H175" s="10"/>
       <c r="I175" s="2"/>
-      <c r="J175" s="6"/>
-      <c r="K175" s="6"/>
-      <c r="L175" s="6"/>
+      <c r="J175" s="7"/>
+      <c r="K175" s="7"/>
+      <c r="L175" s="7"/>
     </row>
     <row r="176" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="2"/>
@@ -3622,39 +3913,39 @@
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
       <c r="G176" s="2"/>
-      <c r="H176" s="7"/>
+      <c r="H176" s="10"/>
       <c r="I176" s="2"/>
-      <c r="J176" s="6"/>
-      <c r="K176" s="6"/>
-      <c r="L176" s="6"/>
+      <c r="J176" s="7"/>
+      <c r="K176" s="7"/>
+      <c r="L176" s="7"/>
     </row>
     <row r="177" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
       <c r="D177" s="2"/>
-      <c r="E177" s="6"/>
-      <c r="F177" s="6"/>
-      <c r="G177" s="2"/>
-      <c r="H177" s="2"/>
+      <c r="E177" s="2"/>
+      <c r="F177" s="2"/>
+      <c r="G177" s="7"/>
+      <c r="H177" s="10"/>
       <c r="I177" s="2"/>
-      <c r="J177" s="2"/>
-      <c r="K177" s="2"/>
-      <c r="L177" s="2"/>
+      <c r="J177" s="7"/>
+      <c r="K177" s="7"/>
+      <c r="L177" s="7"/>
     </row>
     <row r="178" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
       <c r="D178" s="2"/>
-      <c r="E178" s="2"/>
-      <c r="F178" s="2"/>
-      <c r="G178" s="6"/>
-      <c r="H178" s="7"/>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="7"/>
+      <c r="H178" s="2"/>
       <c r="I178" s="2"/>
-      <c r="J178" s="6"/>
-      <c r="K178" s="6"/>
-      <c r="L178" s="6"/>
+      <c r="J178" s="2"/>
+      <c r="K178" s="2"/>
+      <c r="L178" s="2"/>
     </row>
     <row r="179" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="2"/>
@@ -3664,53 +3955,53 @@
       <c r="E179" s="2"/>
       <c r="F179" s="2"/>
       <c r="G179" s="2"/>
-      <c r="H179" s="7"/>
+      <c r="H179" s="10"/>
       <c r="I179" s="2"/>
-      <c r="J179" s="6"/>
-      <c r="K179" s="6"/>
-      <c r="L179" s="6"/>
+      <c r="J179" s="7"/>
+      <c r="K179" s="7"/>
+      <c r="L179" s="7"/>
     </row>
     <row r="180" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="2"/>
-      <c r="B180" s="6"/>
+      <c r="B180" s="7"/>
       <c r="C180" s="2"/>
       <c r="D180" s="2"/>
-      <c r="E180" s="6"/>
+      <c r="E180" s="7"/>
       <c r="F180" s="2"/>
       <c r="G180" s="2"/>
-      <c r="H180" s="2"/>
+      <c r="H180" s="10"/>
       <c r="I180" s="2"/>
-      <c r="J180" s="2"/>
-      <c r="K180" s="2"/>
-      <c r="L180" s="2"/>
+      <c r="J180" s="7"/>
+      <c r="K180" s="7"/>
+      <c r="L180" s="7"/>
     </row>
     <row r="181" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A181" s="6"/>
+      <c r="A181" s="7"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
       <c r="F181" s="2"/>
       <c r="G181" s="2"/>
-      <c r="H181" s="7"/>
+      <c r="H181" s="2"/>
       <c r="I181" s="2"/>
-      <c r="J181" s="6"/>
-      <c r="K181" s="6"/>
-      <c r="L181" s="6"/>
+      <c r="J181" s="2"/>
+      <c r="K181" s="2"/>
+      <c r="L181" s="2"/>
     </row>
     <row r="182" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
       <c r="D182" s="2"/>
-      <c r="E182" s="2"/>
-      <c r="F182" s="2"/>
-      <c r="G182" s="2"/>
-      <c r="H182" s="7"/>
+      <c r="E182" s="7"/>
+      <c r="F182" s="7"/>
+      <c r="G182" s="7"/>
+      <c r="H182" s="2"/>
       <c r="I182" s="2"/>
-      <c r="J182" s="6"/>
-      <c r="K182" s="6"/>
-      <c r="L182" s="6"/>
+      <c r="J182" s="2"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2"/>
     </row>
     <row r="183" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A183" s="2"/>
@@ -3720,25 +4011,25 @@
       <c r="E183" s="2"/>
       <c r="F183" s="2"/>
       <c r="G183" s="2"/>
-      <c r="H183" s="7"/>
+      <c r="H183" s="10"/>
       <c r="I183" s="2"/>
-      <c r="J183" s="6"/>
-      <c r="K183" s="6"/>
-      <c r="L183" s="6"/>
+      <c r="J183" s="7"/>
+      <c r="K183" s="7"/>
+      <c r="L183" s="7"/>
     </row>
     <row r="184" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
       <c r="D184" s="2"/>
-      <c r="E184" s="6"/>
-      <c r="F184" s="6"/>
+      <c r="E184" s="2"/>
+      <c r="F184" s="2"/>
       <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
+      <c r="H184" s="10"/>
       <c r="I184" s="2"/>
-      <c r="J184" s="2"/>
-      <c r="K184" s="2"/>
-      <c r="L184" s="2"/>
+      <c r="J184" s="7"/>
+      <c r="K184" s="7"/>
+      <c r="L184" s="7"/>
     </row>
     <row r="185" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A185" s="2"/>
@@ -3748,25 +4039,25 @@
       <c r="E185" s="2"/>
       <c r="F185" s="2"/>
       <c r="G185" s="2"/>
-      <c r="H185" s="7"/>
+      <c r="H185" s="10"/>
       <c r="I185" s="2"/>
-      <c r="J185" s="6"/>
-      <c r="K185" s="6"/>
-      <c r="L185" s="6"/>
+      <c r="J185" s="7"/>
+      <c r="K185" s="7"/>
+      <c r="L185" s="7"/>
     </row>
     <row r="186" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
       <c r="D186" s="2"/>
-      <c r="E186" s="2"/>
-      <c r="F186" s="2"/>
+      <c r="E186" s="7"/>
+      <c r="F186" s="7"/>
       <c r="G186" s="2"/>
-      <c r="H186" s="7"/>
+      <c r="H186" s="2"/>
       <c r="I186" s="2"/>
-      <c r="J186" s="6"/>
-      <c r="K186" s="6"/>
-      <c r="L186" s="6"/>
+      <c r="J186" s="2"/>
+      <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
     </row>
     <row r="187" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A187" s="2"/>
@@ -3775,12 +4066,12 @@
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
       <c r="F187" s="2"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="7"/>
+      <c r="G187" s="7"/>
+      <c r="H187" s="10"/>
       <c r="I187" s="2"/>
-      <c r="J187" s="6"/>
-      <c r="K187" s="6"/>
-      <c r="L187" s="6"/>
+      <c r="J187" s="7"/>
+      <c r="K187" s="7"/>
+      <c r="L187" s="7"/>
     </row>
     <row r="188" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A188" s="2"/>
@@ -3790,19 +4081,19 @@
       <c r="E188" s="2"/>
       <c r="F188" s="2"/>
       <c r="G188" s="2"/>
-      <c r="H188" s="7"/>
+      <c r="H188" s="10"/>
       <c r="I188" s="2"/>
-      <c r="J188" s="6"/>
-      <c r="K188" s="6"/>
-      <c r="L188" s="6"/>
+      <c r="J188" s="7"/>
+      <c r="K188" s="7"/>
+      <c r="L188" s="7"/>
     </row>
     <row r="189" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A189" s="2"/>
-      <c r="B189" s="2"/>
+      <c r="B189" s="7"/>
       <c r="C189" s="2"/>
       <c r="D189" s="2"/>
-      <c r="E189" s="6"/>
-      <c r="F189" s="6"/>
+      <c r="E189" s="7"/>
+      <c r="F189" s="2"/>
       <c r="G189" s="2"/>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
@@ -3811,32 +4102,32 @@
       <c r="L189" s="2"/>
     </row>
     <row r="190" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A190" s="2"/>
-      <c r="B190" s="3"/>
+      <c r="A190" s="7"/>
+      <c r="B190" s="2"/>
       <c r="C190" s="2"/>
       <c r="D190" s="2"/>
-      <c r="E190" s="21"/>
+      <c r="E190" s="2"/>
       <c r="F190" s="2"/>
       <c r="G190" s="2"/>
-      <c r="H190" s="7"/>
+      <c r="H190" s="10"/>
       <c r="I190" s="2"/>
-      <c r="J190" s="19"/>
-      <c r="K190" s="19"/>
-      <c r="L190" s="19"/>
+      <c r="J190" s="7"/>
+      <c r="K190" s="7"/>
+      <c r="L190" s="7"/>
     </row>
     <row r="191" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A191" s="6"/>
+      <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
       <c r="F191" s="2"/>
       <c r="G191" s="2"/>
-      <c r="H191" s="2"/>
+      <c r="H191" s="10"/>
       <c r="I191" s="2"/>
-      <c r="J191" s="2"/>
-      <c r="K191" s="2"/>
-      <c r="L191" s="2"/>
+      <c r="J191" s="7"/>
+      <c r="K191" s="7"/>
+      <c r="L191" s="7"/>
     </row>
     <row r="192" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A192" s="2"/>
@@ -3846,25 +4137,25 @@
       <c r="E192" s="2"/>
       <c r="F192" s="2"/>
       <c r="G192" s="2"/>
-      <c r="H192" s="7"/>
+      <c r="H192" s="10"/>
       <c r="I192" s="2"/>
-      <c r="J192" s="6"/>
-      <c r="K192" s="6"/>
-      <c r="L192" s="6"/>
+      <c r="J192" s="7"/>
+      <c r="K192" s="7"/>
+      <c r="L192" s="7"/>
     </row>
     <row r="193" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
       <c r="D193" s="2"/>
-      <c r="E193" s="2"/>
-      <c r="F193" s="2"/>
+      <c r="E193" s="7"/>
+      <c r="F193" s="7"/>
       <c r="G193" s="2"/>
-      <c r="H193" s="7"/>
+      <c r="H193" s="2"/>
       <c r="I193" s="2"/>
-      <c r="J193" s="6"/>
-      <c r="K193" s="6"/>
-      <c r="L193" s="6"/>
+      <c r="J193" s="2"/>
+      <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
     </row>
     <row r="194" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A194" s="2"/>
@@ -3874,11 +4165,11 @@
       <c r="E194" s="2"/>
       <c r="F194" s="2"/>
       <c r="G194" s="2"/>
-      <c r="H194" s="7"/>
+      <c r="H194" s="10"/>
       <c r="I194" s="2"/>
-      <c r="J194" s="6"/>
-      <c r="K194" s="6"/>
-      <c r="L194" s="6"/>
+      <c r="J194" s="7"/>
+      <c r="K194" s="7"/>
+      <c r="L194" s="7"/>
     </row>
     <row r="195" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A195" s="2"/>
@@ -3888,11 +4179,11 @@
       <c r="E195" s="2"/>
       <c r="F195" s="2"/>
       <c r="G195" s="2"/>
-      <c r="H195" s="7"/>
+      <c r="H195" s="10"/>
       <c r="I195" s="2"/>
-      <c r="J195" s="6"/>
-      <c r="K195" s="6"/>
-      <c r="L195" s="6"/>
+      <c r="J195" s="7"/>
+      <c r="K195" s="7"/>
+      <c r="L195" s="7"/>
     </row>
     <row r="196" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A196" s="2"/>
@@ -3902,11 +4193,11 @@
       <c r="E196" s="2"/>
       <c r="F196" s="2"/>
       <c r="G196" s="2"/>
-      <c r="H196" s="7"/>
+      <c r="H196" s="10"/>
       <c r="I196" s="2"/>
-      <c r="J196" s="6"/>
-      <c r="K196" s="6"/>
-      <c r="L196" s="6"/>
+      <c r="J196" s="7"/>
+      <c r="K196" s="7"/>
+      <c r="L196" s="7"/>
     </row>
     <row r="197" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A197" s="2"/>
@@ -3916,19 +4207,19 @@
       <c r="E197" s="2"/>
       <c r="F197" s="2"/>
       <c r="G197" s="2"/>
-      <c r="H197" s="7"/>
+      <c r="H197" s="10"/>
       <c r="I197" s="2"/>
-      <c r="J197" s="6"/>
-      <c r="K197" s="6"/>
-      <c r="L197" s="6"/>
+      <c r="J197" s="7"/>
+      <c r="K197" s="7"/>
+      <c r="L197" s="7"/>
     </row>
     <row r="198" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
       <c r="D198" s="2"/>
-      <c r="E198" s="6"/>
-      <c r="F198" s="6"/>
+      <c r="E198" s="7"/>
+      <c r="F198" s="7"/>
       <c r="G198" s="2"/>
       <c r="H198" s="2"/>
       <c r="I198" s="2"/>
@@ -3938,20 +4229,20 @@
     </row>
     <row r="199" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A199" s="2"/>
-      <c r="B199" s="6"/>
+      <c r="B199" s="3"/>
       <c r="C199" s="2"/>
       <c r="D199" s="2"/>
-      <c r="E199" s="6"/>
+      <c r="E199" s="19"/>
       <c r="F199" s="2"/>
       <c r="G199" s="2"/>
-      <c r="H199" s="2"/>
+      <c r="H199" s="10"/>
       <c r="I199" s="2"/>
-      <c r="J199" s="2"/>
-      <c r="K199" s="2"/>
-      <c r="L199" s="2"/>
+      <c r="J199" s="13"/>
+      <c r="K199" s="13"/>
+      <c r="L199" s="13"/>
     </row>
     <row r="200" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A200" s="6"/>
+      <c r="A200" s="7"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
       <c r="D200" s="2"/>
@@ -3969,14 +4260,14 @@
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
       <c r="D201" s="2"/>
-      <c r="E201" s="6"/>
-      <c r="F201" s="6"/>
-      <c r="G201" s="6"/>
-      <c r="H201" s="2"/>
+      <c r="E201" s="2"/>
+      <c r="F201" s="2"/>
+      <c r="G201" s="2"/>
+      <c r="H201" s="10"/>
       <c r="I201" s="2"/>
-      <c r="J201" s="2"/>
-      <c r="K201" s="2"/>
-      <c r="L201" s="2"/>
+      <c r="J201" s="7"/>
+      <c r="K201" s="7"/>
+      <c r="L201" s="7"/>
     </row>
     <row r="202" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A202" s="2"/>
@@ -3986,38 +4277,39 @@
       <c r="E202" s="2"/>
       <c r="F202" s="2"/>
       <c r="G202" s="2"/>
-      <c r="H202" s="7"/>
+      <c r="H202" s="10"/>
       <c r="I202" s="2"/>
-      <c r="J202" s="6"/>
-      <c r="K202" s="6"/>
-      <c r="L202" s="6"/>
+      <c r="J202" s="7"/>
+      <c r="K202" s="7"/>
+      <c r="L202" s="7"/>
     </row>
     <row r="203" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A203" s="2"/>
-      <c r="B203" s="3"/>
+      <c r="B203" s="2"/>
       <c r="C203" s="2"/>
       <c r="D203" s="2"/>
+      <c r="E203" s="2"/>
       <c r="F203" s="2"/>
       <c r="G203" s="2"/>
-      <c r="H203" s="7"/>
+      <c r="H203" s="10"/>
       <c r="I203" s="2"/>
-      <c r="J203" s="19"/>
-      <c r="K203" s="19"/>
-      <c r="L203" s="19"/>
+      <c r="J203" s="7"/>
+      <c r="K203" s="7"/>
+      <c r="L203" s="7"/>
     </row>
     <row r="204" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A204" s="6"/>
+      <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
       <c r="F204" s="2"/>
       <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
+      <c r="H204" s="10"/>
       <c r="I204" s="2"/>
-      <c r="J204" s="2"/>
-      <c r="K204" s="2"/>
-      <c r="L204" s="2"/>
+      <c r="J204" s="7"/>
+      <c r="K204" s="7"/>
+      <c r="L204" s="7"/>
     </row>
     <row r="205" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A205" s="2"/>
@@ -4027,25 +4319,33 @@
       <c r="E205" s="2"/>
       <c r="F205" s="2"/>
       <c r="G205" s="2"/>
-      <c r="H205" s="7"/>
+      <c r="H205" s="10"/>
       <c r="I205" s="2"/>
-      <c r="J205" s="6"/>
-      <c r="K205" s="6"/>
-      <c r="L205" s="6"/>
+      <c r="J205" s="7"/>
+      <c r="K205" s="7"/>
+      <c r="L205" s="7"/>
     </row>
     <row r="206" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A206" s="2"/>
-      <c r="B206" s="6"/>
+      <c r="B206" s="2"/>
       <c r="C206" s="2"/>
       <c r="D206" s="2"/>
+      <c r="E206" s="2"/>
+      <c r="F206" s="2"/>
+      <c r="G206" s="2"/>
+      <c r="H206" s="10"/>
+      <c r="I206" s="2"/>
+      <c r="J206" s="7"/>
+      <c r="K206" s="7"/>
+      <c r="L206" s="7"/>
     </row>
     <row r="207" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A207" s="6"/>
+      <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
       <c r="D207" s="2"/>
-      <c r="E207" s="2"/>
-      <c r="F207" s="2"/>
+      <c r="E207" s="7"/>
+      <c r="F207" s="7"/>
       <c r="G207" s="2"/>
       <c r="H207" s="2"/>
       <c r="I207" s="2"/>
@@ -4055,25 +4355,25 @@
     </row>
     <row r="208" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A208" s="2"/>
-      <c r="B208" s="2"/>
+      <c r="B208" s="7"/>
       <c r="C208" s="2"/>
       <c r="D208" s="2"/>
-      <c r="E208" s="2"/>
+      <c r="E208" s="7"/>
       <c r="F208" s="2"/>
       <c r="G208" s="2"/>
-      <c r="H208" s="7"/>
+      <c r="H208" s="2"/>
       <c r="I208" s="2"/>
-      <c r="J208" s="6"/>
-      <c r="K208" s="6"/>
-      <c r="L208" s="6"/>
+      <c r="J208" s="2"/>
+      <c r="K208" s="2"/>
+      <c r="L208" s="2"/>
     </row>
     <row r="209" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A209" s="2"/>
-      <c r="B209" s="6"/>
+      <c r="A209" s="7"/>
+      <c r="B209" s="2"/>
       <c r="C209" s="2"/>
       <c r="D209" s="2"/>
-      <c r="E209" s="6"/>
-      <c r="F209" s="6"/>
+      <c r="E209" s="2"/>
+      <c r="F209" s="2"/>
       <c r="G209" s="2"/>
       <c r="H209" s="2"/>
       <c r="I209" s="2"/>
@@ -4086,51 +4386,50 @@
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
       <c r="D210" s="2"/>
-      <c r="E210" s="2"/>
-      <c r="F210" s="2"/>
-      <c r="G210" s="2"/>
-      <c r="H210" s="7"/>
+      <c r="E210" s="7"/>
+      <c r="F210" s="7"/>
+      <c r="G210" s="7"/>
+      <c r="H210" s="2"/>
       <c r="I210" s="2"/>
-      <c r="J210" s="6"/>
-      <c r="K210" s="6"/>
-      <c r="L210" s="6"/>
+      <c r="J210" s="2"/>
+      <c r="K210" s="2"/>
+      <c r="L210" s="2"/>
     </row>
     <row r="211" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A211" s="2"/>
-      <c r="B211" s="6"/>
+      <c r="B211" s="2"/>
       <c r="C211" s="2"/>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
       <c r="F211" s="2"/>
       <c r="G211" s="2"/>
-      <c r="H211" s="2"/>
+      <c r="H211" s="10"/>
       <c r="I211" s="2"/>
-      <c r="J211" s="2"/>
-      <c r="K211" s="2"/>
-      <c r="L211" s="2"/>
+      <c r="J211" s="7"/>
+      <c r="K211" s="7"/>
+      <c r="L211" s="7"/>
     </row>
     <row r="212" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A212" s="6"/>
-      <c r="B212" s="2"/>
+      <c r="A212" s="2"/>
+      <c r="B212" s="3"/>
       <c r="C212" s="2"/>
       <c r="D212" s="2"/>
-      <c r="E212" s="2"/>
       <c r="F212" s="2"/>
       <c r="G212" s="2"/>
-      <c r="H212" s="2"/>
+      <c r="H212" s="10"/>
       <c r="I212" s="2"/>
-      <c r="J212" s="2"/>
-      <c r="K212" s="2"/>
-      <c r="L212" s="2"/>
+      <c r="J212" s="13"/>
+      <c r="K212" s="13"/>
+      <c r="L212" s="13"/>
     </row>
     <row r="213" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A213" s="2"/>
+      <c r="A213" s="7"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
       <c r="D213" s="2"/>
-      <c r="E213" s="6"/>
-      <c r="F213" s="6"/>
-      <c r="G213" s="6"/>
+      <c r="E213" s="2"/>
+      <c r="F213" s="2"/>
+      <c r="G213" s="2"/>
       <c r="H213" s="2"/>
       <c r="I213" s="2"/>
       <c r="J213" s="2"/>
@@ -4145,28 +4444,20 @@
       <c r="E214" s="2"/>
       <c r="F214" s="2"/>
       <c r="G214" s="2"/>
-      <c r="H214" s="7"/>
+      <c r="H214" s="10"/>
       <c r="I214" s="2"/>
-      <c r="J214" s="6"/>
-      <c r="K214" s="6"/>
-      <c r="L214" s="6"/>
+      <c r="J214" s="7"/>
+      <c r="K214" s="7"/>
+      <c r="L214" s="7"/>
     </row>
     <row r="215" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A215" s="2"/>
-      <c r="B215" s="2"/>
+      <c r="B215" s="7"/>
       <c r="C215" s="2"/>
       <c r="D215" s="2"/>
-      <c r="E215" s="2"/>
-      <c r="F215" s="2"/>
-      <c r="G215" s="2"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="2"/>
-      <c r="J215" s="2"/>
-      <c r="K215" s="2"/>
-      <c r="L215" s="2"/>
     </row>
     <row r="216" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A216" s="2"/>
+      <c r="A216" s="7"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
       <c r="D216" s="2"/>
@@ -4184,59 +4475,59 @@
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
       <c r="D217" s="2"/>
-      <c r="E217" s="6"/>
-      <c r="F217" s="6"/>
+      <c r="E217" s="2"/>
+      <c r="F217" s="2"/>
       <c r="G217" s="2"/>
-      <c r="H217" s="7"/>
+      <c r="H217" s="10"/>
       <c r="I217" s="2"/>
-      <c r="J217" s="2"/>
-      <c r="K217" s="2"/>
-      <c r="L217" s="2"/>
+      <c r="J217" s="7"/>
+      <c r="K217" s="7"/>
+      <c r="L217" s="7"/>
     </row>
     <row r="218" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A218" s="2"/>
-      <c r="B218" s="2"/>
+      <c r="B218" s="7"/>
       <c r="C218" s="2"/>
       <c r="D218" s="2"/>
-      <c r="E218" s="19"/>
-      <c r="F218" s="19"/>
+      <c r="E218" s="7"/>
+      <c r="F218" s="7"/>
       <c r="G218" s="2"/>
-      <c r="H218" s="7"/>
+      <c r="H218" s="2"/>
       <c r="I218" s="2"/>
-      <c r="J218" s="6"/>
-      <c r="K218" s="6"/>
-      <c r="L218" s="6"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
     </row>
     <row r="219" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
       <c r="D219" s="2"/>
-      <c r="E219" s="6"/>
+      <c r="E219" s="2"/>
       <c r="F219" s="2"/>
       <c r="G219" s="2"/>
-      <c r="H219" s="7"/>
+      <c r="H219" s="10"/>
       <c r="I219" s="2"/>
-      <c r="J219" s="19"/>
-      <c r="K219" s="6"/>
-      <c r="L219" s="19"/>
+      <c r="J219" s="7"/>
+      <c r="K219" s="7"/>
+      <c r="L219" s="7"/>
     </row>
     <row r="220" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A220" s="2"/>
-      <c r="B220" s="3"/>
+      <c r="B220" s="7"/>
       <c r="C220" s="2"/>
       <c r="D220" s="2"/>
-      <c r="E220" s="21"/>
+      <c r="E220" s="2"/>
       <c r="F220" s="2"/>
       <c r="G220" s="2"/>
-      <c r="H220" s="7"/>
+      <c r="H220" s="2"/>
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
       <c r="K220" s="2"/>
       <c r="L220" s="2"/>
     </row>
     <row r="221" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A221" s="6"/>
+      <c r="A221" s="7"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
       <c r="D221" s="2"/>
@@ -4254,9 +4545,9 @@
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
       <c r="D222" s="2"/>
-      <c r="E222" s="6"/>
-      <c r="F222" s="6"/>
-      <c r="G222" s="6"/>
+      <c r="E222" s="7"/>
+      <c r="F222" s="7"/>
+      <c r="G222" s="7"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
       <c r="J222" s="2"/>
@@ -4271,11 +4562,11 @@
       <c r="E223" s="2"/>
       <c r="F223" s="2"/>
       <c r="G223" s="2"/>
-      <c r="H223" s="7"/>
+      <c r="H223" s="10"/>
       <c r="I223" s="2"/>
-      <c r="J223" s="6"/>
-      <c r="K223" s="6"/>
-      <c r="L223" s="6"/>
+      <c r="J223" s="7"/>
+      <c r="K223" s="7"/>
+      <c r="L223" s="7"/>
     </row>
     <row r="224" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A224" s="2"/>
@@ -4284,12 +4575,12 @@
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
       <c r="F224" s="2"/>
-      <c r="G224" s="6"/>
-      <c r="H224" s="7"/>
+      <c r="G224" s="2"/>
+      <c r="H224" s="2"/>
       <c r="I224" s="2"/>
-      <c r="J224" s="6"/>
-      <c r="K224" s="6"/>
-      <c r="L224" s="6"/>
+      <c r="J224" s="2"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
     </row>
     <row r="225" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A225" s="2"/>
@@ -4298,96 +4589,96 @@
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
       <c r="F225" s="2"/>
-      <c r="G225" s="6"/>
-      <c r="H225" s="7"/>
+      <c r="G225" s="2"/>
+      <c r="H225" s="2"/>
       <c r="I225" s="2"/>
-      <c r="J225" s="6"/>
-      <c r="K225" s="6"/>
-      <c r="L225" s="6"/>
+      <c r="J225" s="2"/>
+      <c r="K225" s="2"/>
+      <c r="L225" s="2"/>
     </row>
     <row r="226" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
       <c r="D226" s="2"/>
-      <c r="E226" s="2"/>
-      <c r="F226" s="2"/>
-      <c r="G226" s="6"/>
-      <c r="H226" s="7"/>
+      <c r="E226" s="7"/>
+      <c r="F226" s="7"/>
+      <c r="G226" s="2"/>
+      <c r="H226" s="10"/>
       <c r="I226" s="2"/>
-      <c r="J226" s="6"/>
-      <c r="K226" s="6"/>
-      <c r="L226" s="6"/>
+      <c r="J226" s="2"/>
+      <c r="K226" s="2"/>
+      <c r="L226" s="2"/>
     </row>
     <row r="227" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
       <c r="D227" s="2"/>
-      <c r="E227" s="6"/>
-      <c r="F227" s="6"/>
-      <c r="G227" s="6"/>
-      <c r="H227" s="2"/>
+      <c r="E227" s="13"/>
+      <c r="F227" s="13"/>
+      <c r="G227" s="2"/>
+      <c r="H227" s="10"/>
       <c r="I227" s="2"/>
-      <c r="J227" s="2"/>
-      <c r="K227" s="2"/>
-      <c r="L227" s="2"/>
+      <c r="J227" s="7"/>
+      <c r="K227" s="7"/>
+      <c r="L227" s="7"/>
     </row>
     <row r="228" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
       <c r="D228" s="2"/>
-      <c r="E228" s="2"/>
+      <c r="E228" s="7"/>
       <c r="F228" s="2"/>
       <c r="G228" s="2"/>
-      <c r="H228" s="7"/>
+      <c r="H228" s="10"/>
       <c r="I228" s="2"/>
-      <c r="J228" s="6"/>
-      <c r="K228" s="6"/>
-      <c r="L228" s="6"/>
+      <c r="J228" s="13"/>
+      <c r="K228" s="7"/>
+      <c r="L228" s="13"/>
     </row>
     <row r="229" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A229" s="2"/>
-      <c r="B229" s="2"/>
+      <c r="B229" s="3"/>
       <c r="C229" s="2"/>
       <c r="D229" s="2"/>
-      <c r="E229" s="6"/>
-      <c r="F229" s="6"/>
-      <c r="G229" s="6"/>
-      <c r="H229" s="2"/>
+      <c r="E229" s="19"/>
+      <c r="F229" s="2"/>
+      <c r="G229" s="2"/>
+      <c r="H229" s="10"/>
       <c r="I229" s="2"/>
       <c r="J229" s="2"/>
       <c r="K229" s="2"/>
       <c r="L229" s="2"/>
     </row>
     <row r="230" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A230" s="2"/>
+      <c r="A230" s="7"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
       <c r="F230" s="2"/>
       <c r="G230" s="2"/>
-      <c r="H230" s="7"/>
+      <c r="H230" s="2"/>
       <c r="I230" s="2"/>
-      <c r="J230" s="6"/>
-      <c r="K230" s="6"/>
-      <c r="L230" s="6"/>
+      <c r="J230" s="2"/>
+      <c r="K230" s="2"/>
+      <c r="L230" s="2"/>
     </row>
     <row r="231" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
       <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
-      <c r="G231" s="2"/>
-      <c r="H231" s="7"/>
+      <c r="E231" s="7"/>
+      <c r="F231" s="7"/>
+      <c r="G231" s="7"/>
+      <c r="H231" s="2"/>
       <c r="I231" s="2"/>
-      <c r="J231" s="6"/>
-      <c r="K231" s="6"/>
-      <c r="L231" s="6"/>
+      <c r="J231" s="2"/>
+      <c r="K231" s="2"/>
+      <c r="L231" s="2"/>
     </row>
     <row r="232" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A232" s="2"/>
@@ -4397,25 +4688,25 @@
       <c r="E232" s="2"/>
       <c r="F232" s="2"/>
       <c r="G232" s="2"/>
-      <c r="H232" s="7"/>
+      <c r="H232" s="10"/>
       <c r="I232" s="2"/>
-      <c r="J232" s="6"/>
-      <c r="K232" s="6"/>
-      <c r="L232" s="6"/>
+      <c r="J232" s="7"/>
+      <c r="K232" s="7"/>
+      <c r="L232" s="7"/>
     </row>
     <row r="233" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
       <c r="D233" s="2"/>
-      <c r="E233" s="6"/>
-      <c r="F233" s="6"/>
-      <c r="G233" s="6"/>
-      <c r="H233" s="2"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="7"/>
+      <c r="H233" s="10"/>
       <c r="I233" s="2"/>
-      <c r="J233" s="2"/>
-      <c r="K233" s="2"/>
-      <c r="L233" s="2"/>
+      <c r="J233" s="7"/>
+      <c r="K233" s="7"/>
+      <c r="L233" s="7"/>
     </row>
     <row r="234" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A234" s="2"/>
@@ -4424,35 +4715,35 @@
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
       <c r="F234" s="2"/>
-      <c r="G234" s="2"/>
-      <c r="H234" s="7"/>
+      <c r="G234" s="7"/>
+      <c r="H234" s="10"/>
       <c r="I234" s="2"/>
-      <c r="J234" s="6"/>
-      <c r="K234" s="6"/>
-      <c r="L234" s="6"/>
+      <c r="J234" s="7"/>
+      <c r="K234" s="7"/>
+      <c r="L234" s="7"/>
     </row>
     <row r="235" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
       <c r="D235" s="2"/>
-      <c r="E235" s="6"/>
-      <c r="F235" s="6"/>
-      <c r="G235" s="2"/>
-      <c r="H235" s="2"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="7"/>
+      <c r="H235" s="10"/>
       <c r="I235" s="2"/>
-      <c r="J235" s="2"/>
-      <c r="K235" s="2"/>
-      <c r="L235" s="2"/>
+      <c r="J235" s="7"/>
+      <c r="K235" s="7"/>
+      <c r="L235" s="7"/>
     </row>
     <row r="236" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A236" s="2"/>
-      <c r="B236" s="6"/>
+      <c r="B236" s="2"/>
       <c r="C236" s="2"/>
       <c r="D236" s="2"/>
-      <c r="E236" s="6"/>
-      <c r="F236" s="2"/>
-      <c r="G236" s="2"/>
+      <c r="E236" s="7"/>
+      <c r="F236" s="7"/>
+      <c r="G236" s="7"/>
       <c r="H236" s="2"/>
       <c r="I236" s="2"/>
       <c r="J236" s="2"/>
@@ -4460,32 +4751,32 @@
       <c r="L236" s="2"/>
     </row>
     <row r="237" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A237" s="6"/>
+      <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
       <c r="F237" s="2"/>
       <c r="G237" s="2"/>
-      <c r="H237" s="2"/>
+      <c r="H237" s="10"/>
       <c r="I237" s="2"/>
-      <c r="J237" s="2"/>
-      <c r="K237" s="2"/>
-      <c r="L237" s="2"/>
+      <c r="J237" s="7"/>
+      <c r="K237" s="7"/>
+      <c r="L237" s="7"/>
     </row>
     <row r="238" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
       <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
-      <c r="G238" s="2"/>
-      <c r="H238" s="7"/>
+      <c r="E238" s="7"/>
+      <c r="F238" s="7"/>
+      <c r="G238" s="7"/>
+      <c r="H238" s="2"/>
       <c r="I238" s="2"/>
-      <c r="J238" s="6"/>
-      <c r="K238" s="6"/>
-      <c r="L238" s="6"/>
+      <c r="J238" s="2"/>
+      <c r="K238" s="2"/>
+      <c r="L238" s="2"/>
     </row>
     <row r="239" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A239" s="2"/>
@@ -4494,26 +4785,26 @@
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
       <c r="F239" s="2"/>
-      <c r="G239" s="6"/>
-      <c r="H239" s="7"/>
+      <c r="G239" s="2"/>
+      <c r="H239" s="10"/>
       <c r="I239" s="2"/>
-      <c r="J239" s="6"/>
-      <c r="K239" s="6"/>
-      <c r="L239" s="6"/>
+      <c r="J239" s="7"/>
+      <c r="K239" s="7"/>
+      <c r="L239" s="7"/>
     </row>
     <row r="240" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
       <c r="D240" s="2"/>
-      <c r="E240" s="6"/>
-      <c r="F240" s="6"/>
-      <c r="G240" s="6"/>
-      <c r="H240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="2"/>
+      <c r="H240" s="10"/>
       <c r="I240" s="2"/>
-      <c r="J240" s="2"/>
-      <c r="K240" s="2"/>
-      <c r="L240" s="2"/>
+      <c r="J240" s="7"/>
+      <c r="K240" s="7"/>
+      <c r="L240" s="7"/>
     </row>
     <row r="241" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A241" s="2"/>
@@ -4523,20 +4814,20 @@
       <c r="E241" s="2"/>
       <c r="F241" s="2"/>
       <c r="G241" s="2"/>
-      <c r="H241" s="7"/>
+      <c r="H241" s="10"/>
       <c r="I241" s="2"/>
-      <c r="J241" s="6"/>
-      <c r="K241" s="6"/>
-      <c r="L241" s="6"/>
+      <c r="J241" s="7"/>
+      <c r="K241" s="7"/>
+      <c r="L241" s="7"/>
     </row>
     <row r="242" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
       <c r="D242" s="2"/>
-      <c r="E242" s="6"/>
-      <c r="F242" s="6"/>
-      <c r="G242" s="6"/>
+      <c r="E242" s="7"/>
+      <c r="F242" s="7"/>
+      <c r="G242" s="7"/>
       <c r="H242" s="2"/>
       <c r="I242" s="2"/>
       <c r="J242" s="2"/>
@@ -4551,53 +4842,53 @@
       <c r="E243" s="2"/>
       <c r="F243" s="2"/>
       <c r="G243" s="2"/>
-      <c r="H243" s="7"/>
+      <c r="H243" s="10"/>
       <c r="I243" s="2"/>
-      <c r="J243" s="6"/>
-      <c r="K243" s="6"/>
-      <c r="L243" s="6"/>
+      <c r="J243" s="7"/>
+      <c r="K243" s="7"/>
+      <c r="L243" s="7"/>
     </row>
     <row r="244" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
       <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
+      <c r="E244" s="7"/>
+      <c r="F244" s="7"/>
       <c r="G244" s="2"/>
-      <c r="H244" s="7"/>
+      <c r="H244" s="2"/>
       <c r="I244" s="2"/>
-      <c r="J244" s="6"/>
-      <c r="K244" s="6"/>
-      <c r="L244" s="6"/>
+      <c r="J244" s="2"/>
+      <c r="K244" s="2"/>
+      <c r="L244" s="2"/>
     </row>
     <row r="245" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A245" s="2"/>
-      <c r="B245" s="2"/>
+      <c r="B245" s="7"/>
       <c r="C245" s="2"/>
       <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
+      <c r="E245" s="7"/>
       <c r="F245" s="2"/>
-      <c r="G245" s="6"/>
-      <c r="H245" s="7"/>
+      <c r="G245" s="2"/>
+      <c r="H245" s="2"/>
       <c r="I245" s="2"/>
-      <c r="J245" s="6"/>
-      <c r="K245" s="6"/>
-      <c r="L245" s="6"/>
+      <c r="J245" s="2"/>
+      <c r="K245" s="2"/>
+      <c r="L245" s="2"/>
     </row>
     <row r="246" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A246" s="2"/>
+      <c r="A246" s="7"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
       <c r="F246" s="2"/>
       <c r="G246" s="2"/>
-      <c r="H246" s="7"/>
+      <c r="H246" s="2"/>
       <c r="I246" s="2"/>
-      <c r="J246" s="6"/>
-      <c r="K246" s="6"/>
-      <c r="L246" s="6"/>
+      <c r="J246" s="2"/>
+      <c r="K246" s="2"/>
+      <c r="L246" s="2"/>
     </row>
     <row r="247" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A247" s="2"/>
@@ -4607,11 +4898,11 @@
       <c r="E247" s="2"/>
       <c r="F247" s="2"/>
       <c r="G247" s="2"/>
-      <c r="H247" s="7"/>
+      <c r="H247" s="10"/>
       <c r="I247" s="2"/>
-      <c r="J247" s="6"/>
-      <c r="K247" s="6"/>
-      <c r="L247" s="6"/>
+      <c r="J247" s="7"/>
+      <c r="K247" s="7"/>
+      <c r="L247" s="7"/>
     </row>
     <row r="248" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A248" s="2"/>
@@ -4620,68 +4911,68 @@
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
       <c r="F248" s="2"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="7"/>
+      <c r="G248" s="7"/>
+      <c r="H248" s="10"/>
       <c r="I248" s="2"/>
-      <c r="J248" s="6"/>
-      <c r="K248" s="6"/>
-      <c r="L248" s="6"/>
+      <c r="J248" s="7"/>
+      <c r="K248" s="7"/>
+      <c r="L248" s="7"/>
     </row>
     <row r="249" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
-      <c r="C249" s="6"/>
+      <c r="C249" s="2"/>
       <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
-      <c r="G249" s="6"/>
-      <c r="H249" s="7"/>
+      <c r="E249" s="7"/>
+      <c r="F249" s="7"/>
+      <c r="G249" s="7"/>
+      <c r="H249" s="2"/>
       <c r="I249" s="2"/>
-      <c r="J249" s="6"/>
-      <c r="K249" s="6"/>
-      <c r="L249" s="6"/>
+      <c r="J249" s="2"/>
+      <c r="K249" s="2"/>
+      <c r="L249" s="2"/>
     </row>
     <row r="250" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
-      <c r="C250" s="6"/>
+      <c r="C250" s="2"/>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
       <c r="F250" s="2"/>
-      <c r="G250" s="6"/>
-      <c r="H250" s="7"/>
+      <c r="G250" s="2"/>
+      <c r="H250" s="10"/>
       <c r="I250" s="2"/>
-      <c r="J250" s="6"/>
-      <c r="K250" s="6"/>
-      <c r="L250" s="6"/>
+      <c r="J250" s="7"/>
+      <c r="K250" s="7"/>
+      <c r="L250" s="7"/>
     </row>
     <row r="251" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
       <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
-      <c r="G251" s="6"/>
-      <c r="H251" s="7"/>
+      <c r="E251" s="7"/>
+      <c r="F251" s="7"/>
+      <c r="G251" s="7"/>
+      <c r="H251" s="2"/>
       <c r="I251" s="2"/>
-      <c r="J251" s="6"/>
-      <c r="K251" s="6"/>
-      <c r="L251" s="6"/>
+      <c r="J251" s="2"/>
+      <c r="K251" s="2"/>
+      <c r="L251" s="2"/>
     </row>
     <row r="252" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
       <c r="D252" s="2"/>
-      <c r="E252" s="6"/>
-      <c r="F252" s="6"/>
-      <c r="G252" s="6"/>
-      <c r="H252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="2"/>
+      <c r="H252" s="10"/>
       <c r="I252" s="2"/>
-      <c r="J252" s="2"/>
-      <c r="K252" s="2"/>
-      <c r="L252" s="2"/>
+      <c r="J252" s="7"/>
+      <c r="K252" s="7"/>
+      <c r="L252" s="7"/>
     </row>
     <row r="253" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A253" s="2"/>
@@ -4690,26 +4981,26 @@
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
       <c r="F253" s="2"/>
-      <c r="G253" s="6"/>
-      <c r="H253" s="7"/>
+      <c r="G253" s="2"/>
+      <c r="H253" s="10"/>
       <c r="I253" s="2"/>
-      <c r="J253" s="6"/>
-      <c r="K253" s="6"/>
-      <c r="L253" s="6"/>
+      <c r="J253" s="7"/>
+      <c r="K253" s="7"/>
+      <c r="L253" s="7"/>
     </row>
     <row r="254" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
       <c r="D254" s="2"/>
-      <c r="E254" s="6"/>
-      <c r="F254" s="6"/>
-      <c r="G254" s="6"/>
-      <c r="H254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="7"/>
+      <c r="H254" s="10"/>
       <c r="I254" s="2"/>
-      <c r="J254" s="2"/>
-      <c r="K254" s="2"/>
-      <c r="L254" s="2"/>
+      <c r="J254" s="7"/>
+      <c r="K254" s="7"/>
+      <c r="L254" s="7"/>
     </row>
     <row r="255" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A255" s="2"/>
@@ -4718,12 +5009,12 @@
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
       <c r="F255" s="2"/>
-      <c r="G255" s="6"/>
-      <c r="H255" s="7"/>
+      <c r="G255" s="2"/>
+      <c r="H255" s="10"/>
       <c r="I255" s="2"/>
-      <c r="J255" s="6"/>
-      <c r="K255" s="6"/>
-      <c r="L255" s="6"/>
+      <c r="J255" s="7"/>
+      <c r="K255" s="7"/>
+      <c r="L255" s="7"/>
     </row>
     <row r="256" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A256" s="2"/>
@@ -4733,11 +5024,11 @@
       <c r="E256" s="2"/>
       <c r="F256" s="2"/>
       <c r="G256" s="2"/>
-      <c r="H256" s="7"/>
+      <c r="H256" s="10"/>
       <c r="I256" s="2"/>
-      <c r="J256" s="6"/>
-      <c r="K256" s="6"/>
-      <c r="L256" s="6"/>
+      <c r="J256" s="7"/>
+      <c r="K256" s="7"/>
+      <c r="L256" s="7"/>
     </row>
     <row r="257" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A257" s="2"/>
@@ -4746,68 +5037,68 @@
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
       <c r="F257" s="2"/>
-      <c r="G257" s="6"/>
-      <c r="H257" s="7"/>
+      <c r="G257" s="2"/>
+      <c r="H257" s="10"/>
       <c r="I257" s="2"/>
-      <c r="J257" s="6"/>
-      <c r="K257" s="6"/>
-      <c r="L257" s="6"/>
+      <c r="J257" s="7"/>
+      <c r="K257" s="7"/>
+      <c r="L257" s="7"/>
     </row>
     <row r="258" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
-      <c r="C258" s="2"/>
+      <c r="C258" s="7"/>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
       <c r="F258" s="2"/>
-      <c r="G258" s="6"/>
-      <c r="H258" s="7"/>
+      <c r="G258" s="7"/>
+      <c r="H258" s="10"/>
       <c r="I258" s="2"/>
-      <c r="J258" s="6"/>
-      <c r="K258" s="6"/>
-      <c r="L258" s="6"/>
+      <c r="J258" s="7"/>
+      <c r="K258" s="7"/>
+      <c r="L258" s="7"/>
     </row>
     <row r="259" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
-      <c r="C259" s="2"/>
+      <c r="C259" s="7"/>
       <c r="D259" s="2"/>
       <c r="E259" s="2"/>
       <c r="F259" s="2"/>
-      <c r="G259" s="6"/>
-      <c r="H259" s="7"/>
+      <c r="G259" s="7"/>
+      <c r="H259" s="10"/>
       <c r="I259" s="2"/>
-      <c r="J259" s="6"/>
-      <c r="K259" s="6"/>
-      <c r="L259" s="6"/>
+      <c r="J259" s="7"/>
+      <c r="K259" s="7"/>
+      <c r="L259" s="7"/>
     </row>
     <row r="260" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
       <c r="D260" s="2"/>
-      <c r="E260" s="6"/>
-      <c r="F260" s="6"/>
-      <c r="G260" s="6"/>
-      <c r="H260" s="7"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="7"/>
+      <c r="H260" s="10"/>
       <c r="I260" s="2"/>
-      <c r="J260" s="6"/>
-      <c r="K260" s="6"/>
-      <c r="L260" s="6"/>
+      <c r="J260" s="7"/>
+      <c r="K260" s="7"/>
+      <c r="L260" s="7"/>
     </row>
     <row r="261" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
       <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
-      <c r="G261" s="6"/>
-      <c r="H261" s="7"/>
+      <c r="E261" s="7"/>
+      <c r="F261" s="7"/>
+      <c r="G261" s="7"/>
+      <c r="H261" s="2"/>
       <c r="I261" s="2"/>
-      <c r="J261" s="6"/>
-      <c r="K261" s="6"/>
-      <c r="L261" s="6"/>
+      <c r="J261" s="2"/>
+      <c r="K261" s="2"/>
+      <c r="L261" s="2"/>
     </row>
     <row r="262" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A262" s="2"/>
@@ -4816,21 +5107,21 @@
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
       <c r="F262" s="2"/>
-      <c r="G262" s="6"/>
-      <c r="H262" s="7"/>
+      <c r="G262" s="7"/>
+      <c r="H262" s="10"/>
       <c r="I262" s="2"/>
-      <c r="J262" s="6"/>
-      <c r="K262" s="6"/>
-      <c r="L262" s="6"/>
+      <c r="J262" s="7"/>
+      <c r="K262" s="7"/>
+      <c r="L262" s="7"/>
     </row>
     <row r="263" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
       <c r="D263" s="2"/>
-      <c r="E263" s="6"/>
-      <c r="F263" s="6"/>
-      <c r="G263" s="6"/>
+      <c r="E263" s="7"/>
+      <c r="F263" s="7"/>
+      <c r="G263" s="7"/>
       <c r="H263" s="2"/>
       <c r="I263" s="2"/>
       <c r="J263" s="2"/>
@@ -4844,40 +5135,40 @@
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
       <c r="F264" s="2"/>
-      <c r="G264" s="2"/>
-      <c r="H264" s="7"/>
+      <c r="G264" s="7"/>
+      <c r="H264" s="10"/>
       <c r="I264" s="2"/>
-      <c r="J264" s="6"/>
-      <c r="K264" s="6"/>
-      <c r="L264" s="6"/>
+      <c r="J264" s="7"/>
+      <c r="K264" s="7"/>
+      <c r="L264" s="7"/>
     </row>
     <row r="265" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
       <c r="D265" s="2"/>
-      <c r="E265" s="6"/>
-      <c r="F265" s="6"/>
-      <c r="G265" s="6"/>
-      <c r="H265" s="2"/>
+      <c r="E265" s="2"/>
+      <c r="F265" s="2"/>
+      <c r="G265" s="2"/>
+      <c r="H265" s="10"/>
       <c r="I265" s="2"/>
-      <c r="J265" s="2"/>
-      <c r="K265" s="2"/>
-      <c r="L265" s="2"/>
+      <c r="J265" s="7"/>
+      <c r="K265" s="7"/>
+      <c r="L265" s="7"/>
     </row>
     <row r="266" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
       <c r="D266" s="2"/>
-      <c r="E266" s="6"/>
-      <c r="F266" s="6"/>
-      <c r="G266" s="6"/>
-      <c r="H266" s="2"/>
+      <c r="E266" s="2"/>
+      <c r="F266" s="2"/>
+      <c r="G266" s="7"/>
+      <c r="H266" s="10"/>
       <c r="I266" s="2"/>
-      <c r="J266" s="2"/>
-      <c r="K266" s="2"/>
-      <c r="L266" s="2"/>
+      <c r="J266" s="7"/>
+      <c r="K266" s="7"/>
+      <c r="L266" s="7"/>
     </row>
     <row r="267" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A267" s="2"/>
@@ -4886,40 +5177,40 @@
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
       <c r="F267" s="2"/>
-      <c r="G267" s="2"/>
-      <c r="H267" s="7"/>
+      <c r="G267" s="7"/>
+      <c r="H267" s="10"/>
       <c r="I267" s="2"/>
-      <c r="J267" s="6"/>
-      <c r="K267" s="6"/>
-      <c r="L267" s="6"/>
+      <c r="J267" s="7"/>
+      <c r="K267" s="7"/>
+      <c r="L267" s="7"/>
     </row>
     <row r="268" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
       <c r="D268" s="2"/>
-      <c r="E268" s="6"/>
-      <c r="F268" s="6"/>
-      <c r="G268" s="6"/>
-      <c r="H268" s="7"/>
+      <c r="E268" s="2"/>
+      <c r="F268" s="2"/>
+      <c r="G268" s="7"/>
+      <c r="H268" s="10"/>
       <c r="I268" s="2"/>
-      <c r="J268" s="6"/>
-      <c r="K268" s="6"/>
-      <c r="L268" s="6"/>
+      <c r="J268" s="7"/>
+      <c r="K268" s="7"/>
+      <c r="L268" s="7"/>
     </row>
     <row r="269" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
       <c r="D269" s="2"/>
-      <c r="E269" s="2"/>
-      <c r="F269" s="2"/>
-      <c r="G269" s="6"/>
-      <c r="H269" s="7"/>
+      <c r="E269" s="7"/>
+      <c r="F269" s="7"/>
+      <c r="G269" s="7"/>
+      <c r="H269" s="10"/>
       <c r="I269" s="2"/>
-      <c r="J269" s="6"/>
-      <c r="K269" s="6"/>
-      <c r="L269" s="6"/>
+      <c r="J269" s="7"/>
+      <c r="K269" s="7"/>
+      <c r="L269" s="7"/>
     </row>
     <row r="270" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A270" s="2"/>
@@ -4928,82 +5219,82 @@
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
       <c r="F270" s="2"/>
-      <c r="G270" s="2"/>
-      <c r="H270" s="7"/>
+      <c r="G270" s="7"/>
+      <c r="H270" s="10"/>
       <c r="I270" s="2"/>
-      <c r="J270" s="6"/>
-      <c r="K270" s="6"/>
-      <c r="L270" s="6"/>
+      <c r="J270" s="7"/>
+      <c r="K270" s="7"/>
+      <c r="L270" s="7"/>
     </row>
     <row r="271" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
       <c r="D271" s="2"/>
-      <c r="E271" s="6"/>
-      <c r="F271" s="6"/>
-      <c r="G271" s="6"/>
-      <c r="H271" s="7"/>
+      <c r="E271" s="2"/>
+      <c r="F271" s="2"/>
+      <c r="G271" s="7"/>
+      <c r="H271" s="10"/>
       <c r="I271" s="2"/>
-      <c r="J271" s="6"/>
-      <c r="K271" s="6"/>
-      <c r="L271" s="6"/>
+      <c r="J271" s="7"/>
+      <c r="K271" s="7"/>
+      <c r="L271" s="7"/>
     </row>
     <row r="272" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
       <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
-      <c r="G272" s="2"/>
-      <c r="H272" s="7"/>
+      <c r="E272" s="7"/>
+      <c r="F272" s="7"/>
+      <c r="G272" s="7"/>
+      <c r="H272" s="2"/>
       <c r="I272" s="2"/>
-      <c r="J272" s="6"/>
-      <c r="K272" s="6"/>
-      <c r="L272" s="6"/>
+      <c r="J272" s="2"/>
+      <c r="K272" s="2"/>
+      <c r="L272" s="2"/>
     </row>
     <row r="273" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
       <c r="D273" s="2"/>
-      <c r="E273" s="6"/>
-      <c r="F273" s="6"/>
-      <c r="G273" s="6"/>
-      <c r="H273" s="2"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="2"/>
+      <c r="H273" s="10"/>
       <c r="I273" s="2"/>
-      <c r="J273" s="2"/>
-      <c r="K273" s="2"/>
-      <c r="L273" s="2"/>
+      <c r="J273" s="7"/>
+      <c r="K273" s="7"/>
+      <c r="L273" s="7"/>
     </row>
     <row r="274" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
-      <c r="C274" s="6"/>
+      <c r="C274" s="2"/>
       <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
-      <c r="G274" s="6"/>
-      <c r="H274" s="7"/>
+      <c r="E274" s="7"/>
+      <c r="F274" s="7"/>
+      <c r="G274" s="7"/>
+      <c r="H274" s="2"/>
       <c r="I274" s="2"/>
-      <c r="J274" s="6"/>
-      <c r="K274" s="6"/>
-      <c r="L274" s="6"/>
+      <c r="J274" s="2"/>
+      <c r="K274" s="2"/>
+      <c r="L274" s="2"/>
     </row>
     <row r="275" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
-      <c r="C275" s="6"/>
+      <c r="C275" s="2"/>
       <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
-      <c r="F275" s="2"/>
-      <c r="G275" s="6"/>
-      <c r="H275" s="7"/>
+      <c r="E275" s="7"/>
+      <c r="F275" s="7"/>
+      <c r="G275" s="7"/>
+      <c r="H275" s="2"/>
       <c r="I275" s="2"/>
-      <c r="J275" s="6"/>
-      <c r="K275" s="6"/>
-      <c r="L275" s="6"/>
+      <c r="J275" s="2"/>
+      <c r="K275" s="2"/>
+      <c r="L275" s="2"/>
     </row>
     <row r="276" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A276" s="2"/>
@@ -5012,26 +5303,26 @@
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
       <c r="F276" s="2"/>
-      <c r="G276" s="6"/>
-      <c r="H276" s="7"/>
+      <c r="G276" s="2"/>
+      <c r="H276" s="10"/>
       <c r="I276" s="2"/>
-      <c r="J276" s="6"/>
-      <c r="K276" s="6"/>
-      <c r="L276" s="6"/>
+      <c r="J276" s="7"/>
+      <c r="K276" s="7"/>
+      <c r="L276" s="7"/>
     </row>
     <row r="277" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
       <c r="D277" s="2"/>
-      <c r="E277" s="6"/>
-      <c r="F277" s="6"/>
-      <c r="G277" s="6"/>
-      <c r="H277" s="2"/>
+      <c r="E277" s="7"/>
+      <c r="F277" s="7"/>
+      <c r="G277" s="7"/>
+      <c r="H277" s="10"/>
       <c r="I277" s="2"/>
-      <c r="J277" s="2"/>
-      <c r="K277" s="2"/>
-      <c r="L277" s="2"/>
+      <c r="J277" s="7"/>
+      <c r="K277" s="7"/>
+      <c r="L277" s="7"/>
     </row>
     <row r="278" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A278" s="2"/>
@@ -5040,12 +5331,12 @@
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
       <c r="F278" s="2"/>
-      <c r="G278" s="2"/>
-      <c r="H278" s="7"/>
+      <c r="G278" s="7"/>
+      <c r="H278" s="10"/>
       <c r="I278" s="2"/>
-      <c r="J278" s="6"/>
-      <c r="K278" s="6"/>
-      <c r="L278" s="6"/>
+      <c r="J278" s="7"/>
+      <c r="K278" s="7"/>
+      <c r="L278" s="7"/>
     </row>
     <row r="279" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A279" s="2"/>
@@ -5055,81 +5346,81 @@
       <c r="E279" s="2"/>
       <c r="F279" s="2"/>
       <c r="G279" s="2"/>
-      <c r="H279" s="7"/>
+      <c r="H279" s="10"/>
       <c r="I279" s="2"/>
-      <c r="J279" s="6"/>
-      <c r="K279" s="6"/>
-      <c r="L279" s="6"/>
+      <c r="J279" s="7"/>
+      <c r="K279" s="7"/>
+      <c r="L279" s="7"/>
     </row>
     <row r="280" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
       <c r="D280" s="2"/>
-      <c r="E280" s="2"/>
-      <c r="F280" s="2"/>
-      <c r="G280" s="2"/>
-      <c r="H280" s="7"/>
+      <c r="E280" s="7"/>
+      <c r="F280" s="7"/>
+      <c r="G280" s="7"/>
+      <c r="H280" s="10"/>
       <c r="I280" s="2"/>
-      <c r="J280" s="6"/>
-      <c r="K280" s="6"/>
-      <c r="L280" s="6"/>
+      <c r="J280" s="7"/>
+      <c r="K280" s="7"/>
+      <c r="L280" s="7"/>
     </row>
     <row r="281" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
       <c r="D281" s="2"/>
-      <c r="E281" s="6"/>
-      <c r="F281" s="6"/>
-      <c r="G281" s="6"/>
-      <c r="H281" s="7"/>
+      <c r="E281" s="2"/>
+      <c r="F281" s="2"/>
+      <c r="G281" s="2"/>
+      <c r="H281" s="10"/>
       <c r="I281" s="2"/>
-      <c r="J281" s="6"/>
-      <c r="K281" s="6"/>
-      <c r="L281" s="6"/>
+      <c r="J281" s="7"/>
+      <c r="K281" s="7"/>
+      <c r="L281" s="7"/>
     </row>
     <row r="282" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
       <c r="D282" s="2"/>
-      <c r="E282" s="2"/>
-      <c r="F282" s="2"/>
-      <c r="G282" s="6"/>
-      <c r="H282" s="7"/>
+      <c r="E282" s="7"/>
+      <c r="F282" s="7"/>
+      <c r="G282" s="7"/>
+      <c r="H282" s="2"/>
       <c r="I282" s="2"/>
-      <c r="J282" s="6"/>
-      <c r="K282" s="6"/>
-      <c r="L282" s="6"/>
+      <c r="J282" s="2"/>
+      <c r="K282" s="2"/>
+      <c r="L282" s="2"/>
     </row>
     <row r="283" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
-      <c r="C283" s="2"/>
+      <c r="C283" s="7"/>
       <c r="D283" s="2"/>
-      <c r="E283" s="6"/>
-      <c r="F283" s="6"/>
-      <c r="G283" s="6"/>
-      <c r="H283" s="7"/>
+      <c r="E283" s="2"/>
+      <c r="F283" s="2"/>
+      <c r="G283" s="7"/>
+      <c r="H283" s="10"/>
       <c r="I283" s="2"/>
-      <c r="J283" s="6"/>
-      <c r="K283" s="6"/>
-      <c r="L283" s="6"/>
+      <c r="J283" s="7"/>
+      <c r="K283" s="7"/>
+      <c r="L283" s="7"/>
     </row>
     <row r="284" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
-      <c r="C284" s="2"/>
+      <c r="C284" s="7"/>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
       <c r="F284" s="2"/>
-      <c r="G284" s="2"/>
-      <c r="H284" s="7"/>
+      <c r="G284" s="7"/>
+      <c r="H284" s="10"/>
       <c r="I284" s="2"/>
-      <c r="J284" s="6"/>
-      <c r="K284" s="6"/>
-      <c r="L284" s="6"/>
+      <c r="J284" s="7"/>
+      <c r="K284" s="7"/>
+      <c r="L284" s="7"/>
     </row>
     <row r="285" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A285" s="2"/>
@@ -5138,21 +5429,21 @@
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
       <c r="F285" s="2"/>
-      <c r="G285" s="2"/>
-      <c r="H285" s="7"/>
+      <c r="G285" s="7"/>
+      <c r="H285" s="10"/>
       <c r="I285" s="2"/>
-      <c r="J285" s="6"/>
-      <c r="K285" s="6"/>
-      <c r="L285" s="6"/>
+      <c r="J285" s="7"/>
+      <c r="K285" s="7"/>
+      <c r="L285" s="7"/>
     </row>
     <row r="286" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
       <c r="D286" s="2"/>
-      <c r="E286" s="6"/>
-      <c r="F286" s="6"/>
-      <c r="G286" s="6"/>
+      <c r="E286" s="7"/>
+      <c r="F286" s="7"/>
+      <c r="G286" s="7"/>
       <c r="H286" s="2"/>
       <c r="I286" s="2"/>
       <c r="J286" s="2"/>
@@ -5166,26 +5457,26 @@
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
       <c r="F287" s="2"/>
-      <c r="G287" s="6"/>
-      <c r="H287" s="7"/>
+      <c r="G287" s="2"/>
+      <c r="H287" s="10"/>
       <c r="I287" s="2"/>
-      <c r="J287" s="6"/>
-      <c r="K287" s="6"/>
-      <c r="L287" s="6"/>
+      <c r="J287" s="7"/>
+      <c r="K287" s="7"/>
+      <c r="L287" s="7"/>
     </row>
     <row r="288" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
       <c r="D288" s="2"/>
-      <c r="E288" s="6"/>
-      <c r="F288" s="6"/>
-      <c r="G288" s="6"/>
-      <c r="H288" s="2"/>
+      <c r="E288" s="2"/>
+      <c r="F288" s="2"/>
+      <c r="G288" s="2"/>
+      <c r="H288" s="10"/>
       <c r="I288" s="2"/>
-      <c r="J288" s="2"/>
-      <c r="K288" s="2"/>
-      <c r="L288" s="2"/>
+      <c r="J288" s="7"/>
+      <c r="K288" s="7"/>
+      <c r="L288" s="7"/>
     </row>
     <row r="289" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A289" s="2"/>
@@ -5194,83 +5485,91 @@
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
       <c r="F289" s="2"/>
-      <c r="G289" s="6"/>
-      <c r="H289" s="7"/>
+      <c r="G289" s="2"/>
+      <c r="H289" s="10"/>
       <c r="I289" s="2"/>
-      <c r="J289" s="6"/>
-      <c r="K289" s="6"/>
-      <c r="L289" s="6"/>
+      <c r="J289" s="7"/>
+      <c r="K289" s="7"/>
+      <c r="L289" s="7"/>
     </row>
     <row r="290" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
       <c r="D290" s="2"/>
-      <c r="E290" s="6"/>
-      <c r="F290" s="6"/>
-      <c r="G290" s="2"/>
-      <c r="H290" s="2"/>
+      <c r="E290" s="7"/>
+      <c r="F290" s="7"/>
+      <c r="G290" s="7"/>
+      <c r="H290" s="10"/>
       <c r="I290" s="2"/>
-      <c r="J290" s="2"/>
-      <c r="K290" s="2"/>
-      <c r="L290" s="2"/>
+      <c r="J290" s="7"/>
+      <c r="K290" s="7"/>
+      <c r="L290" s="7"/>
     </row>
     <row r="291" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
       <c r="D291" s="2"/>
-      <c r="E291" s="6"/>
-      <c r="F291" s="6"/>
-      <c r="G291" s="2"/>
-      <c r="H291" s="2"/>
+      <c r="E291" s="2"/>
+      <c r="F291" s="2"/>
+      <c r="G291" s="7"/>
+      <c r="H291" s="10"/>
       <c r="I291" s="2"/>
-      <c r="J291" s="2"/>
-      <c r="K291" s="2"/>
-      <c r="L291" s="2"/>
+      <c r="J291" s="7"/>
+      <c r="K291" s="7"/>
+      <c r="L291" s="7"/>
     </row>
     <row r="292" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
       <c r="D292" s="2"/>
-      <c r="E292" s="6"/>
-      <c r="F292" s="2"/>
-      <c r="G292" s="2"/>
-      <c r="H292" s="2"/>
+      <c r="E292" s="7"/>
+      <c r="F292" s="7"/>
+      <c r="G292" s="7"/>
+      <c r="H292" s="10"/>
       <c r="I292" s="2"/>
-      <c r="J292" s="2"/>
-      <c r="K292" s="2"/>
-      <c r="L292" s="2"/>
+      <c r="J292" s="7"/>
+      <c r="K292" s="7"/>
+      <c r="L292" s="7"/>
     </row>
     <row r="293" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A293" s="2"/>
+      <c r="B293" s="2"/>
+      <c r="C293" s="2"/>
+      <c r="D293" s="2"/>
+      <c r="E293" s="2"/>
       <c r="F293" s="2"/>
       <c r="G293" s="2"/>
-      <c r="H293" s="7"/>
+      <c r="H293" s="10"/>
       <c r="I293" s="2"/>
-      <c r="J293" s="6"/>
-      <c r="K293" s="6"/>
-      <c r="L293" s="6"/>
+      <c r="J293" s="7"/>
+      <c r="K293" s="7"/>
+      <c r="L293" s="7"/>
     </row>
     <row r="294" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A294" s="2"/>
+      <c r="B294" s="2"/>
+      <c r="C294" s="2"/>
+      <c r="D294" s="2"/>
+      <c r="E294" s="2"/>
       <c r="F294" s="2"/>
       <c r="G294" s="2"/>
-      <c r="H294" s="7"/>
+      <c r="H294" s="10"/>
       <c r="I294" s="2"/>
-      <c r="J294" s="6"/>
-      <c r="K294" s="6"/>
-      <c r="L294" s="6"/>
+      <c r="J294" s="7"/>
+      <c r="K294" s="7"/>
+      <c r="L294" s="7"/>
     </row>
     <row r="295" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A295" s="2"/>
-      <c r="B295" s="6"/>
+      <c r="B295" s="2"/>
       <c r="C295" s="2"/>
       <c r="D295" s="2"/>
-      <c r="E295" s="6"/>
-      <c r="F295" s="2"/>
-      <c r="G295" s="2"/>
+      <c r="E295" s="7"/>
+      <c r="F295" s="7"/>
+      <c r="G295" s="7"/>
       <c r="H295" s="2"/>
       <c r="I295" s="2"/>
       <c r="J295" s="2"/>
@@ -5278,27 +5577,27 @@
       <c r="L295" s="2"/>
     </row>
     <row r="296" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A296" s="6"/>
+      <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
       <c r="F296" s="2"/>
-      <c r="G296" s="2"/>
-      <c r="H296" s="2"/>
+      <c r="G296" s="7"/>
+      <c r="H296" s="10"/>
       <c r="I296" s="2"/>
-      <c r="J296" s="2"/>
-      <c r="K296" s="2"/>
-      <c r="L296" s="2"/>
+      <c r="J296" s="7"/>
+      <c r="K296" s="7"/>
+      <c r="L296" s="7"/>
     </row>
     <row r="297" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
       <c r="D297" s="2"/>
-      <c r="E297" s="6"/>
-      <c r="F297" s="6"/>
-      <c r="G297" s="6"/>
+      <c r="E297" s="7"/>
+      <c r="F297" s="7"/>
+      <c r="G297" s="7"/>
       <c r="H297" s="2"/>
       <c r="I297" s="2"/>
       <c r="J297" s="2"/>
@@ -5312,21 +5611,21 @@
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
       <c r="F298" s="2"/>
-      <c r="G298" s="2"/>
-      <c r="H298" s="7"/>
+      <c r="G298" s="7"/>
+      <c r="H298" s="10"/>
       <c r="I298" s="2"/>
-      <c r="J298" s="6"/>
-      <c r="K298" s="6"/>
-      <c r="L298" s="6"/>
+      <c r="J298" s="7"/>
+      <c r="K298" s="7"/>
+      <c r="L298" s="7"/>
     </row>
     <row r="299" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
       <c r="D299" s="2"/>
-      <c r="E299" s="6"/>
-      <c r="F299" s="6"/>
-      <c r="G299" s="6"/>
+      <c r="E299" s="7"/>
+      <c r="F299" s="7"/>
+      <c r="G299" s="2"/>
       <c r="H299" s="2"/>
       <c r="I299" s="2"/>
       <c r="J299" s="2"/>
@@ -5338,65 +5637,57 @@
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
       <c r="D300" s="2"/>
-      <c r="E300" s="2"/>
-      <c r="F300" s="2"/>
+      <c r="E300" s="7"/>
+      <c r="F300" s="7"/>
       <c r="G300" s="2"/>
-      <c r="H300" s="7"/>
+      <c r="H300" s="2"/>
       <c r="I300" s="2"/>
-      <c r="J300" s="6"/>
-      <c r="K300" s="6"/>
-      <c r="L300" s="6"/>
+      <c r="J300" s="2"/>
+      <c r="K300" s="2"/>
+      <c r="L300" s="2"/>
     </row>
     <row r="301" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
       <c r="D301" s="2"/>
-      <c r="E301" s="2"/>
+      <c r="E301" s="7"/>
       <c r="F301" s="2"/>
       <c r="G301" s="2"/>
-      <c r="H301" s="7"/>
+      <c r="H301" s="2"/>
       <c r="I301" s="2"/>
-      <c r="J301" s="6"/>
-      <c r="K301" s="6"/>
-      <c r="L301" s="6"/>
+      <c r="J301" s="2"/>
+      <c r="K301" s="2"/>
+      <c r="L301" s="2"/>
     </row>
     <row r="302" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A302" s="2"/>
-      <c r="B302" s="2"/>
-      <c r="C302" s="2"/>
-      <c r="D302" s="2"/>
-      <c r="E302" s="2"/>
       <c r="F302" s="2"/>
       <c r="G302" s="2"/>
-      <c r="H302" s="7"/>
+      <c r="H302" s="10"/>
       <c r="I302" s="2"/>
-      <c r="J302" s="6"/>
-      <c r="K302" s="6"/>
-      <c r="L302" s="6"/>
+      <c r="J302" s="7"/>
+      <c r="K302" s="7"/>
+      <c r="L302" s="7"/>
     </row>
     <row r="303" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A303" s="2"/>
-      <c r="B303" s="2"/>
-      <c r="C303" s="2"/>
-      <c r="D303" s="2"/>
-      <c r="E303" s="2"/>
       <c r="F303" s="2"/>
       <c r="G303" s="2"/>
-      <c r="H303" s="7"/>
+      <c r="H303" s="10"/>
       <c r="I303" s="2"/>
-      <c r="J303" s="6"/>
-      <c r="K303" s="6"/>
-      <c r="L303" s="6"/>
+      <c r="J303" s="7"/>
+      <c r="K303" s="7"/>
+      <c r="L303" s="7"/>
     </row>
     <row r="304" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A304" s="2"/>
-      <c r="B304" s="2"/>
+      <c r="B304" s="7"/>
       <c r="C304" s="2"/>
       <c r="D304" s="2"/>
-      <c r="E304" s="6"/>
-      <c r="F304" s="6"/>
-      <c r="G304" s="6"/>
+      <c r="E304" s="7"/>
+      <c r="F304" s="2"/>
+      <c r="G304" s="2"/>
       <c r="H304" s="2"/>
       <c r="I304" s="2"/>
       <c r="J304" s="2"/>
@@ -5404,27 +5695,27 @@
       <c r="L304" s="2"/>
     </row>
     <row r="305" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A305" s="2"/>
+      <c r="A305" s="7"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
       <c r="D305" s="2"/>
       <c r="E305" s="2"/>
       <c r="F305" s="2"/>
       <c r="G305" s="2"/>
-      <c r="H305" s="7"/>
+      <c r="H305" s="2"/>
       <c r="I305" s="2"/>
-      <c r="J305" s="6"/>
-      <c r="K305" s="6"/>
-      <c r="L305" s="6"/>
+      <c r="J305" s="2"/>
+      <c r="K305" s="2"/>
+      <c r="L305" s="2"/>
     </row>
     <row r="306" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
       <c r="D306" s="2"/>
-      <c r="E306" s="6"/>
-      <c r="F306" s="6"/>
-      <c r="G306" s="6"/>
+      <c r="E306" s="7"/>
+      <c r="F306" s="7"/>
+      <c r="G306" s="7"/>
       <c r="H306" s="2"/>
       <c r="I306" s="2"/>
       <c r="J306" s="2"/>
@@ -5439,20 +5730,20 @@
       <c r="E307" s="2"/>
       <c r="F307" s="2"/>
       <c r="G307" s="2"/>
-      <c r="H307" s="7"/>
+      <c r="H307" s="10"/>
       <c r="I307" s="2"/>
-      <c r="J307" s="6"/>
-      <c r="K307" s="6"/>
-      <c r="L307" s="6"/>
+      <c r="J307" s="7"/>
+      <c r="K307" s="7"/>
+      <c r="L307" s="7"/>
     </row>
     <row r="308" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
       <c r="D308" s="2"/>
-      <c r="E308" s="6"/>
-      <c r="F308" s="6"/>
-      <c r="G308" s="2"/>
+      <c r="E308" s="7"/>
+      <c r="F308" s="7"/>
+      <c r="G308" s="7"/>
       <c r="H308" s="2"/>
       <c r="I308" s="2"/>
       <c r="J308" s="2"/>
@@ -5461,45 +5752,45 @@
     </row>
     <row r="309" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A309" s="2"/>
-      <c r="B309" s="6"/>
+      <c r="B309" s="2"/>
       <c r="C309" s="2"/>
       <c r="D309" s="2"/>
-      <c r="E309" s="6"/>
+      <c r="E309" s="2"/>
       <c r="F309" s="2"/>
       <c r="G309" s="2"/>
-      <c r="H309" s="2"/>
+      <c r="H309" s="10"/>
       <c r="I309" s="2"/>
-      <c r="J309" s="2"/>
-      <c r="K309" s="2"/>
-      <c r="L309" s="2"/>
+      <c r="J309" s="7"/>
+      <c r="K309" s="7"/>
+      <c r="L309" s="7"/>
     </row>
     <row r="310" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A310" s="6"/>
+      <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
       <c r="D310" s="2"/>
       <c r="E310" s="2"/>
       <c r="F310" s="2"/>
       <c r="G310" s="2"/>
-      <c r="H310" s="2"/>
+      <c r="H310" s="10"/>
       <c r="I310" s="2"/>
-      <c r="J310" s="2"/>
-      <c r="K310" s="2"/>
-      <c r="L310" s="2"/>
+      <c r="J310" s="7"/>
+      <c r="K310" s="7"/>
+      <c r="L310" s="7"/>
     </row>
     <row r="311" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
       <c r="D311" s="2"/>
-      <c r="E311" s="6"/>
-      <c r="F311" s="6"/>
-      <c r="G311" s="6"/>
-      <c r="H311" s="2"/>
+      <c r="E311" s="2"/>
+      <c r="F311" s="2"/>
+      <c r="G311" s="2"/>
+      <c r="H311" s="10"/>
       <c r="I311" s="2"/>
-      <c r="J311" s="2"/>
-      <c r="K311" s="2"/>
-      <c r="L311" s="2"/>
+      <c r="J311" s="7"/>
+      <c r="K311" s="7"/>
+      <c r="L311" s="7"/>
     </row>
     <row r="312" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A312" s="2"/>
@@ -5509,25 +5800,25 @@
       <c r="E312" s="2"/>
       <c r="F312" s="2"/>
       <c r="G312" s="2"/>
-      <c r="H312" s="7"/>
+      <c r="H312" s="10"/>
       <c r="I312" s="2"/>
-      <c r="J312" s="6"/>
-      <c r="K312" s="6"/>
-      <c r="L312" s="6"/>
+      <c r="J312" s="7"/>
+      <c r="K312" s="7"/>
+      <c r="L312" s="7"/>
     </row>
     <row r="313" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
       <c r="D313" s="2"/>
-      <c r="E313" s="2"/>
-      <c r="F313" s="2"/>
-      <c r="G313" s="2"/>
-      <c r="H313" s="7"/>
+      <c r="E313" s="7"/>
+      <c r="F313" s="7"/>
+      <c r="G313" s="7"/>
+      <c r="H313" s="2"/>
       <c r="I313" s="2"/>
-      <c r="J313" s="6"/>
-      <c r="K313" s="6"/>
-      <c r="L313" s="6"/>
+      <c r="J313" s="2"/>
+      <c r="K313" s="2"/>
+      <c r="L313" s="2"/>
     </row>
     <row r="314" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A314" s="2"/>
@@ -5537,20 +5828,20 @@
       <c r="E314" s="2"/>
       <c r="F314" s="2"/>
       <c r="G314" s="2"/>
-      <c r="H314" s="7"/>
+      <c r="H314" s="10"/>
       <c r="I314" s="2"/>
-      <c r="J314" s="6"/>
-      <c r="K314" s="6"/>
-      <c r="L314" s="6"/>
+      <c r="J314" s="7"/>
+      <c r="K314" s="7"/>
+      <c r="L314" s="7"/>
     </row>
     <row r="315" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
       <c r="D315" s="2"/>
-      <c r="E315" s="6"/>
-      <c r="F315" s="6"/>
-      <c r="G315" s="6"/>
+      <c r="E315" s="7"/>
+      <c r="F315" s="7"/>
+      <c r="G315" s="7"/>
       <c r="H315" s="2"/>
       <c r="I315" s="2"/>
       <c r="J315" s="2"/>
@@ -5565,19 +5856,19 @@
       <c r="E316" s="2"/>
       <c r="F316" s="2"/>
       <c r="G316" s="2"/>
-      <c r="H316" s="7"/>
+      <c r="H316" s="10"/>
       <c r="I316" s="2"/>
-      <c r="J316" s="6"/>
-      <c r="K316" s="6"/>
-      <c r="L316" s="6"/>
+      <c r="J316" s="7"/>
+      <c r="K316" s="7"/>
+      <c r="L316" s="7"/>
     </row>
     <row r="317" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
       <c r="D317" s="2"/>
-      <c r="E317" s="6"/>
-      <c r="F317" s="6"/>
+      <c r="E317" s="7"/>
+      <c r="F317" s="7"/>
       <c r="G317" s="2"/>
       <c r="H317" s="2"/>
       <c r="I317" s="2"/>
@@ -5587,10 +5878,10 @@
     </row>
     <row r="318" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A318" s="2"/>
-      <c r="B318" s="6"/>
+      <c r="B318" s="7"/>
       <c r="C318" s="2"/>
       <c r="D318" s="2"/>
-      <c r="E318" s="6"/>
+      <c r="E318" s="7"/>
       <c r="F318" s="2"/>
       <c r="G318" s="2"/>
       <c r="H318" s="2"/>
@@ -5600,7 +5891,7 @@
       <c r="L318" s="2"/>
     </row>
     <row r="319" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A319" s="6"/>
+      <c r="A319" s="7"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
       <c r="D319" s="2"/>
@@ -5618,65 +5909,65 @@
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
       <c r="D320" s="2"/>
-      <c r="E320" s="2"/>
-      <c r="F320" s="2"/>
-      <c r="G320" s="6"/>
-      <c r="H320" s="7"/>
+      <c r="E320" s="7"/>
+      <c r="F320" s="7"/>
+      <c r="G320" s="7"/>
+      <c r="H320" s="2"/>
       <c r="I320" s="2"/>
-      <c r="J320" s="6"/>
-      <c r="K320" s="6"/>
-      <c r="L320" s="6"/>
+      <c r="J320" s="2"/>
+      <c r="K320" s="2"/>
+      <c r="L320" s="2"/>
     </row>
     <row r="321" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A321" s="2"/>
-      <c r="B321" s="6"/>
+      <c r="B321" s="2"/>
       <c r="C321" s="2"/>
       <c r="D321" s="2"/>
-      <c r="E321" s="6"/>
+      <c r="E321" s="2"/>
       <c r="F321" s="2"/>
       <c r="G321" s="2"/>
-      <c r="H321" s="7"/>
+      <c r="H321" s="10"/>
       <c r="I321" s="2"/>
-      <c r="J321" s="6"/>
-      <c r="K321" s="6"/>
-      <c r="L321" s="6"/>
+      <c r="J321" s="7"/>
+      <c r="K321" s="7"/>
+      <c r="L321" s="7"/>
     </row>
     <row r="322" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A322" s="2"/>
-      <c r="B322" s="6"/>
+      <c r="B322" s="2"/>
       <c r="C322" s="2"/>
       <c r="D322" s="2"/>
-      <c r="E322" s="6"/>
+      <c r="E322" s="2"/>
       <c r="F322" s="2"/>
       <c r="G322" s="2"/>
-      <c r="H322" s="7"/>
+      <c r="H322" s="10"/>
       <c r="I322" s="2"/>
-      <c r="J322" s="6"/>
-      <c r="K322" s="6"/>
-      <c r="L322" s="6"/>
+      <c r="J322" s="7"/>
+      <c r="K322" s="7"/>
+      <c r="L322" s="7"/>
     </row>
     <row r="323" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A323" s="2"/>
-      <c r="B323" s="6"/>
+      <c r="B323" s="2"/>
       <c r="C323" s="2"/>
       <c r="D323" s="2"/>
-      <c r="E323" s="6"/>
+      <c r="E323" s="2"/>
       <c r="F323" s="2"/>
       <c r="G323" s="2"/>
-      <c r="H323" s="2"/>
+      <c r="H323" s="10"/>
       <c r="I323" s="2"/>
-      <c r="J323" s="2"/>
-      <c r="K323" s="2"/>
-      <c r="L323" s="2"/>
+      <c r="J323" s="7"/>
+      <c r="K323" s="7"/>
+      <c r="L323" s="7"/>
     </row>
     <row r="324" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A324" s="6"/>
+      <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
       <c r="D324" s="2"/>
-      <c r="E324" s="2"/>
-      <c r="F324" s="2"/>
-      <c r="G324" s="2"/>
+      <c r="E324" s="7"/>
+      <c r="F324" s="7"/>
+      <c r="G324" s="7"/>
       <c r="H324" s="2"/>
       <c r="I324" s="2"/>
       <c r="J324" s="2"/>
@@ -5690,35 +5981,35 @@
       <c r="D325" s="2"/>
       <c r="E325" s="2"/>
       <c r="F325" s="2"/>
-      <c r="G325" s="6"/>
-      <c r="H325" s="7"/>
+      <c r="G325" s="2"/>
+      <c r="H325" s="10"/>
       <c r="I325" s="2"/>
-      <c r="J325" s="6"/>
-      <c r="K325" s="6"/>
-      <c r="L325" s="6"/>
+      <c r="J325" s="7"/>
+      <c r="K325" s="7"/>
+      <c r="L325" s="7"/>
     </row>
     <row r="326" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
       <c r="D326" s="2"/>
-      <c r="E326" s="2"/>
-      <c r="F326" s="2"/>
-      <c r="G326" s="6"/>
-      <c r="H326" s="7"/>
+      <c r="E326" s="7"/>
+      <c r="F326" s="7"/>
+      <c r="G326" s="2"/>
+      <c r="H326" s="2"/>
       <c r="I326" s="2"/>
-      <c r="J326" s="6"/>
-      <c r="K326" s="6"/>
-      <c r="L326" s="6"/>
+      <c r="J326" s="2"/>
+      <c r="K326" s="2"/>
+      <c r="L326" s="2"/>
     </row>
     <row r="327" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A327" s="2"/>
-      <c r="B327" s="2"/>
+      <c r="B327" s="7"/>
       <c r="C327" s="2"/>
       <c r="D327" s="2"/>
-      <c r="E327" s="6"/>
-      <c r="F327" s="6"/>
-      <c r="G327" s="6"/>
+      <c r="E327" s="7"/>
+      <c r="F327" s="2"/>
+      <c r="G327" s="2"/>
       <c r="H327" s="2"/>
       <c r="I327" s="2"/>
       <c r="J327" s="2"/>
@@ -5726,18 +6017,18 @@
       <c r="L327" s="2"/>
     </row>
     <row r="328" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A328" s="2"/>
+      <c r="A328" s="7"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
       <c r="D328" s="2"/>
       <c r="E328" s="2"/>
       <c r="F328" s="2"/>
       <c r="G328" s="2"/>
-      <c r="H328" s="7"/>
+      <c r="H328" s="2"/>
       <c r="I328" s="2"/>
-      <c r="J328" s="6"/>
-      <c r="K328" s="6"/>
-      <c r="L328" s="6"/>
+      <c r="J328" s="2"/>
+      <c r="K328" s="2"/>
+      <c r="L328" s="2"/>
     </row>
     <row r="329" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A329" s="2"/>
@@ -5746,105 +6037,105 @@
       <c r="D329" s="2"/>
       <c r="E329" s="2"/>
       <c r="F329" s="2"/>
-      <c r="G329" s="6"/>
-      <c r="H329" s="7"/>
+      <c r="G329" s="7"/>
+      <c r="H329" s="10"/>
       <c r="I329" s="2"/>
-      <c r="J329" s="6"/>
-      <c r="K329" s="6"/>
-      <c r="L329" s="6"/>
+      <c r="J329" s="7"/>
+      <c r="K329" s="7"/>
+      <c r="L329" s="7"/>
     </row>
     <row r="330" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A330" s="2"/>
-      <c r="B330" s="6"/>
+      <c r="B330" s="7"/>
       <c r="C330" s="2"/>
       <c r="D330" s="2"/>
-      <c r="E330" s="6"/>
+      <c r="E330" s="7"/>
       <c r="F330" s="2"/>
       <c r="G330" s="2"/>
-      <c r="H330" s="7"/>
+      <c r="H330" s="10"/>
       <c r="I330" s="2"/>
-      <c r="J330" s="6"/>
-      <c r="K330" s="6"/>
-      <c r="L330" s="6"/>
+      <c r="J330" s="7"/>
+      <c r="K330" s="7"/>
+      <c r="L330" s="7"/>
     </row>
     <row r="331" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A331" s="2"/>
-      <c r="B331" s="6"/>
+      <c r="B331" s="7"/>
       <c r="C331" s="2"/>
       <c r="D331" s="2"/>
-      <c r="E331" s="6"/>
+      <c r="E331" s="7"/>
       <c r="F331" s="2"/>
       <c r="G331" s="2"/>
-      <c r="H331" s="7"/>
+      <c r="H331" s="10"/>
       <c r="I331" s="2"/>
-      <c r="J331" s="6"/>
-      <c r="K331" s="6"/>
-      <c r="L331" s="6"/>
+      <c r="J331" s="7"/>
+      <c r="K331" s="7"/>
+      <c r="L331" s="7"/>
     </row>
     <row r="332" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A332" s="2"/>
-      <c r="B332" s="6"/>
+      <c r="B332" s="7"/>
       <c r="C332" s="2"/>
       <c r="D332" s="2"/>
-      <c r="E332" s="6"/>
+      <c r="E332" s="7"/>
       <c r="F332" s="2"/>
       <c r="G332" s="2"/>
-      <c r="H332" s="7"/>
+      <c r="H332" s="2"/>
       <c r="I332" s="2"/>
-      <c r="J332" s="6"/>
-      <c r="K332" s="6"/>
-      <c r="L332" s="6"/>
+      <c r="J332" s="2"/>
+      <c r="K332" s="2"/>
+      <c r="L332" s="2"/>
     </row>
     <row r="333" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A333" s="2"/>
-      <c r="B333" s="6"/>
+      <c r="A333" s="7"/>
+      <c r="B333" s="2"/>
       <c r="C333" s="2"/>
       <c r="D333" s="2"/>
-      <c r="E333" s="6"/>
+      <c r="E333" s="2"/>
       <c r="F333" s="2"/>
       <c r="G333" s="2"/>
-      <c r="H333" s="7"/>
+      <c r="H333" s="2"/>
       <c r="I333" s="2"/>
-      <c r="J333" s="6"/>
-      <c r="K333" s="6"/>
-      <c r="L333" s="6"/>
+      <c r="J333" s="2"/>
+      <c r="K333" s="2"/>
+      <c r="L333" s="2"/>
     </row>
     <row r="334" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A334" s="2"/>
-      <c r="B334" s="6"/>
+      <c r="B334" s="2"/>
       <c r="C334" s="2"/>
       <c r="D334" s="2"/>
-      <c r="E334" s="6"/>
+      <c r="E334" s="2"/>
       <c r="F334" s="2"/>
-      <c r="G334" s="2"/>
-      <c r="H334" s="7"/>
+      <c r="G334" s="7"/>
+      <c r="H334" s="10"/>
       <c r="I334" s="2"/>
-      <c r="J334" s="6"/>
-      <c r="K334" s="6"/>
-      <c r="L334" s="6"/>
+      <c r="J334" s="7"/>
+      <c r="K334" s="7"/>
+      <c r="L334" s="7"/>
     </row>
     <row r="335" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A335" s="2"/>
-      <c r="B335" s="6"/>
+      <c r="B335" s="2"/>
       <c r="C335" s="2"/>
       <c r="D335" s="2"/>
-      <c r="E335" s="6"/>
+      <c r="E335" s="2"/>
       <c r="F335" s="2"/>
-      <c r="G335" s="2"/>
-      <c r="H335" s="7"/>
+      <c r="G335" s="7"/>
+      <c r="H335" s="10"/>
       <c r="I335" s="2"/>
-      <c r="J335" s="6"/>
-      <c r="K335" s="6"/>
-      <c r="L335" s="6"/>
+      <c r="J335" s="7"/>
+      <c r="K335" s="7"/>
+      <c r="L335" s="7"/>
     </row>
     <row r="336" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A336" s="6"/>
+      <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
       <c r="D336" s="2"/>
-      <c r="E336" s="2"/>
-      <c r="F336" s="2"/>
-      <c r="G336" s="2"/>
+      <c r="E336" s="7"/>
+      <c r="F336" s="7"/>
+      <c r="G336" s="7"/>
       <c r="H336" s="2"/>
       <c r="I336" s="2"/>
       <c r="J336" s="2"/>
@@ -5856,14 +6147,14 @@
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
       <c r="D337" s="2"/>
-      <c r="E337" s="6"/>
-      <c r="F337" s="6"/>
-      <c r="G337" s="6"/>
-      <c r="H337" s="2"/>
+      <c r="E337" s="2"/>
+      <c r="F337" s="2"/>
+      <c r="G337" s="2"/>
+      <c r="H337" s="10"/>
       <c r="I337" s="2"/>
-      <c r="J337" s="2"/>
-      <c r="K337" s="2"/>
-      <c r="L337" s="2"/>
+      <c r="J337" s="7"/>
+      <c r="K337" s="7"/>
+      <c r="L337" s="7"/>
     </row>
     <row r="338" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A338" s="2"/>
@@ -5872,99 +6163,99 @@
       <c r="D338" s="2"/>
       <c r="E338" s="2"/>
       <c r="F338" s="2"/>
-      <c r="G338" s="2"/>
-      <c r="H338" s="7"/>
+      <c r="G338" s="7"/>
+      <c r="H338" s="10"/>
       <c r="I338" s="2"/>
-      <c r="J338" s="6"/>
-      <c r="K338" s="6"/>
-      <c r="L338" s="6"/>
+      <c r="J338" s="7"/>
+      <c r="K338" s="7"/>
+      <c r="L338" s="7"/>
     </row>
     <row r="339" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A339" s="2"/>
-      <c r="B339" s="2"/>
+      <c r="B339" s="7"/>
       <c r="C339" s="2"/>
       <c r="D339" s="2"/>
-      <c r="E339" s="6"/>
-      <c r="F339" s="6"/>
-      <c r="G339" s="6"/>
-      <c r="H339" s="2"/>
+      <c r="E339" s="7"/>
+      <c r="F339" s="2"/>
+      <c r="G339" s="2"/>
+      <c r="H339" s="10"/>
       <c r="I339" s="2"/>
-      <c r="J339" s="2"/>
-      <c r="K339" s="2"/>
-      <c r="L339" s="2"/>
+      <c r="J339" s="7"/>
+      <c r="K339" s="7"/>
+      <c r="L339" s="7"/>
     </row>
     <row r="340" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A340" s="2"/>
-      <c r="B340" s="2"/>
+      <c r="B340" s="7"/>
       <c r="C340" s="2"/>
       <c r="D340" s="2"/>
-      <c r="E340" s="6"/>
-      <c r="F340" s="6"/>
+      <c r="E340" s="7"/>
+      <c r="F340" s="2"/>
       <c r="G340" s="2"/>
-      <c r="H340" s="2"/>
+      <c r="H340" s="10"/>
       <c r="I340" s="2"/>
-      <c r="J340" s="2"/>
-      <c r="K340" s="2"/>
-      <c r="L340" s="2"/>
+      <c r="J340" s="7"/>
+      <c r="K340" s="7"/>
+      <c r="L340" s="7"/>
     </row>
     <row r="341" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A341" s="2"/>
-      <c r="B341" s="2"/>
+      <c r="B341" s="7"/>
       <c r="C341" s="2"/>
       <c r="D341" s="2"/>
-      <c r="E341" s="2"/>
+      <c r="E341" s="7"/>
       <c r="F341" s="2"/>
-      <c r="G341" s="6"/>
-      <c r="H341" s="7"/>
+      <c r="G341" s="2"/>
+      <c r="H341" s="10"/>
       <c r="I341" s="2"/>
-      <c r="J341" s="6"/>
-      <c r="K341" s="6"/>
-      <c r="L341" s="6"/>
+      <c r="J341" s="7"/>
+      <c r="K341" s="7"/>
+      <c r="L341" s="7"/>
     </row>
     <row r="342" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A342" s="2"/>
-      <c r="B342" s="2"/>
+      <c r="B342" s="7"/>
       <c r="C342" s="2"/>
       <c r="D342" s="2"/>
-      <c r="E342" s="2"/>
+      <c r="E342" s="7"/>
       <c r="F342" s="2"/>
-      <c r="G342" s="19"/>
-      <c r="H342" s="7"/>
+      <c r="G342" s="2"/>
+      <c r="H342" s="10"/>
       <c r="I342" s="2"/>
-      <c r="J342" s="19"/>
-      <c r="K342" s="19"/>
-      <c r="L342" s="19"/>
+      <c r="J342" s="7"/>
+      <c r="K342" s="7"/>
+      <c r="L342" s="7"/>
     </row>
     <row r="343" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A343" s="2"/>
-      <c r="B343" s="2"/>
+      <c r="B343" s="7"/>
       <c r="C343" s="2"/>
       <c r="D343" s="2"/>
-      <c r="E343" s="2"/>
+      <c r="E343" s="7"/>
       <c r="F343" s="2"/>
       <c r="G343" s="2"/>
-      <c r="H343" s="2"/>
+      <c r="H343" s="10"/>
       <c r="I343" s="2"/>
-      <c r="J343" s="2"/>
-      <c r="K343" s="2"/>
-      <c r="L343" s="2"/>
+      <c r="J343" s="7"/>
+      <c r="K343" s="7"/>
+      <c r="L343" s="7"/>
     </row>
     <row r="344" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A344" s="2"/>
-      <c r="B344" s="2"/>
+      <c r="B344" s="7"/>
       <c r="C344" s="2"/>
       <c r="D344" s="2"/>
-      <c r="E344" s="2"/>
+      <c r="E344" s="7"/>
       <c r="F344" s="2"/>
       <c r="G344" s="2"/>
-      <c r="H344" s="2"/>
+      <c r="H344" s="10"/>
       <c r="I344" s="2"/>
-      <c r="J344" s="2"/>
-      <c r="K344" s="2"/>
-      <c r="L344" s="2"/>
+      <c r="J344" s="7"/>
+      <c r="K344" s="7"/>
+      <c r="L344" s="7"/>
     </row>
     <row r="345" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A345" s="2"/>
+      <c r="A345" s="7"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
       <c r="D345" s="2"/>
@@ -5982,9 +6273,9 @@
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
       <c r="D346" s="2"/>
-      <c r="E346" s="2"/>
-      <c r="F346" s="2"/>
-      <c r="G346" s="2"/>
+      <c r="E346" s="7"/>
+      <c r="F346" s="7"/>
+      <c r="G346" s="7"/>
       <c r="H346" s="2"/>
       <c r="I346" s="2"/>
       <c r="J346" s="2"/>
@@ -5999,20 +6290,20 @@
       <c r="E347" s="2"/>
       <c r="F347" s="2"/>
       <c r="G347" s="2"/>
-      <c r="H347" s="2"/>
+      <c r="H347" s="10"/>
       <c r="I347" s="2"/>
-      <c r="J347" s="2"/>
-      <c r="K347" s="2"/>
-      <c r="L347" s="2"/>
+      <c r="J347" s="7"/>
+      <c r="K347" s="7"/>
+      <c r="L347" s="7"/>
     </row>
     <row r="348" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
       <c r="D348" s="2"/>
-      <c r="E348" s="2"/>
-      <c r="F348" s="2"/>
-      <c r="G348" s="2"/>
+      <c r="E348" s="7"/>
+      <c r="F348" s="7"/>
+      <c r="G348" s="7"/>
       <c r="H348" s="2"/>
       <c r="I348" s="2"/>
       <c r="J348" s="2"/>
@@ -6024,8 +6315,8 @@
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
       <c r="D349" s="2"/>
-      <c r="E349" s="2"/>
-      <c r="F349" s="2"/>
+      <c r="E349" s="7"/>
+      <c r="F349" s="7"/>
       <c r="G349" s="2"/>
       <c r="H349" s="2"/>
       <c r="I349" s="2"/>
@@ -6040,12 +6331,12 @@
       <c r="D350" s="2"/>
       <c r="E350" s="2"/>
       <c r="F350" s="2"/>
-      <c r="G350" s="2"/>
-      <c r="H350" s="2"/>
+      <c r="G350" s="7"/>
+      <c r="H350" s="10"/>
       <c r="I350" s="2"/>
-      <c r="J350" s="2"/>
-      <c r="K350" s="2"/>
-      <c r="L350" s="2"/>
+      <c r="J350" s="7"/>
+      <c r="K350" s="7"/>
+      <c r="L350" s="7"/>
     </row>
     <row r="351" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A351" s="2"/>
@@ -6054,12 +6345,12 @@
       <c r="D351" s="2"/>
       <c r="E351" s="2"/>
       <c r="F351" s="2"/>
-      <c r="G351" s="2"/>
-      <c r="H351" s="2"/>
+      <c r="G351" s="13"/>
+      <c r="H351" s="10"/>
       <c r="I351" s="2"/>
-      <c r="J351" s="2"/>
-      <c r="K351" s="2"/>
-      <c r="L351" s="2"/>
+      <c r="J351" s="13"/>
+      <c r="K351" s="13"/>
+      <c r="L351" s="13"/>
     </row>
     <row r="352" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A352" s="2"/>
@@ -6665,10 +6956,10 @@
     </row>
     <row r="395" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A395" s="2"/>
-      <c r="B395" s="6"/>
+      <c r="B395" s="2"/>
       <c r="C395" s="2"/>
       <c r="D395" s="2"/>
-      <c r="E395" s="6"/>
+      <c r="E395" s="2"/>
       <c r="F395" s="2"/>
       <c r="G395" s="2"/>
       <c r="H395" s="2"/>
@@ -6791,10 +7082,10 @@
     </row>
     <row r="404" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A404" s="2"/>
-      <c r="B404" s="2"/>
+      <c r="B404" s="7"/>
       <c r="C404" s="2"/>
       <c r="D404" s="2"/>
-      <c r="E404" s="2"/>
+      <c r="E404" s="7"/>
       <c r="F404" s="2"/>
       <c r="G404" s="2"/>
       <c r="H404" s="2"/>
@@ -6995,9 +7286,9 @@
       <c r="G418" s="2"/>
       <c r="H418" s="2"/>
       <c r="I418" s="2"/>
-      <c r="J418" s="6"/>
-      <c r="K418" s="6"/>
-      <c r="L418" s="6"/>
+      <c r="J418" s="2"/>
+      <c r="K418" s="2"/>
+      <c r="L418" s="2"/>
     </row>
     <row r="419" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A419" s="2"/>
@@ -7015,10 +7306,10 @@
     </row>
     <row r="420" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A420" s="2"/>
-      <c r="B420" s="6"/>
+      <c r="B420" s="2"/>
       <c r="C420" s="2"/>
       <c r="D420" s="2"/>
-      <c r="E420" s="6"/>
+      <c r="E420" s="2"/>
       <c r="F420" s="2"/>
       <c r="G420" s="2"/>
       <c r="H420" s="2"/>
@@ -7121,8 +7412,9 @@
       <c r="G427" s="2"/>
       <c r="H427" s="2"/>
       <c r="I427" s="2"/>
-      <c r="J427" s="2"/>
-      <c r="K427" s="2"/>
+      <c r="J427" s="7"/>
+      <c r="K427" s="7"/>
+      <c r="L427" s="7"/>
     </row>
     <row r="428" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A428" s="2"/>
@@ -7136,32 +7428,157 @@
       <c r="I428" s="2"/>
       <c r="J428" s="2"/>
       <c r="K428" s="2"/>
+      <c r="L428" s="2"/>
     </row>
     <row r="429" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A429" s="2"/>
-      <c r="B429" s="2"/>
+      <c r="B429" s="7"/>
       <c r="C429" s="2"/>
       <c r="D429" s="2"/>
-      <c r="E429" s="2"/>
+      <c r="E429" s="7"/>
       <c r="F429" s="2"/>
       <c r="G429" s="2"/>
       <c r="H429" s="2"/>
       <c r="I429" s="2"/>
       <c r="J429" s="2"/>
       <c r="K429" s="2"/>
+      <c r="L429" s="2"/>
     </row>
     <row r="430" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A430" s="2"/>
-      <c r="B430" s="6"/>
+      <c r="B430" s="2"/>
       <c r="C430" s="2"/>
       <c r="D430" s="2"/>
-      <c r="E430" s="6"/>
+      <c r="E430" s="2"/>
       <c r="F430" s="2"/>
       <c r="G430" s="2"/>
       <c r="H430" s="2"/>
       <c r="I430" s="2"/>
       <c r="J430" s="2"/>
       <c r="K430" s="2"/>
+      <c r="L430" s="2"/>
+    </row>
+    <row r="431" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A431" s="2"/>
+      <c r="B431" s="2"/>
+      <c r="C431" s="2"/>
+      <c r="D431" s="2"/>
+      <c r="E431" s="2"/>
+      <c r="F431" s="2"/>
+      <c r="G431" s="2"/>
+      <c r="H431" s="2"/>
+      <c r="I431" s="2"/>
+      <c r="J431" s="2"/>
+      <c r="K431" s="2"/>
+      <c r="L431" s="2"/>
+    </row>
+    <row r="432" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A432" s="2"/>
+      <c r="B432" s="2"/>
+      <c r="C432" s="2"/>
+      <c r="D432" s="2"/>
+      <c r="E432" s="2"/>
+      <c r="F432" s="2"/>
+      <c r="G432" s="2"/>
+      <c r="H432" s="2"/>
+      <c r="I432" s="2"/>
+      <c r="J432" s="2"/>
+      <c r="K432" s="2"/>
+      <c r="L432" s="2"/>
+    </row>
+    <row r="433" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A433" s="2"/>
+      <c r="B433" s="2"/>
+      <c r="C433" s="2"/>
+      <c r="D433" s="2"/>
+      <c r="E433" s="2"/>
+      <c r="F433" s="2"/>
+      <c r="G433" s="2"/>
+      <c r="H433" s="2"/>
+      <c r="I433" s="2"/>
+      <c r="J433" s="2"/>
+      <c r="K433" s="2"/>
+      <c r="L433" s="2"/>
+    </row>
+    <row r="434" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A434" s="2"/>
+      <c r="B434" s="2"/>
+      <c r="C434" s="2"/>
+      <c r="D434" s="2"/>
+      <c r="E434" s="2"/>
+      <c r="F434" s="2"/>
+      <c r="G434" s="2"/>
+      <c r="H434" s="2"/>
+      <c r="I434" s="2"/>
+      <c r="J434" s="2"/>
+      <c r="K434" s="2"/>
+      <c r="L434" s="2"/>
+    </row>
+    <row r="435" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A435" s="2"/>
+      <c r="B435" s="2"/>
+      <c r="C435" s="2"/>
+      <c r="D435" s="2"/>
+      <c r="E435" s="2"/>
+      <c r="F435" s="2"/>
+      <c r="G435" s="2"/>
+      <c r="H435" s="2"/>
+      <c r="I435" s="2"/>
+      <c r="J435" s="2"/>
+      <c r="K435" s="2"/>
+      <c r="L435" s="2"/>
+    </row>
+    <row r="436" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A436" s="2"/>
+      <c r="B436" s="2"/>
+      <c r="C436" s="2"/>
+      <c r="D436" s="2"/>
+      <c r="E436" s="2"/>
+      <c r="F436" s="2"/>
+      <c r="G436" s="2"/>
+      <c r="H436" s="2"/>
+      <c r="I436" s="2"/>
+      <c r="J436" s="2"/>
+      <c r="K436" s="2"/>
+    </row>
+    <row r="437" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A437" s="2"/>
+      <c r="B437" s="2"/>
+      <c r="C437" s="2"/>
+      <c r="D437" s="2"/>
+      <c r="E437" s="2"/>
+      <c r="F437" s="2"/>
+      <c r="G437" s="2"/>
+      <c r="H437" s="2"/>
+      <c r="I437" s="2"/>
+      <c r="J437" s="2"/>
+      <c r="K437" s="2"/>
+    </row>
+    <row r="438" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A438" s="2"/>
+      <c r="B438" s="2"/>
+      <c r="C438" s="2"/>
+      <c r="D438" s="2"/>
+      <c r="E438" s="2"/>
+      <c r="F438" s="2"/>
+      <c r="G438" s="2"/>
+      <c r="H438" s="2"/>
+      <c r="I438" s="2"/>
+      <c r="J438" s="2"/>
+      <c r="K438" s="2"/>
+    </row>
+    <row r="439" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A439" s="2"/>
+      <c r="B439" s="7"/>
+      <c r="C439" s="2"/>
+      <c r="D439" s="2"/>
+      <c r="E439" s="7"/>
+      <c r="F439" s="2"/>
+      <c r="G439" s="2"/>
+      <c r="H439" s="2"/>
+      <c r="I439" s="2"/>
+      <c r="J439" s="2"/>
+      <c r="K439" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
